--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
   <si>
     <t>Loans: monthly payments, prepayment, borrower credit, and funding</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Funding discount factors multiply EURIBOR12m by a separate treasury-spread curve.</t>
   </si>
   <si>
-    <t>FairRate solves a uniform fixed coupon or floating margin at origination. Introductory/bounded schedules omit this unsupported solve.</t>
+    <t>FairRate bootstraps each rate segment: repay remaining capital at its end, solve, lock, and extend. Arrays are transposed into a row; bounded coupons omit the solve.</t>
   </si>
   <si>
     <t>Cashflows include scheduled receipts, prepayments, and recovery in legs 0, 1, and 2. Bounded coupons exclude option time value.</t>
@@ -242,7 +242,13 @@
     <t>PV less advance</t>
   </si>
   <si>
-    <t>Fair coupon / spread</t>
+    <t>Fair first segment</t>
+  </si>
+  <si>
+    <t>Fair second segment</t>
+  </si>
+  <si>
+    <t>Fair third segment</t>
   </si>
   <si>
     <t>French</t>
@@ -278,15 +284,15 @@
     <t>{"introductory_periods": 60, "introductory_rate": 0.04}</t>
   </si>
   <si>
-    <t>Unsupported for mixed/bounded coupons</t>
-  </si>
-  <si>
     <t>Bounded floating</t>
   </si>
   <si>
     <t>{"amortization_rate": 0.05, "floor": 0.02, "cap": 0.045}</t>
   </si>
   <si>
+    <t>Unsupported for bounded coupons</t>
+  </si>
+  <si>
     <t>15% annual CPR</t>
   </si>
   <si>
@@ -309,6 +315,18 @@
   </si>
   <si>
     <t>{"amortization_rate": 0.05, "discount_index": {"Other": "FUNDING"}}</t>
+  </si>
+  <si>
+    <t>Stepped fixed</t>
+  </si>
+  <si>
+    <t>{"coupon_segments": [{"rate": 0.03, "periods": 60}, {"rate": 0.04, "periods": 60}, {"rate": 0.05}]}</t>
+  </si>
+  <si>
+    <t>Stepped then floating</t>
+  </si>
+  <si>
+    <t>{"coupon_segments": [{"rate": 0.03, "periods": 60}, {"rate": 0.04, "periods": 60}, {"rate": 0.01, "market_index": "EURIBOR12m"}]}</t>
   </si>
   <si>
     <t>French contractual receipts</t>
@@ -1195,17 +1213,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:L14"/>
+  <dimension ref="A4:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
     <col min="2" max="4" width="22.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="70.7109375" customWidth="1"/>
     <col min="6" max="6" width="48.7109375" customWidth="1"/>
-    <col min="7" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="22.7109375" style="1" customWidth="1"/>
+    <col min="9" max="11" width="21.7109375" style="6" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
         <v>58</v>
       </c>
@@ -1233,10 +1253,16 @@
       <c r="I4" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1244,10 +1270,10 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F5" cm="1">
         <f t="array" ref="F5">_xll.QS.TRADE.LOAN("Loans.Case5",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B5,C5,D5,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E5)</f>
@@ -1262,13 +1288,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="6" cm="1">
-        <f t="array" ref="I5">_xll.QS.FAIR.RATE(F5,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <f t="array" ref="I5">_xll.QS.FAIR.RATE(F5,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1276,10 +1302,10 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F6" cm="1">
         <f t="array" ref="F6">_xll.QS.TRADE.LOAN("Loans.Case6",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B6,C6,D6,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E6)</f>
@@ -1294,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" cm="1">
-        <f t="array" ref="I6">_xll.QS.FAIR.RATE(F6,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <f t="array" ref="I6">_xll.QS.FAIR.RATE(F6,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1308,10 +1334,10 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" cm="1">
         <f t="array" ref="F7">_xll.QS.TRADE.LOAN("Loans.Case7",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B7,C7,D7,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E7)</f>
@@ -1326,26 +1352,26 @@
         <v>0</v>
       </c>
       <c r="I7" s="6" cm="1">
-        <f t="array" ref="I7">_xll.QS.FAIR.RATE(F7,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <f t="array" ref="I7">_xll.QS.FAIR.RATE(F7,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="6">
         <f>'Loan Inputs'!B6</f>
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8" cm="1">
         <f t="array" ref="F8">_xll.QS.TRADE.LOAN("Loans.Case8",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B8,C8,D8,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E8)</f>
@@ -1360,26 +1386,26 @@
         <v>0</v>
       </c>
       <c r="I8" s="6" cm="1">
-        <f t="array" ref="I8">_xll.QS.FAIR.RATE(F8,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <f t="array" ref="I8">_xll.QS.FAIR.RATE(F8,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B9" s="6">
         <f>'Loan Inputs'!B6</f>
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" cm="1">
         <f t="array" ref="F9">_xll.QS.TRADE.LOAN("Loans.Case9",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B9,C9,D9,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E9)</f>
@@ -1393,26 +1419,27 @@
         <f>G9-'Loan Inputs'!$B$4</f>
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="I9" s="6" cm="1">
+        <f t="array" ref="I9">_xll.QS.FAIR.RATE(F9,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="6">
         <f>'Loan Inputs'!B6</f>
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F10" cm="1">
         <f t="array" ref="F10">_xll.QS.TRADE.LOAN("Loans.Case10",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B10,C10,D10,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E10)</f>
@@ -1426,13 +1453,13 @@
         <f>G10-'Loan Inputs'!$B$4</f>
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="I10" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B11" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1440,10 +1467,10 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11" cm="1">
         <f t="array" ref="F11">_xll.QS.TRADE.LOAN("Loans.Case11",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B11,C11,D11,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E11)</f>
@@ -1458,13 +1485,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="6" cm="1">
-        <f t="array" ref="I11">_xll.QS.FAIR.RATE(F11,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <f t="array" ref="I11">_xll.QS.FAIR.RATE(F11,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1472,10 +1499,10 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F12" cm="1">
         <f t="array" ref="F12">_xll.QS.TRADE.LOAN("Loans.Case12",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B12,C12,D12,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E12)</f>
@@ -1490,13 +1517,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="6" cm="1">
-        <f t="array" ref="I12">_xll.QS.FAIR.RATE(F12,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <f t="array" ref="I12">_xll.QS.FAIR.RATE(F12,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="6">
         <f>'Loan Inputs'!B5</f>
@@ -1504,10 +1531,10 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13" cm="1">
         <f t="array" ref="F13">_xll.QS.TRADE.LOAN("Loans.Case13",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B13,C13,D13,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E13)</f>
@@ -1522,26 +1549,26 @@
         <v>0</v>
       </c>
       <c r="I13" s="6" cm="1">
-        <f t="array" ref="I13">_xll.QS.FAIR.RATE(F13,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <f t="array" ref="I13">_xll.QS.FAIR.RATE(F13,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B14" s="6">
         <f>'Loan Inputs'!B6</f>
         <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14" cm="1">
         <f t="array" ref="F14">_xll.QS.TRADE.LOAN("Loans.Case14",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B14,C14,D14,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E14)</f>
@@ -1556,7 +1583,69 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" cm="1">
-        <f t="array" ref="I14">_xll.QS.FAIR.RATE(F14,Market!$F$11)</f>
+        <f t="array" ref="I14">_xll.QS.FAIR.RATE(F14,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" cm="1">
+        <f t="array" ref="F15">_xll.QS.TRADE.LOAN("Loans.Case15",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B15,C15,D15,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E15)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" cm="1">
+        <f t="array" ref="G15">_xll.QS.PRICE(F15,Market!$F$11)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <f>G15-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" cm="1">
+        <f t="array" ref="I15">_xll.QS.FAIR.RATE(F15,Market!$F$11,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" cm="1">
+        <f t="array" ref="F16">_xll.QS.TRADE.LOAN("Loans.Case16",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B16,C16,D16,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E16)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" cm="1">
+        <f t="array" ref="G16">_xll.QS.PRICE(F16,Market!$F$11)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
+        <f>G16-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" cm="1">
+        <f t="array" ref="I16">_xll.QS.FAIR.RATE(F16,Market!$F$11,TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1575,10 +1664,10 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1606,10 +1695,10 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1624,7 +1713,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1731,7 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1653,7 +1742,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1664,7 +1753,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1">

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -4,16 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Market" sheetId="2" r:id="rId2"/>
     <sheet name="Loan Inputs" sheetId="3" r:id="rId3"/>
-    <sheet name="Comparison" sheetId="4" r:id="rId4"/>
-    <sheet name="Cashflows" sheetId="5" r:id="rId5"/>
-    <sheet name="Risk" sheetId="6" r:id="rId6"/>
-    <sheet name="Layouts" sheetId="7" r:id="rId7"/>
+    <sheet name="Loan Settings" sheetId="4" r:id="rId4"/>
+    <sheet name="Coupon Schedules" sheetId="5" r:id="rId5"/>
+    <sheet name="Pricing" sheetId="6" r:id="rId6"/>
+    <sheet name="Comparison" sheetId="7" r:id="rId7"/>
+    <sheet name="Cashflows" sheetId="8" r:id="rId8"/>
+    <sheet name="Risk" sheetId="9" r:id="rId9"/>
+    <sheet name="Layouts" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="121">
   <si>
     <t>Loans: monthly payments, prepayment, borrower credit, and funding</t>
   </si>
@@ -65,7 +68,7 @@
     <t>Funding discount factors multiply EURIBOR12m by a separate treasury-spread curve.</t>
   </si>
   <si>
-    <t>FairRate bootstraps each rate segment: repay remaining capital at its end, solve, lock, and extend. Arrays are transposed into a row; bounded coupons omit the solve.</t>
+    <t>FairRate bootstraps each rate segment: repay remaining capital at its end, solve, lock, and extend. Each FairRate(index) request returns one scalar; bounded coupons omit the solve.</t>
   </si>
   <si>
     <t>Cashflows include scheduled receipts, prepayments, and recovery in legs 0, 1, and 2. Bounded coupons exclude option time value.</t>
@@ -146,10 +149,31 @@
     <t>Quote store revision</t>
   </si>
   <si>
+    <t>Credit configurations</t>
+  </si>
+  <si>
     <t>Borrower credit configuration</t>
   </si>
   <si>
-    <t>Native credit configuration JSON (illustrative borrower proxy)</t>
+    <t>Credit index</t>
+  </si>
+  <si>
+    <t>Credit:BORROWER</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Discount index</t>
+  </si>
+  <si>
+    <t>ESTR</t>
+  </si>
+  <si>
+    <t>Recovery</t>
   </si>
   <si>
     <t>Cds_BORROWER_EUR_1Y</t>
@@ -173,9 +197,6 @@
     <t>Cds_BORROWER_EUR_35Y</t>
   </si>
   <si>
-    <t>[{"market_index": {"Credit": "BORROWER"}, "currency": "EUR", "discount_index": "ESTR", "recovery": 0.4, "quotes": ["Cds_BORROWER_EUR_1Y", "Cds_BORROWER_EUR_3Y", "Cds_BORROWER_EUR_5Y", "Cds_BORROWER_EUR_10Y", "Cds_BORROWER_EUR_20Y", "Cds_BORROWER_EUR_30Y", "Cds_BORROWER_EUR_35Y"]}]</t>
-  </si>
-  <si>
     <t>Principal (EUR)</t>
   </si>
   <si>
@@ -206,18 +227,33 @@
     <t>Actual360</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
     <t>Floating principal is agreed at a 5% initial all-in rate; annual resets use EURIBOR12m metadata.</t>
   </si>
   <si>
     <t>The default zero fixing lag makes the first observation today's projected fixing; no historical fixing is required.</t>
   </si>
   <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>FUNDING</t>
+  </si>
+  <si>
+    <t>Native discount policy</t>
+  </si>
+  <si>
+    <t>Native pricer</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Cashflows</t>
+  </si>
+  <si>
+    <t>Sensitivities</t>
+  </si>
+  <si>
     <t>Case</t>
   </si>
   <si>
@@ -230,7 +266,7 @@
     <t>Repayment</t>
   </si>
   <si>
-    <t>Options JSON</t>
+    <t>Editable settings / coupons</t>
   </si>
   <si>
     <t>Loan trade</t>
@@ -251,10 +287,28 @@
     <t>Fair third segment</t>
   </si>
   <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>Pricer</t>
+  </si>
+  <si>
+    <t>Evaluation results</t>
+  </si>
+  <si>
+    <t>Fair target 0 results</t>
+  </si>
+  <si>
+    <t>Fair target 1 results</t>
+  </si>
+  <si>
+    <t>Fair target 2 results</t>
+  </si>
+  <si>
     <t>French</t>
   </si>
   <si>
-    <t>{}</t>
+    <t>Default settings</t>
   </si>
   <si>
     <t>Bullet</t>
@@ -263,31 +317,49 @@
     <t>25% balloon</t>
   </si>
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Balloon fraction</t>
+  </si>
+  <si>
     <t>Balloon</t>
   </si>
   <si>
-    <t>{"balloon_fraction": 0.25}</t>
+    <t>Edit settings</t>
   </si>
   <si>
     <t>Floating</t>
   </si>
   <si>
+    <t>Amortization rate</t>
+  </si>
+  <si>
     <t>EURIBOR12m</t>
   </si>
   <si>
-    <t>{"amortization_rate": 0.05}</t>
-  </si>
-  <si>
     <t>5-year introductory fixed</t>
   </si>
   <si>
-    <t>{"introductory_periods": 60, "introductory_rate": 0.04}</t>
+    <t>Periods</t>
+  </si>
+  <si>
+    <t>Rate / spread</t>
+  </si>
+  <si>
+    <t>Market index</t>
+  </si>
+  <si>
+    <t>Edit coupon schedule</t>
   </si>
   <si>
     <t>Bounded floating</t>
   </si>
   <si>
-    <t>{"amortization_rate": 0.05, "floor": 0.02, "cap": 0.045}</t>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>Cap</t>
   </si>
   <si>
     <t>Unsupported for bounded coupons</t>
@@ -296,37 +368,22 @@
     <t>15% annual CPR</t>
   </si>
   <si>
-    <t>{"prepayment": {"Cpr": 0.15}}</t>
+    <t>Annual CPR</t>
   </si>
   <si>
     <t>Borrower credit</t>
   </si>
   <si>
-    <t>{"credit_index": {"Credit": "BORROWER"}, "recovery": 0.4}</t>
-  </si>
-  <si>
     <t>Funded fixed</t>
   </si>
   <si>
-    <t>{"discount_index": {"Other": "FUNDING"}}</t>
-  </si>
-  <si>
     <t>Funded floating</t>
   </si>
   <si>
-    <t>{"amortization_rate": 0.05, "discount_index": {"Other": "FUNDING"}}</t>
-  </si>
-  <si>
     <t>Stepped fixed</t>
   </si>
   <si>
-    <t>{"coupon_segments": [{"rate": 0.03, "periods": 60}, {"rate": 0.04, "periods": 60}, {"rate": 0.05}]}</t>
-  </si>
-  <si>
     <t>Stepped then floating</t>
-  </si>
-  <si>
-    <t>{"coupon_segments": [{"rate": 0.03, "periods": 60}, {"rate": 0.04, "periods": 60}, {"rate": 0.01, "market_index": "EURIBOR12m"}]}</t>
   </si>
   <si>
     <t>French contractual receipts</t>
@@ -361,7 +418,7 @@
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +449,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -450,10 +514,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -470,17 +538,19 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -848,9 +918,55 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:L18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="12" width="22.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" cm="1">
+        <f t="array" ref="A4">_xll.QS.RESULT.SENSITIVITIES(Comparison!N13,TRUE,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" cm="1">
+        <f t="array" ref="A11">_xll.QS.RESULT.SENSITIVITIES(Comparison!N13,TRUE,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" cm="1">
+        <f t="array" ref="A18">_xll.QS.SCHEDULE("2026-02-24","2027-02-24","Monthly",TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:L16"/>
+  <dimension ref="A3:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="22.7109375" style="1" customWidth="1"/>
@@ -931,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I6" s="5">
         <v>0.005</v>
@@ -962,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I7" s="5">
         <v>0.007</v>
@@ -993,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I8" s="5">
         <v>0.008999999999999999</v>
@@ -1024,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I9" s="5">
         <v>0.011</v>
@@ -1051,11 +1167,11 @@
         <v>34</v>
       </c>
       <c r="F10" cm="1">
-        <f t="array" ref="F10">_xll.QS.CREDIT.CURVE.CONFIGS.FROM.JSON("Loans.Credit",H16)</f>
+        <f t="array" ref="F10">_xll.QS.CREDIT.CURVE.CONFIGS.CREATE("Loans.Credit")</f>
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I10" s="5">
         <v>0.014</v>
@@ -1070,11 +1186,11 @@
         <v>18</v>
       </c>
       <c r="F11" cm="1">
-        <f t="array" ref="F11">_xll.QS.CONTEXT.CREATE("Loans.Context",J12,F9,F10,,,,,,,,,"EUR","ESTR")</f>
+        <f t="array" ref="F11">_xll.QS.CONTEXT.CREATE("Loans.Context",J12,F9,F13,,,,,,,,,"EUR","ESTR")</f>
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I11" s="5">
         <v>0.016</v>
@@ -1093,13 +1209,22 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I12" s="5">
         <v>0.017</v>
       </c>
       <c r="J12" cm="1">
         <f t="array" ref="J12">_xll.QS.QUOTES.SET(J11,H12,I12,,)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xll.QS.CREDIT.CURVE.CONFIGS.ADD(F10,I15,I16,I17,I18,H6:H12)</f>
         <v>0</v>
       </c>
     </row>
@@ -1110,12 +1235,34 @@
     </row>
     <row r="15" spans="1:10">
       <c r="H15" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="H16" s="3" t="s">
-        <v>43</v>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="8:9">
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="8:9">
+      <c r="H18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1281,7 @@
   <sheetData>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>250000</v>
@@ -1142,7 +1289,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B5" s="5">
         <v>0.06</v>
@@ -1150,7 +1297,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5">
         <v>0.01</v>
@@ -1158,7 +1305,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -1166,44 +1313,44 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1213,440 +1360,162 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:L16"/>
+  <dimension ref="A3:L33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" customWidth="1"/>
-    <col min="6" max="6" width="48.7109375" customWidth="1"/>
-    <col min="7" max="8" width="22.7109375" style="1" customWidth="1"/>
-    <col min="9" max="11" width="21.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="12" width="22.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:11">
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" cm="1">
-        <f t="array" ref="F5">_xll.QS.TRADE.LOAN("Loans.Case5",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B5,C5,D5,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E5)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" cm="1">
-        <f t="array" ref="G5">_xll.QS.PRICE(F5,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <f>G5-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" cm="1">
-        <f t="array" ref="I5">_xll.QS.FAIR.RATE(F5,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" cm="1">
-        <f t="array" ref="F6">_xll.QS.TRADE.LOAN("Loans.Case6",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B6,C6,D6,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E6)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" cm="1">
-        <f t="array" ref="G6">_xll.QS.PRICE(F6,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <f>G6-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" cm="1">
-        <f t="array" ref="I6">_xll.QS.FAIR.RATE(F6,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" cm="1">
-        <f t="array" ref="F7">_xll.QS.TRADE.LOAN("Loans.Case7",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B7,C7,D7,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E7)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" cm="1">
-        <f t="array" ref="G7">_xll.QS.PRICE(F7,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <f>G7-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" cm="1">
-        <f t="array" ref="I7">_xll.QS.FAIR.RATE(F7,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="6">
-        <f>'Loan Inputs'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" cm="1">
-        <f t="array" ref="F8">_xll.QS.TRADE.LOAN("Loans.Case8",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B8,C8,D8,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E8)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="7" cm="1">
-        <f t="array" ref="G8">_xll.QS.PRICE(F8,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <f>G8-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" cm="1">
-        <f t="array" ref="I8">_xll.QS.FAIR.RATE(F8,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="6">
-        <f>'Loan Inputs'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" cm="1">
-        <f t="array" ref="F9">_xll.QS.TRADE.LOAN("Loans.Case9",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B9,C9,D9,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E9)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" cm="1">
-        <f t="array" ref="G9">_xll.QS.PRICE(F9,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <f>G9-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" cm="1">
-        <f t="array" ref="I9">_xll.QS.FAIR.RATE(F9,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>91</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="6">
-        <f>'Loan Inputs'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" cm="1">
-        <f t="array" ref="F10">_xll.QS.TRADE.LOAN("Loans.Case10",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B10,C10,D10,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E10)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" cm="1">
-        <f t="array" ref="G10">_xll.QS.PRICE(F10,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <f>G10-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" cm="1">
-        <f t="array" ref="F11">_xll.QS.TRADE.LOAN("Loans.Case11",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B11,C11,D11,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E11)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" cm="1">
-        <f t="array" ref="G11">_xll.QS.PRICE(F11,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <f>G11-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" cm="1">
-        <f t="array" ref="I11">_xll.QS.FAIR.RATE(F11,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" cm="1">
-        <f t="array" ref="F12">_xll.QS.TRADE.LOAN("Loans.Case12",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B12,C12,D12,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E12)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" cm="1">
-        <f t="array" ref="G12">_xll.QS.PRICE(F12,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
-        <f>G12-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" cm="1">
-        <f t="array" ref="I12">_xll.QS.FAIR.RATE(F12,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="6">
-        <f>'Loan Inputs'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" cm="1">
-        <f t="array" ref="F13">_xll.QS.TRADE.LOAN("Loans.Case13",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B13,C13,D13,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E13)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" cm="1">
-        <f t="array" ref="G13">_xll.QS.PRICE(F13,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
-        <f>G13-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" cm="1">
-        <f t="array" ref="I13">_xll.QS.FAIR.RATE(F13,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="6">
-        <f>'Loan Inputs'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F14" cm="1">
-        <f t="array" ref="F14">_xll.QS.TRADE.LOAN("Loans.Case14",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B14,C14,D14,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E14)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" cm="1">
-        <f t="array" ref="G14">_xll.QS.PRICE(F14,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
-        <f>G14-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" cm="1">
-        <f t="array" ref="I14">_xll.QS.FAIR.RATE(F14,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="B14" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" cm="1">
-        <f t="array" ref="F15">_xll.QS.TRADE.LOAN("Loans.Case15",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B15,C15,D15,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E15)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" cm="1">
-        <f t="array" ref="G15">_xll.QS.PRICE(F15,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
-        <f>G15-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" cm="1">
-        <f t="array" ref="I15">_xll.QS.FAIR.RATE(F15,Market!$F$11,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>95</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" cm="1">
-        <f t="array" ref="F16">_xll.QS.TRADE.LOAN("Loans.Case16",Market!$B$3,'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B16,C16,D16,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,"Receive",E16)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" cm="1">
-        <f t="array" ref="G16">_xll.QS.PRICE(F16,Market!$F$11)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
-        <f>G16-'Loan Inputs'!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" cm="1">
-        <f t="array" ref="I16">_xll.QS.FAIR.RATE(F16,Market!$F$11,TRUE)</f>
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1655,6 +1524,924 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:L20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="12" width="22.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3">
+        <v>60</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="5">
+        <f>'Loan Inputs'!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3">
+        <v>60</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3">
+        <v>60</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3">
+        <v>60</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3">
+        <v>60</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="B20" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:L10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="4" width="58.7109375" customWidth="1"/>
+    <col min="5" max="12" width="22.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" cm="1">
+        <f t="array" ref="C4">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loans.RiskFreePolicy",A4:B4)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" cm="1">
+        <f t="array" ref="D4">_xll.QS.PRICER.CREATE("Loans.RiskFreePricer","LoanPricer",C4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" cm="1">
+        <f t="array" ref="C5">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loans.FundingPolicy",A5:B5)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" cm="1">
+        <f t="array" ref="D5">_xll.QS.PRICER.CREATE("Loans.FundingPricer","LoanPricer",C5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" cm="1">
+        <f t="array" ref="B8">_xll.QS.REQUEST.FAIR.RATE(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" cm="1">
+        <f t="array" ref="B9">_xll.QS.REQUEST.FAIR.RATE(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" cm="1">
+        <f t="array" ref="B10">_xll.QS.REQUEST.FAIR.RATE(2)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A4:Q16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="4" width="22.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="48.7109375" customWidth="1"/>
+    <col min="7" max="8" width="22.7109375" style="1" customWidth="1"/>
+    <col min="9" max="11" width="21.7109375" style="7" customWidth="1"/>
+    <col min="12" max="17" width="48.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:17">
+      <c r="A4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" cm="1">
+        <f t="array" ref="F5">_xll.QS.TRADE.CREATE("Loans.Trade5",L5,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" cm="1">
+        <f t="array" ref="G5">_xll.QS.RESULT.VALUE(N5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <f>G5-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" cm="1">
+        <f t="array" ref="I5">_xll.QS.RESULT.FAIR.RATE(O5)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" cm="1">
+        <f t="array" ref="L5">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument5",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B5,C5,D5,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,)</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N5" cm="1">
+        <f t="array" ref="N5">_xll.QS.EVALUATE("Loans.Results5",M5,F5,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" cm="1">
+        <f t="array" ref="O5">_xll.QS.EVALUATE("Loans.Fair5.0",M5,F5,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" cm="1">
+        <f t="array" ref="F6">_xll.QS.TRADE.CREATE("Loans.Trade6",L6,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" cm="1">
+        <f t="array" ref="G6">_xll.QS.RESULT.VALUE(N6)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <f>G6-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" cm="1">
+        <f t="array" ref="I6">_xll.QS.RESULT.FAIR.RATE(O6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" cm="1">
+        <f t="array" ref="L6">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument6",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B6,C6,D6,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,)</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N6" cm="1">
+        <f t="array" ref="N6">_xll.QS.EVALUATE("Loans.Results6",M6,F6,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" cm="1">
+        <f t="array" ref="O6">_xll.QS.EVALUATE("Loans.Fair6.0",M6,F6,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xll.QS.TRADE.CREATE("Loans.Trade7",L7,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" cm="1">
+        <f t="array" ref="G7">_xll.QS.RESULT.VALUE(N7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <f>G7-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" cm="1">
+        <f t="array" ref="I7">_xll.QS.RESULT.FAIR.RATE(O7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument7",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B7,C7,D7,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A4:B5,)</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N7" cm="1">
+        <f t="array" ref="N7">_xll.QS.EVALUATE("Loans.Results7",M7,F7,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" cm="1">
+        <f t="array" ref="O7">_xll.QS.EVALUATE("Loans.Fair7.0",M7,F7,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="7">
+        <f>'Loan Inputs'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xll.QS.TRADE.CREATE("Loans.Trade8",L8,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" cm="1">
+        <f t="array" ref="G8">_xll.QS.RESULT.VALUE(N8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <f>G8-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" cm="1">
+        <f t="array" ref="I8">_xll.QS.RESULT.FAIR.RATE(O8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument8",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B8,C8,D8,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A9:B10,)</f>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">_xll.QS.EVALUATE("Loans.Results8",M8,F8,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" cm="1">
+        <f t="array" ref="O8">_xll.QS.EVALUATE("Loans.Fair8.0",M8,F8,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="7">
+        <f>'Loan Inputs'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xll.QS.TRADE.CREATE("Loans.Trade9",L9,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" cm="1">
+        <f t="array" ref="G9">_xll.QS.RESULT.VALUE(N9)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <f>G9-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" cm="1">
+        <f t="array" ref="I9">_xll.QS.RESULT.FAIR.RATE(O9)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" cm="1">
+        <f t="array" ref="J9">_xll.QS.RESULT.FAIR.RATE(P9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument9",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B9,C9,D9,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,'Coupon Schedules'!A4:C6)</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" ref="N9">_xll.QS.EVALUATE("Loans.Results9",M9,F9,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" cm="1">
+        <f t="array" ref="O9">_xll.QS.EVALUATE("Loans.Fair9.0",M9,F9,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" cm="1">
+        <f t="array" ref="P9">_xll.QS.EVALUATE("Loans.Fair9.1",M9,F9,Market!$F$11,Pricing!$B$9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="7">
+        <f>'Loan Inputs'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xll.QS.TRADE.CREATE("Loans.Trade10",L10,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" cm="1">
+        <f t="array" ref="G10">_xll.QS.RESULT.VALUE(N10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <f>G10-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument10",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B10,C10,D10,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A14:B17,)</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N10" cm="1">
+        <f t="array" ref="N10">_xll.QS.EVALUATE("Loans.Results10",M10,F10,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xll.QS.TRADE.CREATE("Loans.Trade11",L11,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" cm="1">
+        <f t="array" ref="G11">_xll.QS.RESULT.VALUE(N11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <f>G11-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" cm="1">
+        <f t="array" ref="I11">_xll.QS.RESULT.FAIR.RATE(O11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument11",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B11,C11,D11,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A21:B22,)</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N11" cm="1">
+        <f t="array" ref="N11">_xll.QS.EVALUATE("Loans.Results11",M11,F11,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" cm="1">
+        <f t="array" ref="O11">_xll.QS.EVALUATE("Loans.Fair11.0",M11,F11,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">_xll.QS.TRADE.CREATE("Loans.Trade12",L12,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" cm="1">
+        <f t="array" ref="G12">_xll.QS.RESULT.VALUE(N12)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <f>G12-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" cm="1">
+        <f t="array" ref="I12">_xll.QS.RESULT.FAIR.RATE(O12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument12",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B12,C12,D12,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A26:B28,)</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N12" cm="1">
+        <f t="array" ref="N12">_xll.QS.EVALUATE("Loans.Results12",M12,F12,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" cm="1">
+        <f t="array" ref="O12">_xll.QS.EVALUATE("Loans.Fair12.0",M12,F12,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="7">
+        <f>'Loan Inputs'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xll.QS.TRADE.CREATE("Loans.Trade13",L13,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" cm="1">
+        <f t="array" ref="G13">_xll.QS.RESULT.VALUE(N13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <f>G13-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" cm="1">
+        <f t="array" ref="I13">_xll.QS.RESULT.FAIR.RATE(O13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" cm="1">
+        <f t="array" ref="L13">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument13",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B13,C13,D13,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,)</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>Pricing!D5</f>
+        <v>0</v>
+      </c>
+      <c r="N13" cm="1">
+        <f t="array" ref="N13">_xll.QS.EVALUATE("Loans.Results13",M13,F13,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" cm="1">
+        <f t="array" ref="O13">_xll.QS.EVALUATE("Loans.Fair13.0",M13,F13,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="7">
+        <f>'Loan Inputs'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" cm="1">
+        <f t="array" ref="F14">_xll.QS.TRADE.CREATE("Loans.Trade14",L14,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" cm="1">
+        <f t="array" ref="G14">_xll.QS.RESULT.VALUE(N14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <f>G14-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" cm="1">
+        <f t="array" ref="I14">_xll.QS.RESULT.FAIR.RATE(O14)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument14",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B14,C14,D14,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,'Loan Settings'!A32:B33,)</f>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f>Pricing!D5</f>
+        <v>0</v>
+      </c>
+      <c r="N14" cm="1">
+        <f t="array" ref="N14">_xll.QS.EVALUATE("Loans.Results14",M14,F14,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" cm="1">
+        <f t="array" ref="O14">_xll.QS.EVALUATE("Loans.Fair14.0",M14,F14,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" cm="1">
+        <f t="array" ref="F15">_xll.QS.TRADE.CREATE("Loans.Trade15",L15,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" cm="1">
+        <f t="array" ref="G15">_xll.QS.RESULT.VALUE(N15)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <f>G15-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" cm="1">
+        <f t="array" ref="I15">_xll.QS.RESULT.FAIR.RATE(O15)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" cm="1">
+        <f t="array" ref="J15">_xll.QS.RESULT.FAIR.RATE(P15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="7" cm="1">
+        <f t="array" ref="K15">_xll.QS.RESULT.FAIR.RATE(Q15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" cm="1">
+        <f t="array" ref="L15">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument15",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B15,C15,D15,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,'Coupon Schedules'!A10:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N15" cm="1">
+        <f t="array" ref="N15">_xll.QS.EVALUATE("Loans.Results15",M15,F15,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" cm="1">
+        <f t="array" ref="O15">_xll.QS.EVALUATE("Loans.Fair15.0",M15,F15,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" cm="1">
+        <f t="array" ref="P15">_xll.QS.EVALUATE("Loans.Fair15.1",M15,F15,Market!$F$11,Pricing!$B$9)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" cm="1">
+        <f t="array" ref="Q15">_xll.QS.EVALUATE("Loans.Fair15.2",M15,F15,Market!$F$11,Pricing!$B$10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" cm="1">
+        <f t="array" ref="F16">_xll.QS.TRADE.CREATE("Loans.Trade16",L16,Market!$B$3,"Receive")</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" cm="1">
+        <f t="array" ref="G16">_xll.QS.RESULT.VALUE(N16)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <f>G16-'Loan Inputs'!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" cm="1">
+        <f t="array" ref="I16">_xll.QS.RESULT.FAIR.RATE(O16)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" cm="1">
+        <f t="array" ref="J16">_xll.QS.RESULT.FAIR.RATE(P16)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="7" cm="1">
+        <f t="array" ref="K16">_xll.QS.RESULT.FAIR.RATE(Q16)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" cm="1">
+        <f t="array" ref="L16">_xll.QS.INSTRUMENT.LOAN("Loans.Instrument16",'Loan Inputs'!$B$7,'Loan Inputs'!$B$8,'Loan Inputs'!$B$11,'Loan Inputs'!$B$4,B16,C16,D16,'Loan Inputs'!$B$9,'Loan Inputs'!$B$10,,'Coupon Schedules'!A17:C20)</f>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f>Pricing!D4</f>
+        <v>0</v>
+      </c>
+      <c r="N16" cm="1">
+        <f t="array" ref="N16">_xll.QS.EVALUATE("Loans.Results16",M16,F16,Market!$F$11,Pricing!$A$8:$A$10)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" cm="1">
+        <f t="array" ref="O16">_xll.QS.EVALUATE("Loans.Fair16.0",M16,F16,Market!$F$11,Pricing!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" cm="1">
+        <f t="array" ref="P16">_xll.QS.EVALUATE("Loans.Fair16.1",M16,F16,Market!$F$11,Pricing!$B$9)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" cm="1">
+        <f t="array" ref="Q16">_xll.QS.EVALUATE("Loans.Fair16.2",M16,F16,Market!$F$11,Pricing!$B$10)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E7" location="'Loan Settings'!A4" display="Edit settings"/>
+    <hyperlink ref="E8" location="'Loan Settings'!A9" display="Edit settings"/>
+    <hyperlink ref="E9" location="'Coupon Schedules'!A4" display="Edit coupon schedule"/>
+    <hyperlink ref="E10" location="'Loan Settings'!A14" display="Edit settings"/>
+    <hyperlink ref="E11" location="'Loan Settings'!A21" display="Edit settings"/>
+    <hyperlink ref="E12" location="'Loan Settings'!A26" display="Edit settings"/>
+    <hyperlink ref="E14" location="'Loan Settings'!A32" display="Edit settings"/>
+    <hyperlink ref="E15" location="'Coupon Schedules'!A10" display="Edit coupon schedule"/>
+    <hyperlink ref="E16" location="'Coupon Schedules'!A17" display="Edit coupon schedule"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1663,20 +2450,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11">
-      <c r="A2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>96</v>
+      <c r="A2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.QS.CASHFLOWS(Comparison!F5,Market!F11)</f>
+        <f t="array" ref="A4">_xll.QS.RESULT.CASHFLOWS(Comparison!N5)</f>
         <v>0</v>
       </c>
       <c r="K4" s="1" cm="1">
-        <f t="array" ref="K4">_xll.QS.CASHFLOWS(Comparison!F11,Market!F11)</f>
+        <f t="array" ref="K4">_xll.QS.RESULT.CASHFLOWS(Comparison!N11)</f>
         <v>0</v>
       </c>
     </row>
@@ -1685,7 +2472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1694,72 +2481,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>98</v>
+      <c r="A2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.QS.SENSITIVITIES(Comparison!F13,Market!F11)</f>
+        <f t="array" ref="A4">_xll.QS.RESULT.SENSITIVITIES(Comparison!N13)</f>
         <v>0</v>
       </c>
       <c r="E4" s="1" cm="1">
-        <f t="array" ref="E4">_xll.QS.SENSITIVITIES(Comparison!F14,Market!F11)</f>
+        <f t="array" ref="E4">_xll.QS.RESULT.SENSITIVITIES(Comparison!N14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:L18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="12" width="22.7109375" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.QS.SENSITIVITIES(Comparison!F13,Market!F11,TRUE,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" cm="1">
-        <f t="array" ref="A11">_xll.QS.SENSITIVITIES(Comparison!F13,Market!F11,TRUE,TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" cm="1">
-        <f t="array" ref="A18">_xll.QS.SCHEDULE("2026-02-24","2027-02-24","Monthly",TRUE)</f>
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -200,6 +200,8 @@
     <definedName name="Loan_ForwardCurves">'3 Market'!$B$62</definedName>
     <definedName name="Loan_ForwardRates">'3 Market'!$C$7:$C$11</definedName>
     <definedName name="Loan_Frequency">'1 Inputs'!$B$13</definedName>
+    <definedName name="Loan_FundingCurrency">'1 Inputs'!$A$29</definedName>
+    <definedName name="Loan_FundingIndex">'1 Inputs'!$B$29</definedName>
     <definedName name="Loan_FundingMapping">'1 Inputs'!$A$29:$B$29</definedName>
     <definedName name="Loan_FundingPolicy">'4 Build'!$B$16</definedName>
     <definedName name="Loan_FundingPricer">'4 Build'!$B$19</definedName>
@@ -217,6 +219,8 @@
     <definedName name="Loan_Request2">'4 Build'!$B$31</definedName>
     <definedName name="Loan_Requests">'1 Inputs'!$A$21:$A$23</definedName>
     <definedName name="Loan_ResultHandles">'4 Build'!$B$287:$B$298</definedName>
+    <definedName name="Loan_RiskFreeCurrency">'1 Inputs'!$A$28</definedName>
+    <definedName name="Loan_RiskFreeIndex">'1 Inputs'!$B$28</definedName>
     <definedName name="Loan_RiskFreeMapping">'1 Inputs'!$A$28:$B$28</definedName>
     <definedName name="Loan_RiskFreePolicy">'4 Build'!$B$10</definedName>
     <definedName name="Loan_RiskFreePricer">'4 Build'!$B$13</definedName>
@@ -5362,7 +5366,7 @@
         <v>193</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy",Loan_RiskFreeMapping)</f>
+        <f t="array" ref="B10">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy",Loan_RiskFreeCurrency,Loan_RiskFreeIndex)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
@@ -5372,7 +5376,7 @@
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy", Loan_RiskFreeMapping)</v>
+        <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy", Loan_RiskFreeCurrency, Loan_RiskFreeIndex)</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -5402,7 +5406,7 @@
         <v>197</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
-        <f t="array" ref="B16">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy",Loan_FundingMapping)</f>
+        <f t="array" ref="B16">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy",Loan_FundingCurrency,Loan_FundingIndex)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
@@ -5412,7 +5416,7 @@
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy", Loan_FundingMapping)</v>
+        <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy", Loan_FundingCurrency, Loan_FundingIndex)</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -44,142 +44,148 @@
     <definedName name="Loan_C02_Result">'4 Build'!$B$66</definedName>
     <definedName name="Loan_C02_Trade">'4 Build'!$B$60</definedName>
     <definedName name="Loan_C03_Discount">'2 Cases'!$B$29</definedName>
-    <definedName name="Loan_C03_Fair0">'4 Build'!$B$89</definedName>
+    <definedName name="Loan_C03_Fair0">'4 Build'!$B$92</definedName>
     <definedName name="Loan_C03_FairRate0">'5 Results'!$D$9</definedName>
     <definedName name="Loan_C03_Index">'2 Cases'!$D$28</definedName>
-    <definedName name="Loan_C03_Instrument">'4 Build'!$B$77</definedName>
+    <definedName name="Loan_C03_Instrument">'4 Build'!$B$80</definedName>
     <definedName name="Loan_C03_Net">'5 Results'!$C$9</definedName>
-    <definedName name="Loan_C03_Pricer">'4 Build'!$B$83</definedName>
+    <definedName name="Loan_C03_Options">'4 Build'!$B$77</definedName>
+    <definedName name="Loan_C03_Pricer">'4 Build'!$B$86</definedName>
     <definedName name="Loan_C03_PV">'5 Results'!$B$9</definedName>
     <definedName name="Loan_C03_Rate">'2 Cases'!$B$28</definedName>
     <definedName name="Loan_C03_Repayment">'2 Cases'!$F$28</definedName>
-    <definedName name="Loan_C03_Result">'4 Build'!$B$86</definedName>
+    <definedName name="Loan_C03_Result">'4 Build'!$B$89</definedName>
     <definedName name="Loan_C03_Settings">'2 Cases'!$A$31:$B$32</definedName>
-    <definedName name="Loan_C03_Trade">'4 Build'!$B$80</definedName>
+    <definedName name="Loan_C03_Trade">'4 Build'!$B$83</definedName>
     <definedName name="Loan_C04_Discount">'2 Cases'!$B$39</definedName>
-    <definedName name="Loan_C04_Fair0">'4 Build'!$B$109</definedName>
+    <definedName name="Loan_C04_Fair0">'4 Build'!$B$115</definedName>
     <definedName name="Loan_C04_FairRate0">'5 Results'!$D$10</definedName>
     <definedName name="Loan_C04_Index">'2 Cases'!$D$38</definedName>
-    <definedName name="Loan_C04_Instrument">'4 Build'!$B$97</definedName>
+    <definedName name="Loan_C04_Instrument">'4 Build'!$B$103</definedName>
     <definedName name="Loan_C04_Net">'5 Results'!$C$10</definedName>
-    <definedName name="Loan_C04_Pricer">'4 Build'!$B$103</definedName>
+    <definedName name="Loan_C04_Options">'4 Build'!$B$100</definedName>
+    <definedName name="Loan_C04_Pricer">'4 Build'!$B$109</definedName>
     <definedName name="Loan_C04_PV">'5 Results'!$B$10</definedName>
     <definedName name="Loan_C04_Rate">'2 Cases'!$B$38</definedName>
     <definedName name="Loan_C04_Repayment">'2 Cases'!$F$38</definedName>
-    <definedName name="Loan_C04_Result">'4 Build'!$B$106</definedName>
+    <definedName name="Loan_C04_Result">'4 Build'!$B$112</definedName>
     <definedName name="Loan_C04_Settings">'2 Cases'!$A$41:$B$42</definedName>
-    <definedName name="Loan_C04_Trade">'4 Build'!$B$100</definedName>
+    <definedName name="Loan_C04_Trade">'4 Build'!$B$106</definedName>
     <definedName name="Loan_C05_Coupons">'2 Cases'!$D$51:$F$53</definedName>
     <definedName name="Loan_C05_Discount">'2 Cases'!$B$49</definedName>
-    <definedName name="Loan_C05_Fair0">'4 Build'!$B$129</definedName>
-    <definedName name="Loan_C05_Fair1">'4 Build'!$B$132</definedName>
+    <definedName name="Loan_C05_Fair0">'4 Build'!$B$135</definedName>
+    <definedName name="Loan_C05_Fair1">'4 Build'!$B$138</definedName>
     <definedName name="Loan_C05_FairRate0">'5 Results'!$D$11</definedName>
     <definedName name="Loan_C05_FairRate1">'5 Results'!$E$11</definedName>
     <definedName name="Loan_C05_Index">'2 Cases'!$D$48</definedName>
-    <definedName name="Loan_C05_Instrument">'4 Build'!$B$117</definedName>
+    <definedName name="Loan_C05_Instrument">'4 Build'!$B$123</definedName>
     <definedName name="Loan_C05_Net">'5 Results'!$C$11</definedName>
-    <definedName name="Loan_C05_Pricer">'4 Build'!$B$123</definedName>
+    <definedName name="Loan_C05_Pricer">'4 Build'!$B$129</definedName>
     <definedName name="Loan_C05_PV">'5 Results'!$B$11</definedName>
     <definedName name="Loan_C05_Rate">'2 Cases'!$B$48</definedName>
     <definedName name="Loan_C05_Repayment">'2 Cases'!$F$48</definedName>
-    <definedName name="Loan_C05_Result">'4 Build'!$B$126</definedName>
-    <definedName name="Loan_C05_Trade">'4 Build'!$B$120</definedName>
+    <definedName name="Loan_C05_Result">'4 Build'!$B$132</definedName>
+    <definedName name="Loan_C05_Trade">'4 Build'!$B$126</definedName>
     <definedName name="Loan_C06_Discount">'2 Cases'!$B$63</definedName>
     <definedName name="Loan_C06_Index">'2 Cases'!$D$62</definedName>
-    <definedName name="Loan_C06_Instrument">'4 Build'!$B$140</definedName>
+    <definedName name="Loan_C06_Instrument">'4 Build'!$B$149</definedName>
     <definedName name="Loan_C06_Net">'5 Results'!$C$12</definedName>
-    <definedName name="Loan_C06_Pricer">'4 Build'!$B$146</definedName>
+    <definedName name="Loan_C06_Options">'4 Build'!$B$146</definedName>
+    <definedName name="Loan_C06_Pricer">'4 Build'!$B$155</definedName>
     <definedName name="Loan_C06_PV">'5 Results'!$B$12</definedName>
     <definedName name="Loan_C06_Rate">'2 Cases'!$B$62</definedName>
     <definedName name="Loan_C06_Repayment">'2 Cases'!$F$62</definedName>
-    <definedName name="Loan_C06_Result">'4 Build'!$B$149</definedName>
+    <definedName name="Loan_C06_Result">'4 Build'!$B$158</definedName>
     <definedName name="Loan_C06_Settings">'2 Cases'!$A$65:$B$68</definedName>
-    <definedName name="Loan_C06_Trade">'4 Build'!$B$143</definedName>
+    <definedName name="Loan_C06_Trade">'4 Build'!$B$152</definedName>
     <definedName name="Loan_C07_Discount">'2 Cases'!$B$75</definedName>
-    <definedName name="Loan_C07_Fair0">'4 Build'!$B$169</definedName>
+    <definedName name="Loan_C07_Fair0">'4 Build'!$B$181</definedName>
     <definedName name="Loan_C07_FairRate0">'5 Results'!$D$13</definedName>
     <definedName name="Loan_C07_Index">'2 Cases'!$D$74</definedName>
-    <definedName name="Loan_C07_Instrument">'4 Build'!$B$157</definedName>
+    <definedName name="Loan_C07_Instrument">'4 Build'!$B$169</definedName>
     <definedName name="Loan_C07_Net">'5 Results'!$C$13</definedName>
-    <definedName name="Loan_C07_Pricer">'4 Build'!$B$163</definedName>
+    <definedName name="Loan_C07_Options">'4 Build'!$B$166</definedName>
+    <definedName name="Loan_C07_Pricer">'4 Build'!$B$175</definedName>
     <definedName name="Loan_C07_PV">'5 Results'!$B$13</definedName>
     <definedName name="Loan_C07_Rate">'2 Cases'!$B$74</definedName>
     <definedName name="Loan_C07_Repayment">'2 Cases'!$F$74</definedName>
-    <definedName name="Loan_C07_Result">'4 Build'!$B$166</definedName>
+    <definedName name="Loan_C07_Result">'4 Build'!$B$178</definedName>
     <definedName name="Loan_C07_Settings">'2 Cases'!$A$77:$B$78</definedName>
-    <definedName name="Loan_C07_Trade">'4 Build'!$B$160</definedName>
+    <definedName name="Loan_C07_Trade">'4 Build'!$B$172</definedName>
     <definedName name="Loan_C08_Discount">'2 Cases'!$B$85</definedName>
-    <definedName name="Loan_C08_Fair0">'4 Build'!$B$189</definedName>
+    <definedName name="Loan_C08_Fair0">'4 Build'!$B$204</definedName>
     <definedName name="Loan_C08_FairRate0">'5 Results'!$D$14</definedName>
     <definedName name="Loan_C08_Index">'2 Cases'!$D$84</definedName>
-    <definedName name="Loan_C08_Instrument">'4 Build'!$B$177</definedName>
+    <definedName name="Loan_C08_Instrument">'4 Build'!$B$192</definedName>
     <definedName name="Loan_C08_Net">'5 Results'!$C$14</definedName>
-    <definedName name="Loan_C08_Pricer">'4 Build'!$B$183</definedName>
+    <definedName name="Loan_C08_Options">'4 Build'!$B$189</definedName>
+    <definedName name="Loan_C08_Pricer">'4 Build'!$B$198</definedName>
     <definedName name="Loan_C08_PV">'5 Results'!$B$14</definedName>
     <definedName name="Loan_C08_Rate">'2 Cases'!$B$84</definedName>
     <definedName name="Loan_C08_Repayment">'2 Cases'!$F$84</definedName>
-    <definedName name="Loan_C08_Result">'4 Build'!$B$186</definedName>
+    <definedName name="Loan_C08_Result">'4 Build'!$B$201</definedName>
     <definedName name="Loan_C08_Settings">'2 Cases'!$A$87:$B$89</definedName>
-    <definedName name="Loan_C08_Trade">'4 Build'!$B$180</definedName>
+    <definedName name="Loan_C08_Trade">'4 Build'!$B$195</definedName>
     <definedName name="Loan_C09_Discount">'2 Cases'!$B$96</definedName>
-    <definedName name="Loan_C09_Fair0">'4 Build'!$B$209</definedName>
+    <definedName name="Loan_C09_Fair0">'4 Build'!$B$224</definedName>
     <definedName name="Loan_C09_FairRate0">'5 Results'!$D$15</definedName>
     <definedName name="Loan_C09_Index">'2 Cases'!$D$95</definedName>
-    <definedName name="Loan_C09_Instrument">'4 Build'!$B$197</definedName>
+    <definedName name="Loan_C09_Instrument">'4 Build'!$B$212</definedName>
     <definedName name="Loan_C09_Net">'5 Results'!$C$15</definedName>
-    <definedName name="Loan_C09_Pricer">'4 Build'!$B$203</definedName>
+    <definedName name="Loan_C09_Pricer">'4 Build'!$B$218</definedName>
     <definedName name="Loan_C09_PV">'5 Results'!$B$15</definedName>
     <definedName name="Loan_C09_Rate">'2 Cases'!$B$95</definedName>
     <definedName name="Loan_C09_Repayment">'2 Cases'!$F$95</definedName>
-    <definedName name="Loan_C09_Result">'4 Build'!$B$206</definedName>
-    <definedName name="Loan_C09_Trade">'4 Build'!$B$200</definedName>
+    <definedName name="Loan_C09_Result">'4 Build'!$B$221</definedName>
+    <definedName name="Loan_C09_Trade">'4 Build'!$B$215</definedName>
     <definedName name="Loan_C10_Discount">'2 Cases'!$B$106</definedName>
-    <definedName name="Loan_C10_Fair0">'4 Build'!$B$229</definedName>
+    <definedName name="Loan_C10_Fair0">'4 Build'!$B$247</definedName>
     <definedName name="Loan_C10_FairRate0">'5 Results'!$D$16</definedName>
     <definedName name="Loan_C10_Index">'2 Cases'!$D$105</definedName>
-    <definedName name="Loan_C10_Instrument">'4 Build'!$B$217</definedName>
+    <definedName name="Loan_C10_Instrument">'4 Build'!$B$235</definedName>
     <definedName name="Loan_C10_Net">'5 Results'!$C$16</definedName>
-    <definedName name="Loan_C10_Pricer">'4 Build'!$B$223</definedName>
+    <definedName name="Loan_C10_Options">'4 Build'!$B$232</definedName>
+    <definedName name="Loan_C10_Pricer">'4 Build'!$B$241</definedName>
     <definedName name="Loan_C10_PV">'5 Results'!$B$16</definedName>
     <definedName name="Loan_C10_Rate">'2 Cases'!$B$105</definedName>
     <definedName name="Loan_C10_Repayment">'2 Cases'!$F$105</definedName>
-    <definedName name="Loan_C10_Result">'4 Build'!$B$226</definedName>
+    <definedName name="Loan_C10_Result">'4 Build'!$B$244</definedName>
     <definedName name="Loan_C10_Settings">'2 Cases'!$A$108:$B$109</definedName>
-    <definedName name="Loan_C10_Trade">'4 Build'!$B$220</definedName>
+    <definedName name="Loan_C10_Trade">'4 Build'!$B$238</definedName>
     <definedName name="Loan_C11_Coupons">'2 Cases'!$D$118:$F$121</definedName>
     <definedName name="Loan_C11_Discount">'2 Cases'!$B$116</definedName>
-    <definedName name="Loan_C11_Fair0">'4 Build'!$B$249</definedName>
-    <definedName name="Loan_C11_Fair1">'4 Build'!$B$252</definedName>
-    <definedName name="Loan_C11_Fair2">'4 Build'!$B$255</definedName>
+    <definedName name="Loan_C11_Fair0">'4 Build'!$B$267</definedName>
+    <definedName name="Loan_C11_Fair1">'4 Build'!$B$270</definedName>
+    <definedName name="Loan_C11_Fair2">'4 Build'!$B$273</definedName>
     <definedName name="Loan_C11_FairRate0">'5 Results'!$D$17</definedName>
     <definedName name="Loan_C11_FairRate1">'5 Results'!$E$17</definedName>
     <definedName name="Loan_C11_FairRate2">'5 Results'!$F$17</definedName>
     <definedName name="Loan_C11_Index">'2 Cases'!$D$115</definedName>
-    <definedName name="Loan_C11_Instrument">'4 Build'!$B$237</definedName>
+    <definedName name="Loan_C11_Instrument">'4 Build'!$B$255</definedName>
     <definedName name="Loan_C11_Net">'5 Results'!$C$17</definedName>
-    <definedName name="Loan_C11_Pricer">'4 Build'!$B$243</definedName>
+    <definedName name="Loan_C11_Pricer">'4 Build'!$B$261</definedName>
     <definedName name="Loan_C11_PV">'5 Results'!$B$17</definedName>
     <definedName name="Loan_C11_Rate">'2 Cases'!$B$115</definedName>
     <definedName name="Loan_C11_Repayment">'2 Cases'!$F$115</definedName>
-    <definedName name="Loan_C11_Result">'4 Build'!$B$246</definedName>
-    <definedName name="Loan_C11_Trade">'4 Build'!$B$240</definedName>
+    <definedName name="Loan_C11_Result">'4 Build'!$B$264</definedName>
+    <definedName name="Loan_C11_Trade">'4 Build'!$B$258</definedName>
     <definedName name="Loan_C12_Coupons">'2 Cases'!$D$132:$F$135</definedName>
     <definedName name="Loan_C12_Discount">'2 Cases'!$B$130</definedName>
-    <definedName name="Loan_C12_Fair0">'4 Build'!$B$275</definedName>
-    <definedName name="Loan_C12_Fair1">'4 Build'!$B$278</definedName>
-    <definedName name="Loan_C12_Fair2">'4 Build'!$B$281</definedName>
+    <definedName name="Loan_C12_Fair0">'4 Build'!$B$293</definedName>
+    <definedName name="Loan_C12_Fair1">'4 Build'!$B$296</definedName>
+    <definedName name="Loan_C12_Fair2">'4 Build'!$B$299</definedName>
     <definedName name="Loan_C12_FairRate0">'5 Results'!$D$18</definedName>
     <definedName name="Loan_C12_FairRate1">'5 Results'!$E$18</definedName>
     <definedName name="Loan_C12_FairRate2">'5 Results'!$F$18</definedName>
     <definedName name="Loan_C12_Index">'2 Cases'!$D$129</definedName>
-    <definedName name="Loan_C12_Instrument">'4 Build'!$B$263</definedName>
+    <definedName name="Loan_C12_Instrument">'4 Build'!$B$281</definedName>
     <definedName name="Loan_C12_Net">'5 Results'!$C$18</definedName>
-    <definedName name="Loan_C12_Pricer">'4 Build'!$B$269</definedName>
+    <definedName name="Loan_C12_Pricer">'4 Build'!$B$287</definedName>
     <definedName name="Loan_C12_PV">'5 Results'!$B$18</definedName>
     <definedName name="Loan_C12_Rate">'2 Cases'!$B$129</definedName>
     <definedName name="Loan_C12_Repayment">'2 Cases'!$F$129</definedName>
-    <definedName name="Loan_C12_Result">'4 Build'!$B$272</definedName>
-    <definedName name="Loan_C12_Trade">'4 Build'!$B$266</definedName>
+    <definedName name="Loan_C12_Result">'4 Build'!$B$290</definedName>
+    <definedName name="Loan_C12_Trade">'4 Build'!$B$284</definedName>
     <definedName name="Loan_CaseNames">'5 Results'!$A$7:$A$18</definedName>
     <definedName name="Loan_Context">'4 Build'!$B$7</definedName>
     <definedName name="Loan_Credit">'3 Market'!$B$74</definedName>
@@ -218,14 +224,14 @@
     <definedName name="Loan_Request1">'4 Build'!$B$28</definedName>
     <definedName name="Loan_Request2">'4 Build'!$B$31</definedName>
     <definedName name="Loan_Requests">'1 Inputs'!$A$21:$A$23</definedName>
-    <definedName name="Loan_ResultHandles">'4 Build'!$B$287:$B$298</definedName>
+    <definedName name="Loan_ResultHandles">'4 Build'!$B$305:$B$316</definedName>
     <definedName name="Loan_RiskFreeCurrency">'1 Inputs'!$A$28</definedName>
     <definedName name="Loan_RiskFreeIndex">'1 Inputs'!$B$28</definedName>
     <definedName name="Loan_RiskFreeMapping">'1 Inputs'!$A$28:$B$28</definedName>
     <definedName name="Loan_RiskFreePolicy">'4 Build'!$B$10</definedName>
     <definedName name="Loan_RiskFreePricer">'4 Build'!$B$13</definedName>
     <definedName name="Loan_SelectedCase">'5 Results'!$B$22</definedName>
-    <definedName name="Loan_SelectedResult">'4 Build'!$B$301</definedName>
+    <definedName name="Loan_SelectedResult">'4 Build'!$B$319</definedName>
     <definedName name="Loan_Side">'1 Inputs'!$B$16</definedName>
     <definedName name="Loan_SpreadCurves">'3 Market'!$B$65</definedName>
     <definedName name="Loan_Start">'1 Inputs'!$B$11</definedName>
@@ -865,11 +871,24 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>Reserve one quarter of principal for maturity.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -882,7 +901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B83" authorId="0">
+    <comment ref="B86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -895,7 +914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B86" authorId="0">
+    <comment ref="B89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -908,7 +927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
+    <comment ref="B92" authorId="0">
       <text>
         <r>
           <rPr>
@@ -921,7 +940,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="B97" authorId="0">
+    <comment ref="B100" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0">
       <text>
         <r>
           <rPr>
@@ -934,7 +966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B100" authorId="0">
+    <comment ref="B106" authorId="0">
       <text>
         <r>
           <rPr>
@@ -947,7 +979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B103" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <r>
           <rPr>
@@ -960,7 +992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B106" authorId="0">
+    <comment ref="B112" authorId="0">
       <text>
         <r>
           <rPr>
@@ -973,7 +1005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B109" authorId="0">
+    <comment ref="B115" authorId="0">
       <text>
         <r>
           <rPr>
@@ -986,7 +1018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B117" authorId="0">
+    <comment ref="B123" authorId="0">
       <text>
         <r>
           <rPr>
@@ -999,7 +1031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B120" authorId="0">
+    <comment ref="B126" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1012,7 +1044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B123" authorId="0">
+    <comment ref="B129" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1025,7 +1057,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B126" authorId="0">
+    <comment ref="B132" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1070,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B129" authorId="0">
+    <comment ref="B135" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1051,7 +1083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B132" authorId="0">
+    <comment ref="B138" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1064,7 +1096,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="B140" authorId="0">
+    <comment ref="B146" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1077,7 +1122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B143" authorId="0">
+    <comment ref="B152" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1090,7 +1135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B146" authorId="0">
+    <comment ref="B155" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1103,7 +1148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B149" authorId="0">
+    <comment ref="B158" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1116,7 +1161,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="B157" authorId="0">
+    <comment ref="B166" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1129,7 +1187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B160" authorId="0">
+    <comment ref="B172" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1142,7 +1200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B163" authorId="0">
+    <comment ref="B175" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1155,7 +1213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B166" authorId="0">
+    <comment ref="B178" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1168,7 +1226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B169" authorId="0">
+    <comment ref="B181" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1181,7 +1239,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="B177" authorId="0">
+    <comment ref="B189" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1194,7 +1265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B180" authorId="0">
+    <comment ref="B195" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1207,7 +1278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B183" authorId="0">
+    <comment ref="B198" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1220,7 +1291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B186" authorId="0">
+    <comment ref="B201" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1233,7 +1304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B189" authorId="0">
+    <comment ref="B204" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1246,7 +1317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B197" authorId="0">
+    <comment ref="B212" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1259,7 +1330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B200" authorId="0">
+    <comment ref="B215" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1272,7 +1343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B203" authorId="0">
+    <comment ref="B218" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B206" authorId="0">
+    <comment ref="B221" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1298,7 +1369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B209" authorId="0">
+    <comment ref="B224" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1311,7 +1382,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="B217" authorId="0">
+    <comment ref="B232" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B235" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1324,7 +1408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B220" authorId="0">
+    <comment ref="B238" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1337,7 +1421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B223" authorId="0">
+    <comment ref="B241" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1350,7 +1434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B226" authorId="0">
+    <comment ref="B244" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1363,7 +1447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B229" authorId="0">
+    <comment ref="B247" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1376,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B237" authorId="0">
+    <comment ref="B255" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1389,7 +1473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B240" authorId="0">
+    <comment ref="B258" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1402,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B243" authorId="0">
+    <comment ref="B261" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1415,7 +1499,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B246" authorId="0">
+    <comment ref="B264" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1428,7 +1512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B249" authorId="0">
+    <comment ref="B267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1441,7 +1525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B252" authorId="0">
+    <comment ref="B270" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1454,7 +1538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B255" authorId="0">
+    <comment ref="B273" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1467,7 +1551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B263" authorId="0">
+    <comment ref="B281" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1480,7 +1564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B266" authorId="0">
+    <comment ref="B284" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1493,7 +1577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B269" authorId="0">
+    <comment ref="B287" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1506,7 +1590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B272" authorId="0">
+    <comment ref="B290" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1519,7 +1603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B275" authorId="0">
+    <comment ref="B293" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1532,7 +1616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B278" authorId="0">
+    <comment ref="B296" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1545,7 +1629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B281" authorId="0">
+    <comment ref="B299" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1558,7 +1642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B301" authorId="0">
+    <comment ref="B319" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1598,7 +1682,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="264">
   <si>
     <t>Loans · compare one change at a time</t>
   </si>
@@ -2243,6 +2327,12 @@
   </si>
   <si>
     <t>Repay remaining principal at each prefix end, lock earlier solved rates, then extend.</t>
+  </si>
+  <si>
+    <t>Named loan settings</t>
+  </si>
+  <si>
+    <t>Each optional parameter is visible in IntelliSense; its value refers to the case input cell.</t>
   </si>
   <si>
     <t>5.2 Solve segment 1</t>
@@ -2919,7 +3009,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -2946,7 +3036,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="26" customHeight="1">
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2956,7 +3046,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="26" customHeight="1">
+    <row r="4" spans="1:6" ht="26.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2964,7 +3054,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="26" customHeight="1">
+    <row r="6" spans="1:6" ht="26.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -2974,7 +3064,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="26" customHeight="1">
+    <row r="7" spans="1:6" ht="26.25" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2982,7 +3072,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="26" customHeight="1">
+    <row r="9" spans="1:6" ht="26.25" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
@@ -2992,7 +3082,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="34" customHeight="1">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -3006,7 +3096,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="34" customHeight="1">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -3020,7 +3110,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="34" customHeight="1">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -3034,7 +3124,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="34" customHeight="1">
+    <row r="13" spans="1:6" ht="33.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -3048,7 +3138,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="34" customHeight="1">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -3062,7 +3152,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="34" customHeight="1">
+    <row r="15" spans="1:6" ht="33.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -3076,7 +3166,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="34" customHeight="1">
+    <row r="16" spans="1:6" ht="33.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -3090,7 +3180,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="34" customHeight="1">
+    <row r="17" spans="1:6" ht="33.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -3104,7 +3194,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="26" customHeight="1">
+    <row r="20" spans="1:6" ht="26.25" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
@@ -3150,7 +3240,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="26" customHeight="1">
+    <row r="25" spans="1:6" ht="26.25" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -3160,7 +3250,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" ht="34" customHeight="1">
+    <row r="26" spans="1:6" ht="33.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -3170,7 +3260,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="34" customHeight="1">
+    <row r="27" spans="1:6" ht="33.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
@@ -3180,7 +3270,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" ht="34" customHeight="1">
+    <row r="28" spans="1:6" ht="33.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -3190,7 +3280,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="30" spans="1:6" ht="26" customHeight="1">
+    <row r="30" spans="1:6" ht="26.25" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>39</v>
       </c>
@@ -3200,7 +3290,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" ht="26" customHeight="1">
+    <row r="31" spans="1:6" ht="26.25" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3272,7 +3362,7 @@
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3310,7 +3400,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32" customHeight="1">
+    <row r="7" spans="1:3" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -3321,7 +3411,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" customHeight="1">
+    <row r="8" spans="1:3" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
@@ -3332,7 +3422,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32" customHeight="1">
+    <row r="9" spans="1:3" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -3343,7 +3433,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" customHeight="1">
+    <row r="10" spans="1:3" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3354,7 +3444,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1">
+    <row r="11" spans="1:3" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
@@ -3365,7 +3455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32" customHeight="1">
+    <row r="12" spans="1:3" ht="32.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -3376,7 +3466,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="32" customHeight="1">
+    <row r="13" spans="1:3" ht="32.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -3387,7 +3477,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="32" customHeight="1">
+    <row r="14" spans="1:3" ht="32.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -3398,7 +3488,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="32" customHeight="1">
+    <row r="15" spans="1:3" ht="32.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>67</v>
       </c>
@@ -3409,7 +3499,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="32" customHeight="1">
+    <row r="16" spans="1:3" ht="32.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -3512,7 +3602,7 @@
     <col min="6" max="6" width="22.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38" customHeight="1">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -4740,7 +4830,7 @@
     <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="38" customHeight="1">
+    <row r="1" spans="1:4" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>135</v>
       </c>
@@ -4934,7 +5024,7 @@
         <v>0.017</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="32" customHeight="1">
+    <row r="27" spans="1:4" ht="32.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>157</v>
       </c>
@@ -4956,7 +5046,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="38" customHeight="1">
+    <row r="32" spans="1:4" ht="38.25" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>162</v>
       </c>
@@ -4968,7 +5058,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="34" customHeight="1">
+    <row r="33" spans="1:3" ht="33.75" customHeight="1">
       <c r="A33" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B32),",",", ")</f>
         <v>=QS.QUOTES.CREATE("Loan.Quotes", Loan_ValuationDate)</v>
@@ -4976,7 +5066,7 @@
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
     </row>
-    <row r="35" spans="1:3" ht="38" customHeight="1">
+    <row r="35" spans="1:3" ht="38.25" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>164</v>
       </c>
@@ -4988,7 +5078,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="34" customHeight="1">
+    <row r="36" spans="1:3" ht="33.75" customHeight="1">
       <c r="A36" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_InitialQuotes, '3 Market'!A18, '3 Market'!B18, , )</v>
@@ -4996,7 +5086,7 @@
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
     </row>
-    <row r="38" spans="1:3" ht="38" customHeight="1">
+    <row r="38" spans="1:3" ht="38.25" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>166</v>
       </c>
@@ -5008,7 +5098,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="34" customHeight="1">
+    <row r="39" spans="1:3" ht="33.75" customHeight="1">
       <c r="A39" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B38),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote1, '3 Market'!A19, '3 Market'!B19, , )</v>
@@ -5016,7 +5106,7 @@
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
     </row>
-    <row r="41" spans="1:3" ht="38" customHeight="1">
+    <row r="41" spans="1:3" ht="38.25" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>167</v>
       </c>
@@ -5028,7 +5118,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="34" customHeight="1">
+    <row r="42" spans="1:3" ht="33.75" customHeight="1">
       <c r="A42" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B41),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote2, '3 Market'!A20, '3 Market'!B20, , )</v>
@@ -5036,7 +5126,7 @@
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
     </row>
-    <row r="44" spans="1:3" ht="38" customHeight="1">
+    <row r="44" spans="1:3" ht="38.25" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>168</v>
       </c>
@@ -5048,7 +5138,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="34" customHeight="1">
+    <row r="45" spans="1:3" ht="33.75" customHeight="1">
       <c r="A45" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B44),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote3, '3 Market'!A21, '3 Market'!B21, , )</v>
@@ -5056,7 +5146,7 @@
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
     </row>
-    <row r="47" spans="1:3" ht="38" customHeight="1">
+    <row r="47" spans="1:3" ht="38.25" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>169</v>
       </c>
@@ -5068,7 +5158,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="34" customHeight="1">
+    <row r="48" spans="1:3" ht="33.75" customHeight="1">
       <c r="A48" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B47),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote4, '3 Market'!A22, '3 Market'!B22, , )</v>
@@ -5076,7 +5166,7 @@
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
     </row>
-    <row r="50" spans="1:3" ht="38" customHeight="1">
+    <row r="50" spans="1:3" ht="38.25" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>170</v>
       </c>
@@ -5088,7 +5178,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="34" customHeight="1">
+    <row r="51" spans="1:3" ht="33.75" customHeight="1">
       <c r="A51" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B50),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote5, '3 Market'!A23, '3 Market'!B23, , )</v>
@@ -5096,7 +5186,7 @@
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
     </row>
-    <row r="53" spans="1:3" ht="38" customHeight="1">
+    <row r="53" spans="1:3" ht="38.25" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>171</v>
       </c>
@@ -5108,7 +5198,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="34" customHeight="1">
+    <row r="54" spans="1:3" ht="33.75" customHeight="1">
       <c r="A54" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B53),",",", ")</f>
         <v>=QS.QUOTES.SET(Loan_CreditQuote6, '3 Market'!A24, '3 Market'!B24, , )</v>
@@ -5116,7 +5206,7 @@
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
     </row>
-    <row r="56" spans="1:3" ht="38" customHeight="1">
+    <row r="56" spans="1:3" ht="38.25" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>172</v>
       </c>
@@ -5128,7 +5218,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="34" customHeight="1">
+    <row r="57" spans="1:3" ht="33.75" customHeight="1">
       <c r="A57" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B56),",",", ")</f>
         <v>=QS.CURVE.CONFIGS.CREATE("Loan.Curves")</v>
@@ -5136,7 +5226,7 @@
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
     </row>
-    <row r="59" spans="1:3" ht="38" customHeight="1">
+    <row r="59" spans="1:3" ht="38.25" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>174</v>
       </c>
@@ -5148,7 +5238,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="34" customHeight="1">
+    <row r="60" spans="1:3" ht="33.75" customHeight="1">
       <c r="A60" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B59),",",", ")</f>
         <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_InitialCurves, "ESTR", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_ZeroRates, "Continuous", "Annual")</v>
@@ -5156,7 +5246,7 @@
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
     </row>
-    <row r="62" spans="1:3" ht="38" customHeight="1">
+    <row r="62" spans="1:3" ht="38.25" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>176</v>
       </c>
@@ -5168,7 +5258,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="34" customHeight="1">
+    <row r="63" spans="1:3" ht="33.75" customHeight="1">
       <c r="A63" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B62),",",", ")</f>
         <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_BaseCurves, "EURIBOR12m", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_ForwardRates, "Continuous", "Annual")</v>
@@ -5176,7 +5266,7 @@
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
     </row>
-    <row r="65" spans="1:3" ht="38" customHeight="1">
+    <row r="65" spans="1:3" ht="38.25" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>178</v>
       </c>
@@ -5188,7 +5278,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="34" customHeight="1">
+    <row r="66" spans="1:3" ht="33.75" customHeight="1">
       <c r="A66" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B65),",",", ")</f>
         <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_ForwardCurves, "FUNDINGSPREAD", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_FundingSpreads, "Continuous", "Annual")</v>
@@ -5196,7 +5286,7 @@
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
     </row>
-    <row r="68" spans="1:3" ht="38" customHeight="1">
+    <row r="68" spans="1:3" ht="38.25" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>180</v>
       </c>
@@ -5208,7 +5298,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="34" customHeight="1">
+    <row r="69" spans="1:3" ht="33.75" customHeight="1">
       <c r="A69" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B68),",",", ")</f>
         <v>=QS.CURVE.CONFIGS.ADD.COMPOSITE(Loan_SpreadCurves, "FUNDING", "EURIBOR12m", "FUNDINGSPREAD")</v>
@@ -5216,7 +5306,7 @@
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
     </row>
-    <row r="71" spans="1:3" ht="38" customHeight="1">
+    <row r="71" spans="1:3" ht="38.25" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>182</v>
       </c>
@@ -5228,7 +5318,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="34" customHeight="1">
+    <row r="72" spans="1:3" ht="33.75" customHeight="1">
       <c r="A72" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B71),",",", ")</f>
         <v>=QS.CREDIT.CURVE.CONFIGS.CREATE("Loan.Credit")</v>
@@ -5236,7 +5326,7 @@
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
     </row>
-    <row r="74" spans="1:3" ht="38" customHeight="1">
+    <row r="74" spans="1:3" ht="38.25" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>184</v>
       </c>
@@ -5248,7 +5338,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="34" customHeight="1">
+    <row r="75" spans="1:3" ht="33.75" customHeight="1">
       <c r="A75" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B74),",",", ")</f>
         <v>=QS.CREDIT.CURVE.CONFIGS.ADD(Loan_InitialCredit, "Credit:BORROWER", "EUR", "ESTR", Loan_Recovery, Loan_CreditQuotes)</v>
@@ -5296,14 +5386,14 @@
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C302"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>186</v>
       </c>
@@ -5341,27 +5431,27 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38" customHeight="1">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>191</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("Loan.Context",Loan_Quotes,Loan_Curves,Loan_Credit,,,,,,,,,"EUR","ESTR","Mid")</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.FROM.COMPONENTS("Loan.Context",Loan_Quotes,Loan_Curves,Loan_Credit,,,,,,,,,"EUR","ESTR","Mid")</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="34" customHeight="1">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
       <c r="A8" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("Loan.Context", Loan_Quotes, Loan_Curves, Loan_Credit, , , , , , , , , "EUR", "ESTR", "Mid")</v>
+        <v>=QS.CONTEXT.FROM.COMPONENTS("Loan.Context", Loan_Quotes, Loan_Curves, Loan_Credit, , , , , , , , , "EUR", "ESTR", "Mid")</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="10" spans="1:3" ht="38" customHeight="1">
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>193</v>
       </c>
@@ -5373,7 +5463,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="34" customHeight="1">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
       <c r="A11" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy", Loan_RiskFreeCurrency, Loan_RiskFreeIndex)</v>
@@ -5381,7 +5471,7 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="13" spans="1:3" ht="38" customHeight="1">
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>195</v>
       </c>
@@ -5393,7 +5483,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="34" customHeight="1">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
       <c r="A14" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.RiskFreePricer", "LoanPricer", Loan_RiskFreePolicy)</v>
@@ -5401,7 +5491,7 @@
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="16" spans="1:3" ht="38" customHeight="1">
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>197</v>
       </c>
@@ -5413,7 +5503,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="34" customHeight="1">
+    <row r="17" spans="1:3" ht="33.75" customHeight="1">
       <c r="A17" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy", Loan_FundingCurrency, Loan_FundingIndex)</v>
@@ -5421,7 +5511,7 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
     </row>
-    <row r="19" spans="1:3" ht="38" customHeight="1">
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>198</v>
       </c>
@@ -5433,7 +5523,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="34" customHeight="1">
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
       <c r="A20" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.FundingPricer", "LoanPricer", Loan_FundingPolicy)</v>
@@ -5441,7 +5531,7 @@
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
     </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1">
+    <row r="22" spans="1:3" ht="38.25" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>199</v>
       </c>
@@ -5453,7 +5543,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="34" customHeight="1">
+    <row r="23" spans="1:3" ht="33.75" customHeight="1">
       <c r="A23" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
         <v>=QS.CURVE.GET(Loan_Context, "ESTR")</v>
@@ -5461,7 +5551,7 @@
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
-    <row r="25" spans="1:3" ht="38" customHeight="1">
+    <row r="25" spans="1:3" ht="38.25" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>201</v>
       </c>
@@ -5473,7 +5563,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="34" customHeight="1">
+    <row r="26" spans="1:3" ht="33.75" customHeight="1">
       <c r="A26" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(0)</v>
@@ -5481,7 +5571,7 @@
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="28" spans="1:3" ht="38" customHeight="1">
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>203</v>
       </c>
@@ -5493,7 +5583,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="34" customHeight="1">
+    <row r="29" spans="1:3" ht="33.75" customHeight="1">
       <c r="A29" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(1)</v>
@@ -5501,7 +5591,7 @@
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
     </row>
-    <row r="31" spans="1:3" ht="38" customHeight="1">
+    <row r="31" spans="1:3" ht="38.25" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>204</v>
       </c>
@@ -5513,7 +5603,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="34" customHeight="1">
+    <row r="32" spans="1:3" ht="33.75" customHeight="1">
       <c r="A32" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(2)</v>
@@ -5533,7 +5623,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="38" customHeight="1">
+    <row r="37" spans="1:3" ht="38.25" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>206</v>
       </c>
@@ -5553,7 +5643,7 @@
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="40" spans="1:3" ht="38" customHeight="1">
+    <row r="40" spans="1:3" ht="38.25" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>207</v>
       </c>
@@ -5565,7 +5655,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="34" customHeight="1">
+    <row r="41" spans="1:3" ht="33.75" customHeight="1">
       <c r="A41" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C01.Trade", Loan_C01_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5573,7 +5663,7 @@
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
     </row>
-    <row r="43" spans="1:3" ht="38" customHeight="1">
+    <row r="43" spans="1:3" ht="38.25" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>209</v>
       </c>
@@ -5585,7 +5675,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="34" customHeight="1">
+    <row r="44" spans="1:3" ht="33.75" customHeight="1">
       <c r="A44" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
         <v>=IF(Loan_C01_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5593,7 +5683,7 @@
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
     </row>
-    <row r="46" spans="1:3" ht="38" customHeight="1">
+    <row r="46" spans="1:3" ht="38.25" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>211</v>
       </c>
@@ -5605,7 +5695,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="34" customHeight="1">
+    <row r="47" spans="1:3" ht="33.75" customHeight="1">
       <c r="A47" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C01.Result", Loan_C01_Pricer, Loan_C01_Trade, Loan_Context, Loan_Requests)</v>
@@ -5613,7 +5703,7 @@
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
     </row>
-    <row r="49" spans="1:3" ht="38" customHeight="1">
+    <row r="49" spans="1:3" ht="38.25" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>213</v>
       </c>
@@ -5625,7 +5715,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="34" customHeight="1">
+    <row r="50" spans="1:3" ht="33.75" customHeight="1">
       <c r="A50" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C01.Fair0", Loan_C01_Pricer, Loan_C01_Trade, Loan_Context, Loan_Request0)</v>
@@ -5645,7 +5735,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="38" customHeight="1">
+    <row r="57" spans="1:3" ht="38.25" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>206</v>
       </c>
@@ -5665,7 +5755,7 @@
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
     </row>
-    <row r="60" spans="1:3" ht="38" customHeight="1">
+    <row r="60" spans="1:3" ht="38.25" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>207</v>
       </c>
@@ -5677,7 +5767,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="34" customHeight="1">
+    <row r="61" spans="1:3" ht="33.75" customHeight="1">
       <c r="A61" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B60),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C02.Trade", Loan_C02_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5685,7 +5775,7 @@
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
     </row>
-    <row r="63" spans="1:3" ht="38" customHeight="1">
+    <row r="63" spans="1:3" ht="38.25" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>209</v>
       </c>
@@ -5697,7 +5787,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="34" customHeight="1">
+    <row r="64" spans="1:3" ht="33.75" customHeight="1">
       <c r="A64" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B63),",",", ")</f>
         <v>=IF(Loan_C02_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5705,7 +5795,7 @@
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
     </row>
-    <row r="66" spans="1:3" ht="38" customHeight="1">
+    <row r="66" spans="1:3" ht="38.25" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>211</v>
       </c>
@@ -5717,7 +5807,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="34" customHeight="1">
+    <row r="67" spans="1:3" ht="33.75" customHeight="1">
       <c r="A67" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B66),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C02.Result", Loan_C02_Pricer, Loan_C02_Trade, Loan_Context, Loan_Requests)</v>
@@ -5725,7 +5815,7 @@
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
-    <row r="69" spans="1:3" ht="38" customHeight="1">
+    <row r="69" spans="1:3" ht="38.25" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>213</v>
       </c>
@@ -5737,7 +5827,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="34" customHeight="1">
+    <row r="70" spans="1:3" ht="33.75" customHeight="1">
       <c r="A70" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B69),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C02.Fair0", Loan_C02_Pricer, Loan_C02_Trade, Loan_Context, Loan_Request0)</v>
@@ -5757,1333 +5847,1453 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="38" customHeight="1">
+    <row r="77" spans="1:3" ht="38.25" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B77" s="10" cm="1" t="str">
-        <f t="array" ref="B77">_xll.QS.INSTRUMENT.LOAN("Loan.C03.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C03_Rate,Loan_C03_Index,Loan_C03_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C03_Settings,)</f>
+        <f t="array" ref="B77">_xll.QS.LOAN.SETTINGS("Loan.C03.Options",INDEX(Loan_C03_Settings,2,2))</f>
         <v/>
       </c>
       <c r="C77" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="48" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="33.75" customHeight="1">
       <c r="A78" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B77),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C03.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C03_Rate, Loan_C03_Index, Loan_C03_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C03_Settings, )</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C03.Options", INDEX(Loan_C03_Settings, 2, 2))</v>
       </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
     </row>
-    <row r="80" spans="1:3" ht="38" customHeight="1">
+    <row r="80" spans="1:3" ht="38.25" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B80" s="10" cm="1" t="str">
-        <f t="array" ref="B80">_xll.QS.TRADE.CREATE("Loan.C03.Trade",Loan_C03_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <f t="array" ref="B80">_xll.QS.INSTRUMENT.LOAN("Loan.C03.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C03_Rate,Loan_C03_Index,Loan_C03_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C03_Options,)</f>
         <v/>
       </c>
       <c r="C80" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="34" customHeight="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="48" customHeight="1">
       <c r="A81" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B80),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C03.Trade", Loan_C03_Instrument, Loan_ValuationDate, Loan_Side)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C03.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C03_Rate, Loan_C03_Index, Loan_C03_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C03_Options, )</v>
       </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
     </row>
-    <row r="83" spans="1:3" ht="38" customHeight="1">
+    <row r="83" spans="1:3" ht="38.25" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B83" s="10">
-        <f>IF(Loan_C03_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v>207</v>
+      </c>
+      <c r="B83" s="10" cm="1" t="str">
+        <f t="array" ref="B83">_xll.QS.TRADE.CREATE("Loan.C03.Trade",Loan_C03_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C83" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="34" customHeight="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="33.75" customHeight="1">
       <c r="A84" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B83),",",", ")</f>
-        <v>=IF(Loan_C03_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+        <v>=QS.TRADE.CREATE("Loan.C03.Trade", Loan_C03_Instrument, Loan_ValuationDate, Loan_Side)</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
     </row>
-    <row r="86" spans="1:3" ht="38" customHeight="1">
+    <row r="86" spans="1:3" ht="38.25" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B86" s="10" cm="1" t="str">
-        <f t="array" ref="B86">_xll.QS.EVALUATE("Loan.C03.Result",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Requests)</f>
+        <v>209</v>
+      </c>
+      <c r="B86" s="10">
+        <f>IF(Loan_C03_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C86" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="34" customHeight="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="33.75" customHeight="1">
       <c r="A87" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B86),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C03.Result", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=IF(Loan_C03_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
       </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
     </row>
-    <row r="89" spans="1:3" ht="38" customHeight="1">
+    <row r="89" spans="1:3" ht="38.25" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B89" s="10" cm="1" t="str">
-        <f t="array" ref="B89">_xll.QS.EVALUATE("Loan.C03.Fair0",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B89">_xll.QS.EVALUATE("Loan.C03.Result",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Requests)</f>
         <v/>
       </c>
       <c r="C89" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="34" customHeight="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="33.75" customHeight="1">
       <c r="A90" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B89),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C03.Fair0", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE("Loan.C03.Result", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Requests)</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
     </row>
-    <row r="94" spans="1:3" ht="24" customHeight="1">
-      <c r="A94" s="4" t="s">
+    <row r="92" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A92" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B92" s="10" cm="1" t="str">
+        <f t="array" ref="B92">_xll.QS.EVALUATE("Loan.C03.Fair0",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A93" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B92),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C03.Fair0", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+    </row>
+    <row r="97" spans="1:3" ht="24" customHeight="1">
+      <c r="A97" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-    </row>
-    <row r="95" spans="1:3" ht="24" customHeight="1">
-      <c r="A95" s="6" t="s">
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:3" ht="24" customHeight="1">
+      <c r="A98" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="38" customHeight="1">
-      <c r="A97" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B97" s="10" cm="1" t="str">
-        <f t="array" ref="B97">_xll.QS.INSTRUMENT.LOAN("Loan.C04.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C04_Rate,Loan_C04_Index,Loan_C04_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C04_Settings,)</f>
-        <v/>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="48" customHeight="1">
-      <c r="A98" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B97),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C04.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C04_Rate, Loan_C04_Index, Loan_C04_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C04_Settings, )</v>
-      </c>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-    </row>
-    <row r="100" spans="1:3" ht="38" customHeight="1">
+    <row r="100" spans="1:3" ht="38.25" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B100" s="10" cm="1" t="str">
-        <f t="array" ref="B100">_xll.QS.TRADE.CREATE("Loan.C04.Trade",Loan_C04_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <f t="array" ref="B100">_xll.QS.LOAN.SETTINGS("Loan.C04.Options",,INDEX(Loan_C04_Settings,2,2))</f>
         <v/>
       </c>
       <c r="C100" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="34" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="33.75" customHeight="1">
       <c r="A101" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C04.Trade", Loan_C04_Instrument, Loan_ValuationDate, Loan_Side)</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C04.Options", , INDEX(Loan_C04_Settings, 2, 2))</v>
       </c>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
     </row>
-    <row r="103" spans="1:3" ht="38" customHeight="1">
+    <row r="103" spans="1:3" ht="38.25" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B103" s="10">
-        <f>IF(Loan_C04_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v>206</v>
+      </c>
+      <c r="B103" s="10" cm="1" t="str">
+        <f t="array" ref="B103">_xll.QS.INSTRUMENT.LOAN("Loan.C04.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C04_Rate,Loan_C04_Index,Loan_C04_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C04_Options,)</f>
         <v/>
       </c>
       <c r="C103" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="34" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="48" customHeight="1">
       <c r="A104" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B103),",",", ")</f>
-        <v>=IF(Loan_C04_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C04.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C04_Rate, Loan_C04_Index, Loan_C04_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C04_Options, )</v>
       </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
     </row>
-    <row r="106" spans="1:3" ht="38" customHeight="1">
+    <row r="106" spans="1:3" ht="38.25" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B106" s="10" cm="1" t="str">
-        <f t="array" ref="B106">_xll.QS.EVALUATE("Loan.C04.Result",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B106">_xll.QS.TRADE.CREATE("Loan.C04.Trade",Loan_C04_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C106" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="34" customHeight="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="33.75" customHeight="1">
       <c r="A107" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B106),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C04.Result", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.TRADE.CREATE("Loan.C04.Trade", Loan_C04_Instrument, Loan_ValuationDate, Loan_Side)</v>
       </c>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
     </row>
-    <row r="109" spans="1:3" ht="38" customHeight="1">
+    <row r="109" spans="1:3" ht="38.25" customHeight="1">
       <c r="A109" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B109" s="10" cm="1" t="str">
-        <f t="array" ref="B109">_xll.QS.EVALUATE("Loan.C04.Fair0",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Request0)</f>
+        <v>209</v>
+      </c>
+      <c r="B109" s="10">
+        <f>IF(Loan_C04_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C109" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="34" customHeight="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="33.75" customHeight="1">
       <c r="A110" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B109),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C04.Fair0", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=IF(Loan_C04_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
       </c>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
     </row>
-    <row r="114" spans="1:3" ht="24" customHeight="1">
-      <c r="A114" s="4" t="s">
+    <row r="112" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A112" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B112" s="10" cm="1" t="str">
+        <f t="array" ref="B112">_xll.QS.EVALUATE("Loan.C04.Result",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A113" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B112),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C04.Result", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+    </row>
+    <row r="115" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A115" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B115" s="10" cm="1" t="str">
+        <f t="array" ref="B115">_xll.QS.EVALUATE("Loan.C04.Fair0",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A116" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B115),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C04.Fair0", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+    </row>
+    <row r="120" spans="1:3" ht="24" customHeight="1">
+      <c r="A120" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-    </row>
-    <row r="115" spans="1:3" ht="24" customHeight="1">
-      <c r="A115" s="6" t="s">
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+    </row>
+    <row r="121" spans="1:3" ht="24" customHeight="1">
+      <c r="A121" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="38" customHeight="1">
-      <c r="A117" s="4" t="s">
+    <row r="123" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A123" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B117" s="10" cm="1" t="str">
-        <f t="array" ref="B117">_xll.QS.INSTRUMENT.LOAN("Loan.C05.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C05_Rate,Loan_C05_Index,Loan_C05_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C05_Coupons)</f>
-        <v/>
-      </c>
-      <c r="C117" s="7" t="s">
+      <c r="B123" s="10" cm="1" t="str">
+        <f t="array" ref="B123">_xll.QS.INSTRUMENT.LOAN("Loan.C05.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C05_Rate,Loan_C05_Index,Loan_C05_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C05_Coupons)</f>
+        <v/>
+      </c>
+      <c r="C123" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="48" customHeight="1">
-      <c r="A118" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B117),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C05.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C05_Rate, Loan_C05_Index, Loan_C05_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C05_Coupons)</v>
-      </c>
-      <c r="B118" s="14"/>
-      <c r="C118" s="14"/>
-    </row>
-    <row r="120" spans="1:3" ht="38" customHeight="1">
-      <c r="A120" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B120" s="10" cm="1" t="str">
-        <f t="array" ref="B120">_xll.QS.TRADE.CREATE("Loan.C05.Trade",Loan_C05_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="34" customHeight="1">
-      <c r="A121" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B120),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C05.Trade", Loan_C05_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B121" s="14"/>
-      <c r="C121" s="14"/>
-    </row>
-    <row r="123" spans="1:3" ht="38" customHeight="1">
-      <c r="A123" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B123" s="10">
-        <f>IF(Loan_C05_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
-        <v/>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="34" customHeight="1">
+    <row r="124" spans="1:3" ht="48" customHeight="1">
       <c r="A124" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B123),",",", ")</f>
-        <v>=IF(Loan_C05_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C05.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C05_Rate, Loan_C05_Index, Loan_C05_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C05_Coupons)</v>
       </c>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
     </row>
-    <row r="126" spans="1:3" ht="38" customHeight="1">
+    <row r="126" spans="1:3" ht="38.25" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B126" s="10" cm="1" t="str">
-        <f t="array" ref="B126">_xll.QS.EVALUATE("Loan.C05.Result",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B126">_xll.QS.TRADE.CREATE("Loan.C05.Trade",Loan_C05_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C126" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="34" customHeight="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="33.75" customHeight="1">
       <c r="A127" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B126),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Result", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.TRADE.CREATE("Loan.C05.Trade", Loan_C05_Instrument, Loan_ValuationDate, Loan_Side)</v>
       </c>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
     </row>
-    <row r="129" spans="1:3" ht="38" customHeight="1">
+    <row r="129" spans="1:3" ht="38.25" customHeight="1">
       <c r="A129" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B129" s="10" cm="1" t="str">
-        <f t="array" ref="B129">_xll.QS.EVALUATE("Loan.C05.Fair0",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request0)</f>
+        <v>209</v>
+      </c>
+      <c r="B129" s="10">
+        <f>IF(Loan_C05_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C129" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="34" customHeight="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="33.75" customHeight="1">
       <c r="A130" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B129),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Fair0", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=IF(Loan_C05_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
       </c>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
     </row>
-    <row r="132" spans="1:3" ht="38" customHeight="1">
+    <row r="132" spans="1:3" ht="38.25" customHeight="1">
       <c r="A132" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B132" s="10" cm="1" t="str">
-        <f t="array" ref="B132">_xll.QS.EVALUATE("Loan.C05.Fair1",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request1)</f>
+        <f t="array" ref="B132">_xll.QS.EVALUATE("Loan.C05.Result",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Requests)</f>
         <v/>
       </c>
       <c r="C132" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="34" customHeight="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="33.75" customHeight="1">
       <c r="A133" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B132),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Fair1", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request1)</v>
+        <v>=QS.EVALUATE("Loan.C05.Result", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Requests)</v>
       </c>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
     </row>
-    <row r="137" spans="1:3" ht="24" customHeight="1">
-      <c r="A137" s="4" t="s">
+    <row r="135" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A135" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B135" s="10" cm="1" t="str">
+        <f t="array" ref="B135">_xll.QS.EVALUATE("Loan.C05.Fair0",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A136" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B135),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C05.Fair0", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B136" s="14"/>
+      <c r="C136" s="14"/>
+    </row>
+    <row r="138" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A138" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B138" s="10" cm="1" t="str">
+        <f t="array" ref="B138">_xll.QS.EVALUATE("Loan.C05.Fair1",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request1)</f>
+        <v/>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A139" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B138),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C05.Fair1", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request1)</v>
+      </c>
+      <c r="B139" s="14"/>
+      <c r="C139" s="14"/>
+    </row>
+    <row r="143" spans="1:3" ht="24" customHeight="1">
+      <c r="A143" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-    </row>
-    <row r="138" spans="1:3" ht="24" customHeight="1">
-      <c r="A138" s="6" t="s">
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+    </row>
+    <row r="144" spans="1:3" ht="24" customHeight="1">
+      <c r="A144" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="38" customHeight="1">
-      <c r="A140" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B140" s="10" cm="1" t="str">
-        <f t="array" ref="B140">_xll.QS.INSTRUMENT.LOAN("Loan.C06.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C06_Rate,Loan_C06_Index,Loan_C06_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C06_Settings,)</f>
-        <v/>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="48" customHeight="1">
-      <c r="A141" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B140),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C06.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C06_Rate, Loan_C06_Index, Loan_C06_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C06_Settings, )</v>
-      </c>
-      <c r="B141" s="14"/>
-      <c r="C141" s="14"/>
-    </row>
-    <row r="143" spans="1:3" ht="38" customHeight="1">
-      <c r="A143" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B143" s="10" cm="1" t="str">
-        <f t="array" ref="B143">_xll.QS.TRADE.CREATE("Loan.C06.Trade",Loan_C06_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="34" customHeight="1">
-      <c r="A144" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B143),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C06.Trade", Loan_C06_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B144" s="14"/>
-      <c r="C144" s="14"/>
-    </row>
-    <row r="146" spans="1:3" ht="38" customHeight="1">
+    <row r="146" spans="1:3" ht="38.25" customHeight="1">
       <c r="A146" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B146" s="10">
-        <f>IF(Loan_C06_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v>215</v>
+      </c>
+      <c r="B146" s="10" cm="1" t="str">
+        <f t="array" ref="B146">_xll.QS.LOAN.SETTINGS("Loan.C06.Options",,INDEX(Loan_C06_Settings,2,2),,,,,,,,INDEX(Loan_C06_Settings,3,2),INDEX(Loan_C06_Settings,4,2))</f>
         <v/>
       </c>
       <c r="C146" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="34" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="33.75" customHeight="1">
       <c r="A147" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B146),",",", ")</f>
-        <v>=IF(Loan_C06_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C06.Options", , INDEX(Loan_C06_Settings, 2, 2), , , , , , , , INDEX(Loan_C06_Settings, 3, 2), INDEX(Loan_C06_Settings, 4, 2))</v>
       </c>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
     </row>
-    <row r="149" spans="1:3" ht="38" customHeight="1">
+    <row r="149" spans="1:3" ht="38.25" customHeight="1">
       <c r="A149" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B149" s="10" cm="1" t="str">
-        <f t="array" ref="B149">_xll.QS.EVALUATE("Loan.C06.Result",Loan_C06_Pricer,Loan_C06_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B149">_xll.QS.INSTRUMENT.LOAN("Loan.C06.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C06_Rate,Loan_C06_Index,Loan_C06_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C06_Options,)</f>
         <v/>
       </c>
       <c r="C149" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="34" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="48" customHeight="1">
       <c r="A150" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B149),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C06.Result", Loan_C06_Pricer, Loan_C06_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C06.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C06_Rate, Loan_C06_Index, Loan_C06_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C06_Options, )</v>
       </c>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
     </row>
-    <row r="154" spans="1:3" ht="24" customHeight="1">
-      <c r="A154" s="4" t="s">
+    <row r="152" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A152" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B152" s="10" cm="1" t="str">
+        <f t="array" ref="B152">_xll.QS.TRADE.CREATE("Loan.C06.Trade",Loan_C06_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A153" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B152),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Loan.C06.Trade", Loan_C06_Instrument, Loan_ValuationDate, Loan_Side)</v>
+      </c>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+    </row>
+    <row r="155" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A155" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B155" s="10">
+        <f>IF(Loan_C06_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v/>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A156" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B155),",",", ")</f>
+        <v>=IF(Loan_C06_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+      </c>
+      <c r="B156" s="14"/>
+      <c r="C156" s="14"/>
+    </row>
+    <row r="158" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A158" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B158" s="10" cm="1" t="str">
+        <f t="array" ref="B158">_xll.QS.EVALUATE("Loan.C06.Result",Loan_C06_Pricer,Loan_C06_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A159" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B158),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C06.Result", Loan_C06_Pricer, Loan_C06_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
+    </row>
+    <row r="163" spans="1:3" ht="24" customHeight="1">
+      <c r="A163" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-    </row>
-    <row r="155" spans="1:3" ht="24" customHeight="1">
-      <c r="A155" s="6" t="s">
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+    </row>
+    <row r="164" spans="1:3" ht="24" customHeight="1">
+      <c r="A164" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="38" customHeight="1">
-      <c r="A157" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B157" s="10" cm="1" t="str">
-        <f t="array" ref="B157">_xll.QS.INSTRUMENT.LOAN("Loan.C07.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C07_Rate,Loan_C07_Index,Loan_C07_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C07_Settings,)</f>
-        <v/>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="48" customHeight="1">
-      <c r="A158" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B157),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C07.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C07_Rate, Loan_C07_Index, Loan_C07_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C07_Settings, )</v>
-      </c>
-      <c r="B158" s="14"/>
-      <c r="C158" s="14"/>
-    </row>
-    <row r="160" spans="1:3" ht="38" customHeight="1">
-      <c r="A160" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B160" s="10" cm="1" t="str">
-        <f t="array" ref="B160">_xll.QS.TRADE.CREATE("Loan.C07.Trade",Loan_C07_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="34" customHeight="1">
-      <c r="A161" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B160),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C07.Trade", Loan_C07_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B161" s="14"/>
-      <c r="C161" s="14"/>
-    </row>
-    <row r="163" spans="1:3" ht="38" customHeight="1">
-      <c r="A163" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B163" s="10">
-        <f>IF(Loan_C07_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
-        <v/>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="34" customHeight="1">
-      <c r="A164" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B163),",",", ")</f>
-        <v>=IF(Loan_C07_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
-      </c>
-      <c r="B164" s="14"/>
-      <c r="C164" s="14"/>
-    </row>
-    <row r="166" spans="1:3" ht="38" customHeight="1">
+    <row r="166" spans="1:3" ht="38.25" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B166" s="10" cm="1" t="str">
-        <f t="array" ref="B166">_xll.QS.EVALUATE("Loan.C07.Result",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B166">_xll.QS.LOAN.SETTINGS("Loan.C07.Options",,,,,,,,,,,,,,INDEX(Loan_C07_Settings,2,2))</f>
         <v/>
       </c>
       <c r="C166" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="34" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="33.75" customHeight="1">
       <c r="A167" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B166),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C07.Result", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C07.Options", , , , , , , , , , , , , , INDEX(Loan_C07_Settings, 2, 2))</v>
       </c>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
     </row>
-    <row r="169" spans="1:3" ht="38" customHeight="1">
+    <row r="169" spans="1:3" ht="38.25" customHeight="1">
       <c r="A169" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B169" s="10" cm="1" t="str">
-        <f t="array" ref="B169">_xll.QS.EVALUATE("Loan.C07.Fair0",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B169">_xll.QS.INSTRUMENT.LOAN("Loan.C07.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C07_Rate,Loan_C07_Index,Loan_C07_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C07_Options,)</f>
         <v/>
       </c>
       <c r="C169" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="34" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="48" customHeight="1">
       <c r="A170" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B169),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C07.Fair0", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C07.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C07_Rate, Loan_C07_Index, Loan_C07_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C07_Options, )</v>
       </c>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
     </row>
-    <row r="174" spans="1:3" ht="24" customHeight="1">
-      <c r="A174" s="4" t="s">
+    <row r="172" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A172" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B172" s="10" cm="1" t="str">
+        <f t="array" ref="B172">_xll.QS.TRADE.CREATE("Loan.C07.Trade",Loan_C07_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A173" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B172),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Loan.C07.Trade", Loan_C07_Instrument, Loan_ValuationDate, Loan_Side)</v>
+      </c>
+      <c r="B173" s="14"/>
+      <c r="C173" s="14"/>
+    </row>
+    <row r="175" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A175" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B175" s="10">
+        <f>IF(Loan_C07_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v/>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A176" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B175),",",", ")</f>
+        <v>=IF(Loan_C07_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+      </c>
+      <c r="B176" s="14"/>
+      <c r="C176" s="14"/>
+    </row>
+    <row r="178" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A178" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B178" s="10" cm="1" t="str">
+        <f t="array" ref="B178">_xll.QS.EVALUATE("Loan.C07.Result",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A179" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B178),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C07.Result", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B179" s="14"/>
+      <c r="C179" s="14"/>
+    </row>
+    <row r="181" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A181" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B181" s="10" cm="1" t="str">
+        <f t="array" ref="B181">_xll.QS.EVALUATE("Loan.C07.Fair0",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A182" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B181),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C07.Fair0", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B182" s="14"/>
+      <c r="C182" s="14"/>
+    </row>
+    <row r="186" spans="1:3" ht="24" customHeight="1">
+      <c r="A186" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-    </row>
-    <row r="175" spans="1:3" ht="24" customHeight="1">
-      <c r="A175" s="6" t="s">
+      <c r="B186" s="4"/>
+      <c r="C186" s="4"/>
+    </row>
+    <row r="187" spans="1:3" ht="24" customHeight="1">
+      <c r="A187" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="38" customHeight="1">
-      <c r="A177" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B177" s="10" cm="1" t="str">
-        <f t="array" ref="B177">_xll.QS.INSTRUMENT.LOAN("Loan.C08.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C08_Rate,Loan_C08_Index,Loan_C08_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C08_Settings,)</f>
-        <v/>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="48" customHeight="1">
-      <c r="A178" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B177),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C08.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C08_Rate, Loan_C08_Index, Loan_C08_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C08_Settings, )</v>
-      </c>
-      <c r="B178" s="14"/>
-      <c r="C178" s="14"/>
-    </row>
-    <row r="180" spans="1:3" ht="38" customHeight="1">
-      <c r="A180" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B180" s="10" cm="1" t="str">
-        <f t="array" ref="B180">_xll.QS.TRADE.CREATE("Loan.C08.Trade",Loan_C08_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="34" customHeight="1">
-      <c r="A181" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B180),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C08.Trade", Loan_C08_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B181" s="14"/>
-      <c r="C181" s="14"/>
-    </row>
-    <row r="183" spans="1:3" ht="38" customHeight="1">
-      <c r="A183" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B183" s="10">
-        <f>IF(Loan_C08_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
-        <v/>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="34" customHeight="1">
-      <c r="A184" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B183),",",", ")</f>
-        <v>=IF(Loan_C08_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
-      </c>
-      <c r="B184" s="14"/>
-      <c r="C184" s="14"/>
-    </row>
-    <row r="186" spans="1:3" ht="38" customHeight="1">
-      <c r="A186" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B186" s="10" cm="1" t="str">
-        <f t="array" ref="B186">_xll.QS.EVALUATE("Loan.C08.Result",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Requests)</f>
-        <v/>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="34" customHeight="1">
-      <c r="A187" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B186),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C08.Result", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Requests)</v>
-      </c>
-      <c r="B187" s="14"/>
-      <c r="C187" s="14"/>
-    </row>
-    <row r="189" spans="1:3" ht="38" customHeight="1">
+    <row r="189" spans="1:3" ht="38.25" customHeight="1">
       <c r="A189" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B189" s="10" cm="1" t="str">
-        <f t="array" ref="B189">_xll.QS.EVALUATE("Loan.C08.Fair0",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B189">_xll.QS.LOAN.SETTINGS("Loan.C08.Options",,,INDEX(Loan_C08_Settings,2,2),INDEX(Loan_C08_Settings,3,2))</f>
         <v/>
       </c>
       <c r="C189" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="34" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="33.75" customHeight="1">
       <c r="A190" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B189),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C08.Fair0", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C08.Options", , , INDEX(Loan_C08_Settings, 2, 2), INDEX(Loan_C08_Settings, 3, 2))</v>
       </c>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
     </row>
-    <row r="194" spans="1:3" ht="24" customHeight="1">
-      <c r="A194" s="4" t="s">
+    <row r="192" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A192" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" s="10" cm="1" t="str">
+        <f t="array" ref="B192">_xll.QS.INSTRUMENT.LOAN("Loan.C08.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C08_Rate,Loan_C08_Index,Loan_C08_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C08_Options,)</f>
+        <v/>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="48" customHeight="1">
+      <c r="A193" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B192),",",", ")</f>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C08.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C08_Rate, Loan_C08_Index, Loan_C08_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C08_Options, )</v>
+      </c>
+      <c r="B193" s="14"/>
+      <c r="C193" s="14"/>
+    </row>
+    <row r="195" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A195" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B195" s="10" cm="1" t="str">
+        <f t="array" ref="B195">_xll.QS.TRADE.CREATE("Loan.C08.Trade",Loan_C08_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A196" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B195),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Loan.C08.Trade", Loan_C08_Instrument, Loan_ValuationDate, Loan_Side)</v>
+      </c>
+      <c r="B196" s="14"/>
+      <c r="C196" s="14"/>
+    </row>
+    <row r="198" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A198" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B198" s="10">
+        <f>IF(Loan_C08_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v/>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A199" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B198),",",", ")</f>
+        <v>=IF(Loan_C08_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+      </c>
+      <c r="B199" s="14"/>
+      <c r="C199" s="14"/>
+    </row>
+    <row r="201" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A201" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B201" s="10" cm="1" t="str">
+        <f t="array" ref="B201">_xll.QS.EVALUATE("Loan.C08.Result",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A202" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B201),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C08.Result", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B202" s="14"/>
+      <c r="C202" s="14"/>
+    </row>
+    <row r="204" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A204" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B204" s="10" cm="1" t="str">
+        <f t="array" ref="B204">_xll.QS.EVALUATE("Loan.C08.Fair0",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A205" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B204),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C08.Fair0", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B205" s="14"/>
+      <c r="C205" s="14"/>
+    </row>
+    <row r="209" spans="1:3" ht="24" customHeight="1">
+      <c r="A209" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
-    </row>
-    <row r="195" spans="1:3" ht="24" customHeight="1">
-      <c r="A195" s="6" t="s">
+      <c r="B209" s="4"/>
+      <c r="C209" s="4"/>
+    </row>
+    <row r="210" spans="1:3" ht="24" customHeight="1">
+      <c r="A210" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="38" customHeight="1">
-      <c r="A197" s="4" t="s">
+    <row r="212" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A212" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B197" s="10" cm="1" t="str">
-        <f t="array" ref="B197">_xll.QS.INSTRUMENT.LOAN("Loan.C09.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C09_Rate,Loan_C09_Index,Loan_C09_Repayment,Loan_Frequency,Loan_DayCounter,,)</f>
-        <v/>
-      </c>
-      <c r="C197" s="7" t="s">
+      <c r="B212" s="10" cm="1" t="str">
+        <f t="array" ref="B212">_xll.QS.INSTRUMENT.LOAN("Loan.C09.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C09_Rate,Loan_C09_Index,Loan_C09_Repayment,Loan_Frequency,Loan_DayCounter,,)</f>
+        <v/>
+      </c>
+      <c r="C212" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="48" customHeight="1">
-      <c r="A198" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B197),",",", ")</f>
+    <row r="213" spans="1:3" ht="48" customHeight="1">
+      <c r="A213" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B212),",",", ")</f>
         <v>=QS.INSTRUMENT.LOAN("Loan.C09.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C09_Rate, Loan_C09_Index, Loan_C09_Repayment, Loan_Frequency, Loan_DayCounter, , )</v>
       </c>
-      <c r="B198" s="14"/>
-      <c r="C198" s="14"/>
-    </row>
-    <row r="200" spans="1:3" ht="38" customHeight="1">
-      <c r="A200" s="4" t="s">
+      <c r="B213" s="14"/>
+      <c r="C213" s="14"/>
+    </row>
+    <row r="215" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A215" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B200" s="10" cm="1" t="str">
-        <f t="array" ref="B200">_xll.QS.TRADE.CREATE("Loan.C09.Trade",Loan_C09_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C200" s="7" t="s">
+      <c r="B215" s="10" cm="1" t="str">
+        <f t="array" ref="B215">_xll.QS.TRADE.CREATE("Loan.C09.Trade",Loan_C09_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C215" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="34" customHeight="1">
-      <c r="A201" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B200),",",", ")</f>
+    <row r="216" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A216" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B215),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C09.Trade", Loan_C09_Instrument, Loan_ValuationDate, Loan_Side)</v>
       </c>
-      <c r="B201" s="14"/>
-      <c r="C201" s="14"/>
-    </row>
-    <row r="203" spans="1:3" ht="38" customHeight="1">
-      <c r="A203" s="4" t="s">
+      <c r="B216" s="14"/>
+      <c r="C216" s="14"/>
+    </row>
+    <row r="218" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A218" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B203" s="10">
+      <c r="B218" s="10">
         <f>IF(Loan_C09_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
-      <c r="C203" s="7" t="s">
+      <c r="C218" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="34" customHeight="1">
-      <c r="A204" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B203),",",", ")</f>
+    <row r="219" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A219" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B218),",",", ")</f>
         <v>=IF(Loan_C09_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
       </c>
-      <c r="B204" s="14"/>
-      <c r="C204" s="14"/>
-    </row>
-    <row r="206" spans="1:3" ht="38" customHeight="1">
-      <c r="A206" s="4" t="s">
+      <c r="B219" s="14"/>
+      <c r="C219" s="14"/>
+    </row>
+    <row r="221" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A221" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B206" s="10" cm="1" t="str">
-        <f t="array" ref="B206">_xll.QS.EVALUATE("Loan.C09.Result",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Requests)</f>
-        <v/>
-      </c>
-      <c r="C206" s="7" t="s">
+      <c r="B221" s="10" cm="1" t="str">
+        <f t="array" ref="B221">_xll.QS.EVALUATE("Loan.C09.Result",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C221" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="34" customHeight="1">
-      <c r="A207" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B206),",",", ")</f>
+    <row r="222" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A222" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B221),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C09.Result", Loan_C09_Pricer, Loan_C09_Trade, Loan_Context, Loan_Requests)</v>
       </c>
-      <c r="B207" s="14"/>
-      <c r="C207" s="14"/>
-    </row>
-    <row r="209" spans="1:3" ht="38" customHeight="1">
-      <c r="A209" s="4" t="s">
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+    </row>
+    <row r="224" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A224" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B209" s="10" cm="1" t="str">
-        <f t="array" ref="B209">_xll.QS.EVALUATE("Loan.C09.Fair0",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Request0)</f>
-        <v/>
-      </c>
-      <c r="C209" s="7" t="s">
+      <c r="B224" s="10" cm="1" t="str">
+        <f t="array" ref="B224">_xll.QS.EVALUATE("Loan.C09.Fair0",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C224" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="34" customHeight="1">
-      <c r="A210" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B209),",",", ")</f>
+    <row r="225" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A225" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B224),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C09.Fair0", Loan_C09_Pricer, Loan_C09_Trade, Loan_Context, Loan_Request0)</v>
       </c>
-      <c r="B210" s="14"/>
-      <c r="C210" s="14"/>
-    </row>
-    <row r="214" spans="1:3" ht="24" customHeight="1">
-      <c r="A214" s="4" t="s">
+      <c r="B225" s="14"/>
+      <c r="C225" s="14"/>
+    </row>
+    <row r="229" spans="1:3" ht="24" customHeight="1">
+      <c r="A229" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
-    </row>
-    <row r="215" spans="1:3" ht="24" customHeight="1">
-      <c r="A215" s="6" t="s">
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
+    </row>
+    <row r="230" spans="1:3" ht="24" customHeight="1">
+      <c r="A230" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="38" customHeight="1">
-      <c r="A217" s="4" t="s">
+    <row r="232" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A232" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B232" s="10" cm="1" t="str">
+        <f t="array" ref="B232">_xll.QS.LOAN.SETTINGS("Loan.C10.Options",,INDEX(Loan_C10_Settings,2,2))</f>
+        <v/>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A233" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B232),",",", ")</f>
+        <v>=QS.LOAN.SETTINGS("Loan.C10.Options", , INDEX(Loan_C10_Settings, 2, 2))</v>
+      </c>
+      <c r="B233" s="14"/>
+      <c r="C233" s="14"/>
+    </row>
+    <row r="235" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A235" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B217" s="10" cm="1" t="str">
-        <f t="array" ref="B217">_xll.QS.INSTRUMENT.LOAN("Loan.C10.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C10_Rate,Loan_C10_Index,Loan_C10_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C10_Settings,)</f>
-        <v/>
-      </c>
-      <c r="C217" s="7" t="s">
+      <c r="B235" s="10" cm="1" t="str">
+        <f t="array" ref="B235">_xll.QS.INSTRUMENT.LOAN("Loan.C10.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C10_Rate,Loan_C10_Index,Loan_C10_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C10_Options,)</f>
+        <v/>
+      </c>
+      <c r="C235" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="48" customHeight="1">
-      <c r="A218" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B217),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C10.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C10_Rate, Loan_C10_Index, Loan_C10_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C10_Settings, )</v>
-      </c>
-      <c r="B218" s="14"/>
-      <c r="C218" s="14"/>
-    </row>
-    <row r="220" spans="1:3" ht="38" customHeight="1">
-      <c r="A220" s="4" t="s">
+    <row r="236" spans="1:3" ht="48" customHeight="1">
+      <c r="A236" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B235),",",", ")</f>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C10.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C10_Rate, Loan_C10_Index, Loan_C10_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C10_Options, )</v>
+      </c>
+      <c r="B236" s="14"/>
+      <c r="C236" s="14"/>
+    </row>
+    <row r="238" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A238" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B220" s="10" cm="1" t="str">
-        <f t="array" ref="B220">_xll.QS.TRADE.CREATE("Loan.C10.Trade",Loan_C10_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C220" s="7" t="s">
+      <c r="B238" s="10" cm="1" t="str">
+        <f t="array" ref="B238">_xll.QS.TRADE.CREATE("Loan.C10.Trade",Loan_C10_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C238" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="34" customHeight="1">
-      <c r="A221" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B220),",",", ")</f>
+    <row r="239" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A239" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B238),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C10.Trade", Loan_C10_Instrument, Loan_ValuationDate, Loan_Side)</v>
       </c>
-      <c r="B221" s="14"/>
-      <c r="C221" s="14"/>
-    </row>
-    <row r="223" spans="1:3" ht="38" customHeight="1">
-      <c r="A223" s="4" t="s">
+      <c r="B239" s="14"/>
+      <c r="C239" s="14"/>
+    </row>
+    <row r="241" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A241" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B223" s="10">
+      <c r="B241" s="10">
         <f>IF(Loan_C10_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
-      <c r="C223" s="7" t="s">
+      <c r="C241" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="34" customHeight="1">
-      <c r="A224" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B223),",",", ")</f>
+    <row r="242" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A242" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B241),",",", ")</f>
         <v>=IF(Loan_C10_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
       </c>
-      <c r="B224" s="14"/>
-      <c r="C224" s="14"/>
-    </row>
-    <row r="226" spans="1:3" ht="38" customHeight="1">
-      <c r="A226" s="4" t="s">
+      <c r="B242" s="14"/>
+      <c r="C242" s="14"/>
+    </row>
+    <row r="244" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A244" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B226" s="10" cm="1" t="str">
-        <f t="array" ref="B226">_xll.QS.EVALUATE("Loan.C10.Result",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Requests)</f>
-        <v/>
-      </c>
-      <c r="C226" s="7" t="s">
+      <c r="B244" s="10" cm="1" t="str">
+        <f t="array" ref="B244">_xll.QS.EVALUATE("Loan.C10.Result",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C244" s="7" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="34" customHeight="1">
-      <c r="A227" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B226),",",", ")</f>
+    <row r="245" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A245" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B244),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C10.Result", Loan_C10_Pricer, Loan_C10_Trade, Loan_Context, Loan_Requests)</v>
       </c>
-      <c r="B227" s="14"/>
-      <c r="C227" s="14"/>
-    </row>
-    <row r="229" spans="1:3" ht="38" customHeight="1">
-      <c r="A229" s="4" t="s">
+      <c r="B245" s="14"/>
+      <c r="C245" s="14"/>
+    </row>
+    <row r="247" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A247" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B229" s="10" cm="1" t="str">
-        <f t="array" ref="B229">_xll.QS.EVALUATE("Loan.C10.Fair0",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Request0)</f>
-        <v/>
-      </c>
-      <c r="C229" s="7" t="s">
+      <c r="B247" s="10" cm="1" t="str">
+        <f t="array" ref="B247">_xll.QS.EVALUATE("Loan.C10.Fair0",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C247" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="34" customHeight="1">
-      <c r="A230" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B229),",",", ")</f>
+    <row r="248" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A248" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B247),",",", ")</f>
         <v>=QS.EVALUATE("Loan.C10.Fair0", Loan_C10_Pricer, Loan_C10_Trade, Loan_Context, Loan_Request0)</v>
       </c>
-      <c r="B230" s="14"/>
-      <c r="C230" s="14"/>
-    </row>
-    <row r="234" spans="1:3" ht="24" customHeight="1">
-      <c r="A234" s="4" t="s">
+      <c r="B248" s="14"/>
+      <c r="C248" s="14"/>
+    </row>
+    <row r="252" spans="1:3" ht="24" customHeight="1">
+      <c r="A252" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-    </row>
-    <row r="235" spans="1:3" ht="24" customHeight="1">
-      <c r="A235" s="6" t="s">
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
+    </row>
+    <row r="253" spans="1:3" ht="24" customHeight="1">
+      <c r="A253" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="38" customHeight="1">
-      <c r="A237" s="4" t="s">
+    <row r="255" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A255" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B237" s="10" cm="1" t="str">
-        <f t="array" ref="B237">_xll.QS.INSTRUMENT.LOAN("Loan.C11.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C11_Rate,Loan_C11_Index,Loan_C11_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C11_Coupons)</f>
-        <v/>
-      </c>
-      <c r="C237" s="7" t="s">
+      <c r="B255" s="10" cm="1" t="str">
+        <f t="array" ref="B255">_xll.QS.INSTRUMENT.LOAN("Loan.C11.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C11_Rate,Loan_C11_Index,Loan_C11_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C11_Coupons)</f>
+        <v/>
+      </c>
+      <c r="C255" s="7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="48" customHeight="1">
-      <c r="A238" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B237),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C11.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C11_Rate, Loan_C11_Index, Loan_C11_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C11_Coupons)</v>
-      </c>
-      <c r="B238" s="14"/>
-      <c r="C238" s="14"/>
-    </row>
-    <row r="240" spans="1:3" ht="38" customHeight="1">
-      <c r="A240" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B240" s="10" cm="1" t="str">
-        <f t="array" ref="B240">_xll.QS.TRADE.CREATE("Loan.C11.Trade",Loan_C11_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="34" customHeight="1">
-      <c r="A241" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B240),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C11.Trade", Loan_C11_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B241" s="14"/>
-      <c r="C241" s="14"/>
-    </row>
-    <row r="243" spans="1:3" ht="38" customHeight="1">
-      <c r="A243" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B243" s="10">
-        <f>IF(Loan_C11_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
-        <v/>
-      </c>
-      <c r="C243" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="34" customHeight="1">
-      <c r="A244" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B243),",",", ")</f>
-        <v>=IF(Loan_C11_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
-      </c>
-      <c r="B244" s="14"/>
-      <c r="C244" s="14"/>
-    </row>
-    <row r="246" spans="1:3" ht="38" customHeight="1">
-      <c r="A246" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B246" s="10" cm="1" t="str">
-        <f t="array" ref="B246">_xll.QS.EVALUATE("Loan.C11.Result",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Requests)</f>
-        <v/>
-      </c>
-      <c r="C246" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="34" customHeight="1">
-      <c r="A247" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B246),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Result", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Requests)</v>
-      </c>
-      <c r="B247" s="14"/>
-      <c r="C247" s="14"/>
-    </row>
-    <row r="249" spans="1:3" ht="38" customHeight="1">
-      <c r="A249" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B249" s="10" cm="1" t="str">
-        <f t="array" ref="B249">_xll.QS.EVALUATE("Loan.C11.Fair0",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request0)</f>
-        <v/>
-      </c>
-      <c r="C249" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="34" customHeight="1">
-      <c r="A250" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B249),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair0", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request0)</v>
-      </c>
-      <c r="B250" s="14"/>
-      <c r="C250" s="14"/>
-    </row>
-    <row r="252" spans="1:3" ht="38" customHeight="1">
-      <c r="A252" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B252" s="10" cm="1" t="str">
-        <f t="array" ref="B252">_xll.QS.EVALUATE("Loan.C11.Fair1",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request1)</f>
-        <v/>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="34" customHeight="1">
-      <c r="A253" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B252),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair1", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request1)</v>
-      </c>
-      <c r="B253" s="14"/>
-      <c r="C253" s="14"/>
-    </row>
-    <row r="255" spans="1:3" ht="38" customHeight="1">
-      <c r="A255" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B255" s="10" cm="1" t="str">
-        <f t="array" ref="B255">_xll.QS.EVALUATE("Loan.C11.Fair2",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request2)</f>
-        <v/>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="34" customHeight="1">
+    <row r="256" spans="1:3" ht="48" customHeight="1">
       <c r="A256" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B255),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair2", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request2)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C11.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C11_Rate, Loan_C11_Index, Loan_C11_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C11_Coupons)</v>
       </c>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
     </row>
-    <row r="260" spans="1:3" ht="24" customHeight="1">
-      <c r="A260" s="4" t="s">
+    <row r="258" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A258" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B258" s="10" cm="1" t="str">
+        <f t="array" ref="B258">_xll.QS.TRADE.CREATE("Loan.C11.Trade",Loan_C11_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A259" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B258),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Loan.C11.Trade", Loan_C11_Instrument, Loan_ValuationDate, Loan_Side)</v>
+      </c>
+      <c r="B259" s="14"/>
+      <c r="C259" s="14"/>
+    </row>
+    <row r="261" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A261" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B261" s="10">
+        <f>IF(Loan_C11_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v/>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A262" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B261),",",", ")</f>
+        <v>=IF(Loan_C11_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+      </c>
+      <c r="B262" s="14"/>
+      <c r="C262" s="14"/>
+    </row>
+    <row r="264" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A264" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B264" s="10" cm="1" t="str">
+        <f t="array" ref="B264">_xll.QS.EVALUATE("Loan.C11.Result",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A265" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B264),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C11.Result", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B265" s="14"/>
+      <c r="C265" s="14"/>
+    </row>
+    <row r="267" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A267" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B267" s="10" cm="1" t="str">
+        <f t="array" ref="B267">_xll.QS.EVALUATE("Loan.C11.Fair0",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A268" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B267),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C11.Fair0", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B268" s="14"/>
+      <c r="C268" s="14"/>
+    </row>
+    <row r="270" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A270" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B270" s="10" cm="1" t="str">
+        <f t="array" ref="B270">_xll.QS.EVALUATE("Loan.C11.Fair1",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request1)</f>
+        <v/>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A271" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B270),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C11.Fair1", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request1)</v>
+      </c>
+      <c r="B271" s="14"/>
+      <c r="C271" s="14"/>
+    </row>
+    <row r="273" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A273" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B273" s="10" cm="1" t="str">
+        <f t="array" ref="B273">_xll.QS.EVALUATE("Loan.C11.Fair2",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request2)</f>
+        <v/>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A274" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B273),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C11.Fair2", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request2)</v>
+      </c>
+      <c r="B274" s="14"/>
+      <c r="C274" s="14"/>
+    </row>
+    <row r="278" spans="1:3" ht="24" customHeight="1">
+      <c r="A278" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-    </row>
-    <row r="261" spans="1:3" ht="24" customHeight="1">
-      <c r="A261" s="6" t="s">
+      <c r="B278" s="4"/>
+      <c r="C278" s="4"/>
+    </row>
+    <row r="279" spans="1:3" ht="24" customHeight="1">
+      <c r="A279" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="38" customHeight="1">
-      <c r="A263" s="4" t="s">
+    <row r="281" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A281" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B263" s="10" cm="1" t="str">
-        <f t="array" ref="B263">_xll.QS.INSTRUMENT.LOAN("Loan.C12.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C12_Rate,Loan_C12_Index,Loan_C12_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C12_Coupons)</f>
-        <v/>
-      </c>
-      <c r="C263" s="7" t="s">
+      <c r="B281" s="10" cm="1" t="str">
+        <f t="array" ref="B281">_xll.QS.INSTRUMENT.LOAN("Loan.C12.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C12_Rate,Loan_C12_Index,Loan_C12_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C12_Coupons)</f>
+        <v/>
+      </c>
+      <c r="C281" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="48" customHeight="1">
-      <c r="A264" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B263),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C12.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C12_Rate, Loan_C12_Index, Loan_C12_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C12_Coupons)</v>
-      </c>
-      <c r="B264" s="14"/>
-      <c r="C264" s="14"/>
-    </row>
-    <row r="266" spans="1:3" ht="38" customHeight="1">
-      <c r="A266" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B266" s="10" cm="1" t="str">
-        <f t="array" ref="B266">_xll.QS.TRADE.CREATE("Loan.C12.Trade",Loan_C12_Instrument,Loan_ValuationDate,Loan_Side)</f>
-        <v/>
-      </c>
-      <c r="C266" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="34" customHeight="1">
-      <c r="A267" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B266),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Loan.C12.Trade", Loan_C12_Instrument, Loan_ValuationDate, Loan_Side)</v>
-      </c>
-      <c r="B267" s="14"/>
-      <c r="C267" s="14"/>
-    </row>
-    <row r="269" spans="1:3" ht="38" customHeight="1">
-      <c r="A269" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B269" s="10">
-        <f>IF(Loan_C12_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
-        <v/>
-      </c>
-      <c r="C269" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" ht="34" customHeight="1">
-      <c r="A270" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B269),",",", ")</f>
-        <v>=IF(Loan_C12_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
-      </c>
-      <c r="B270" s="14"/>
-      <c r="C270" s="14"/>
-    </row>
-    <row r="272" spans="1:3" ht="38" customHeight="1">
-      <c r="A272" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B272" s="10" cm="1" t="str">
-        <f t="array" ref="B272">_xll.QS.EVALUATE("Loan.C12.Result",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Requests)</f>
-        <v/>
-      </c>
-      <c r="C272" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" ht="34" customHeight="1">
-      <c r="A273" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B272),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Result", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Requests)</v>
-      </c>
-      <c r="B273" s="14"/>
-      <c r="C273" s="14"/>
-    </row>
-    <row r="275" spans="1:3" ht="38" customHeight="1">
-      <c r="A275" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B275" s="10" cm="1" t="str">
-        <f t="array" ref="B275">_xll.QS.EVALUATE("Loan.C12.Fair0",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request0)</f>
-        <v/>
-      </c>
-      <c r="C275" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="34" customHeight="1">
-      <c r="A276" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B275),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair0", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request0)</v>
-      </c>
-      <c r="B276" s="14"/>
-      <c r="C276" s="14"/>
-    </row>
-    <row r="278" spans="1:3" ht="38" customHeight="1">
-      <c r="A278" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B278" s="10" cm="1" t="str">
-        <f t="array" ref="B278">_xll.QS.EVALUATE("Loan.C12.Fair1",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request1)</f>
-        <v/>
-      </c>
-      <c r="C278" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" ht="34" customHeight="1">
-      <c r="A279" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B278),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair1", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request1)</v>
-      </c>
-      <c r="B279" s="14"/>
-      <c r="C279" s="14"/>
-    </row>
-    <row r="281" spans="1:3" ht="38" customHeight="1">
-      <c r="A281" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B281" s="10" cm="1" t="str">
-        <f t="array" ref="B281">_xll.QS.EVALUATE("Loan.C12.Fair2",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request2)</f>
-        <v/>
-      </c>
-      <c r="C281" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" ht="34" customHeight="1">
+    <row r="282" spans="1:3" ht="48" customHeight="1">
       <c r="A282" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B281),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair2", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request2)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C12.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C12_Rate, Loan_C12_Index, Loan_C12_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C12_Coupons)</v>
       </c>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
     </row>
-    <row r="286" spans="1:3" ht="36" customHeight="1">
-      <c r="A286" s="5" t="s">
+    <row r="284" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A284" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B284" s="10" cm="1" t="str">
+        <f t="array" ref="B284">_xll.QS.TRADE.CREATE("Loan.C12.Trade",Loan_C12_Instrument,Loan_ValuationDate,Loan_Side)</f>
+        <v/>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A285" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B284),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Loan.C12.Trade", Loan_C12_Instrument, Loan_ValuationDate, Loan_Side)</v>
+      </c>
+      <c r="B285" s="14"/>
+      <c r="C285" s="14"/>
+    </row>
+    <row r="287" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A287" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B287" s="10">
+        <f>IF(Loan_C12_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
+        <v/>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A288" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B287),",",", ")</f>
+        <v>=IF(Loan_C12_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
+      </c>
+      <c r="B288" s="14"/>
+      <c r="C288" s="14"/>
+    </row>
+    <row r="290" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A290" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B290" s="10" cm="1" t="str">
+        <f t="array" ref="B290">_xll.QS.EVALUATE("Loan.C12.Result",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Requests)</f>
+        <v/>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A291" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B290),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C12.Result", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Requests)</v>
+      </c>
+      <c r="B291" s="14"/>
+      <c r="C291" s="14"/>
+    </row>
+    <row r="293" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A293" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B293" s="10" cm="1" t="str">
+        <f t="array" ref="B293">_xll.QS.EVALUATE("Loan.C12.Fair0",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request0)</f>
+        <v/>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A294" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B293),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C12.Fair0", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request0)</v>
+      </c>
+      <c r="B294" s="14"/>
+      <c r="C294" s="14"/>
+    </row>
+    <row r="296" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A296" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B296" s="10" cm="1" t="str">
+        <f t="array" ref="B296">_xll.QS.EVALUATE("Loan.C12.Fair1",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request1)</f>
+        <v/>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A297" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B296),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C12.Fair1", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request1)</v>
+      </c>
+      <c r="B297" s="14"/>
+      <c r="C297" s="14"/>
+    </row>
+    <row r="299" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A299" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B299" s="10" cm="1" t="str">
+        <f t="array" ref="B299">_xll.QS.EVALUATE("Loan.C12.Fair2",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request2)</f>
+        <v/>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A300" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B299),",",", ")</f>
+        <v>=QS.EVALUATE("Loan.C12.Fair2", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request2)</v>
+      </c>
+      <c r="B300" s="14"/>
+      <c r="C300" s="14"/>
+    </row>
+    <row r="304" spans="1:3" ht="36" customHeight="1">
+      <c r="A304" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C304" s="5"/>
+    </row>
+    <row r="305" spans="1:3" ht="24" customHeight="1">
+      <c r="A305" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B305" s="10">
+        <f>Loan_C01_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="24" customHeight="1">
+      <c r="A306" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B306" s="10">
+        <f>Loan_C02_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="24" customHeight="1">
+      <c r="A307" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B307" s="10">
+        <f>Loan_C03_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="24" customHeight="1">
+      <c r="A308" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B308" s="10">
+        <f>Loan_C04_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="24" customHeight="1">
+      <c r="A309" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B309" s="10">
+        <f>Loan_C05_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="24" customHeight="1">
+      <c r="A310" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B310" s="10">
+        <f>Loan_C06_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="24" customHeight="1">
+      <c r="A311" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B311" s="10">
+        <f>Loan_C07_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="24" customHeight="1">
+      <c r="A312" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B312" s="10">
+        <f>Loan_C08_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="24" customHeight="1">
+      <c r="A313" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B313" s="10">
+        <f>Loan_C09_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="24" customHeight="1">
+      <c r="A314" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B314" s="10">
+        <f>Loan_C10_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="24" customHeight="1">
+      <c r="A315" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B286" s="5" t="s">
+      <c r="B315" s="10">
+        <f>Loan_C11_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="24" customHeight="1">
+      <c r="A316" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C286" s="5"/>
-    </row>
-    <row r="287" spans="1:3" ht="24" customHeight="1">
-      <c r="A287" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B287" s="10">
-        <f>Loan_C01_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:3" ht="24" customHeight="1">
-      <c r="A288" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B288" s="10">
-        <f>Loan_C02_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:3" ht="24" customHeight="1">
-      <c r="A289" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B289" s="10">
-        <f>Loan_C03_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:3" ht="24" customHeight="1">
-      <c r="A290" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B290" s="10">
-        <f>Loan_C04_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:3" ht="24" customHeight="1">
-      <c r="A291" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B291" s="10">
-        <f>Loan_C05_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:3" ht="24" customHeight="1">
-      <c r="A292" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B292" s="10">
-        <f>Loan_C06_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:3" ht="24" customHeight="1">
-      <c r="A293" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B293" s="10">
-        <f>Loan_C07_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="24" customHeight="1">
-      <c r="A294" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B294" s="10">
-        <f>Loan_C08_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="24" customHeight="1">
-      <c r="A295" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B295" s="10">
-        <f>Loan_C09_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:3" ht="24" customHeight="1">
-      <c r="A296" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B296" s="10">
-        <f>Loan_C10_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="24" customHeight="1">
-      <c r="A297" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B297" s="10">
-        <f>Loan_C11_Result</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:3" ht="24" customHeight="1">
-      <c r="A298" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B298" s="10">
+      <c r="B316" s="10">
         <f>Loan_C12_Result</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="38" customHeight="1">
-      <c r="A301" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B301" s="10">
+    <row r="319" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A319" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B319" s="10">
         <f>INDEX(Loan_ResultHandles,MATCH(Loan_SelectedCase,Loan_CaseNames,0))</f>
         <v/>
       </c>
-      <c r="C301" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" ht="34" customHeight="1">
-      <c r="A302" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B301),",",", ")</f>
+      <c r="C319" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A320" s="14" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B319),",",", ")</f>
         <v>=INDEX(Loan_ResultHandles, MATCH(Loan_SelectedCase, Loan_CaseNames, 0))</v>
       </c>
-      <c r="B302" s="14"/>
-      <c r="C302" s="14"/>
+      <c r="B320" s="14"/>
+      <c r="C320" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="94">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A8:C8"/>
@@ -7113,65 +7323,71 @@
     <mergeCell ref="A84:C84"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A97:C97"/>
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A154:C154"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="A163:C163"/>
     <mergeCell ref="A167:C167"/>
     <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A176:C176"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A186:C186"/>
     <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A218:C218"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A224:C224"/>
-    <mergeCell ref="A227:C227"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A234:C234"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A241:C241"/>
-    <mergeCell ref="A244:C244"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A250:C250"/>
-    <mergeCell ref="A253:C253"/>
+    <mergeCell ref="A193:C193"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A209:C209"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A216:C216"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A225:C225"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A233:C233"/>
+    <mergeCell ref="A236:C236"/>
+    <mergeCell ref="A239:C239"/>
+    <mergeCell ref="A242:C242"/>
+    <mergeCell ref="A245:C245"/>
+    <mergeCell ref="A248:C248"/>
+    <mergeCell ref="A252:C252"/>
     <mergeCell ref="A256:C256"/>
-    <mergeCell ref="A260:C260"/>
-    <mergeCell ref="A264:C264"/>
-    <mergeCell ref="A267:C267"/>
-    <mergeCell ref="A270:C270"/>
-    <mergeCell ref="A273:C273"/>
-    <mergeCell ref="A276:C276"/>
-    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A259:C259"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A265:C265"/>
+    <mergeCell ref="A268:C268"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A274:C274"/>
+    <mergeCell ref="A278:C278"/>
     <mergeCell ref="A282:C282"/>
-    <mergeCell ref="A302:C302"/>
+    <mergeCell ref="A285:C285"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A291:C291"/>
+    <mergeCell ref="A294:C294"/>
+    <mergeCell ref="A297:C297"/>
+    <mergeCell ref="A300:C300"/>
+    <mergeCell ref="A320:C320"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -7179,15 +7395,15 @@
     <hyperlink ref="A35" location="'2 Cases'!A6" display="Edit these case inputs →"/>
     <hyperlink ref="A55" location="'2 Cases'!A16" display="Edit these case inputs →"/>
     <hyperlink ref="A75" location="'2 Cases'!A26" display="Edit these case inputs →"/>
-    <hyperlink ref="A95" location="'2 Cases'!A36" display="Edit these case inputs →"/>
-    <hyperlink ref="A115" location="'2 Cases'!A46" display="Edit these case inputs →"/>
-    <hyperlink ref="A138" location="'2 Cases'!A60" display="Edit these case inputs →"/>
-    <hyperlink ref="A155" location="'2 Cases'!A72" display="Edit these case inputs →"/>
-    <hyperlink ref="A175" location="'2 Cases'!A82" display="Edit these case inputs →"/>
-    <hyperlink ref="A195" location="'2 Cases'!A93" display="Edit these case inputs →"/>
-    <hyperlink ref="A215" location="'2 Cases'!A103" display="Edit these case inputs →"/>
-    <hyperlink ref="A235" location="'2 Cases'!A113" display="Edit these case inputs →"/>
-    <hyperlink ref="A261" location="'2 Cases'!A127" display="Edit these case inputs →"/>
+    <hyperlink ref="A98" location="'2 Cases'!A36" display="Edit these case inputs →"/>
+    <hyperlink ref="A121" location="'2 Cases'!A46" display="Edit these case inputs →"/>
+    <hyperlink ref="A144" location="'2 Cases'!A60" display="Edit these case inputs →"/>
+    <hyperlink ref="A164" location="'2 Cases'!A72" display="Edit these case inputs →"/>
+    <hyperlink ref="A187" location="'2 Cases'!A82" display="Edit these case inputs →"/>
+    <hyperlink ref="A210" location="'2 Cases'!A93" display="Edit these case inputs →"/>
+    <hyperlink ref="A230" location="'2 Cases'!A103" display="Edit these case inputs →"/>
+    <hyperlink ref="A253" location="'2 Cases'!A113" display="Edit these case inputs →"/>
+    <hyperlink ref="A279" location="'2 Cases'!A127" display="Edit these case inputs →"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -7213,9 +7429,9 @@
     <col min="7" max="8" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38" customHeight="1">
+    <row r="1" spans="1:8" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7227,7 +7443,7 @@
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7252,36 +7468,36 @@
         <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="34" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="33.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
@@ -7300,13 +7516,13 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -7325,15 +7541,15 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="33.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B9" s="15" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.RESULT.VALUE(Loan_C03_Result)</f>
@@ -7350,15 +7566,15 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="33.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B10" s="15" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.RESULT.VALUE(Loan_C04_Result)</f>
@@ -7375,15 +7591,15 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="33.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B11" s="15" cm="1" t="str">
         <f t="array" ref="B11">_xll.QS.RESULT.VALUE(Loan_C05_Result)</f>
@@ -7403,15 +7619,15 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B12" s="15" cm="1" t="str">
         <f t="array" ref="B12">_xll.QS.RESULT.VALUE(Loan_C06_Result)</f>
@@ -7422,20 +7638,20 @@
         <v/>
       </c>
       <c r="D12" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="33.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B13" s="15" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.RESULT.VALUE(Loan_C07_Result)</f>
@@ -7452,15 +7668,15 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="33.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B14" s="15" cm="1" t="str">
         <f t="array" ref="B14">_xll.QS.RESULT.VALUE(Loan_C08_Result)</f>
@@ -7477,15 +7693,15 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="33.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B15" s="15" cm="1" t="str">
         <f t="array" ref="B15">_xll.QS.RESULT.VALUE(Loan_C09_Result)</f>
@@ -7502,15 +7718,15 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="33.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B16" s="15" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.RESULT.VALUE(Loan_C10_Result)</f>
@@ -7527,15 +7743,15 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="33.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B17" s="15" cm="1" t="str">
         <f t="array" ref="B17">_xll.QS.RESULT.VALUE(Loan_C11_Result)</f>
@@ -7558,15 +7774,15 @@
         <v/>
       </c>
       <c r="G17" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="34" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="33.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B18" s="15" cm="1" t="str">
         <f t="array" ref="B18">_xll.QS.RESULT.VALUE(Loan_C12_Result)</f>
@@ -7589,21 +7805,21 @@
         <v/>
       </c>
       <c r="G18" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -7617,7 +7833,7 @@
     </row>
     <row r="26" spans="1:8" ht="24" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -7669,23 +7885,23 @@
     <hyperlink ref="G9" location="'2 Cases'!A26" display="Edit →"/>
     <hyperlink ref="H9" location="'4 Build'!A74" display="Build →"/>
     <hyperlink ref="G10" location="'2 Cases'!A36" display="Edit →"/>
-    <hyperlink ref="H10" location="'4 Build'!A94" display="Build →"/>
+    <hyperlink ref="H10" location="'4 Build'!A97" display="Build →"/>
     <hyperlink ref="G11" location="'2 Cases'!A46" display="Edit →"/>
-    <hyperlink ref="H11" location="'4 Build'!A114" display="Build →"/>
+    <hyperlink ref="H11" location="'4 Build'!A120" display="Build →"/>
     <hyperlink ref="G12" location="'2 Cases'!A60" display="Edit →"/>
-    <hyperlink ref="H12" location="'4 Build'!A137" display="Build →"/>
+    <hyperlink ref="H12" location="'4 Build'!A143" display="Build →"/>
     <hyperlink ref="G13" location="'2 Cases'!A72" display="Edit →"/>
-    <hyperlink ref="H13" location="'4 Build'!A154" display="Build →"/>
+    <hyperlink ref="H13" location="'4 Build'!A163" display="Build →"/>
     <hyperlink ref="G14" location="'2 Cases'!A82" display="Edit →"/>
-    <hyperlink ref="H14" location="'4 Build'!A174" display="Build →"/>
+    <hyperlink ref="H14" location="'4 Build'!A186" display="Build →"/>
     <hyperlink ref="G15" location="'2 Cases'!A93" display="Edit →"/>
-    <hyperlink ref="H15" location="'4 Build'!A194" display="Build →"/>
+    <hyperlink ref="H15" location="'4 Build'!A209" display="Build →"/>
     <hyperlink ref="G16" location="'2 Cases'!A103" display="Edit →"/>
-    <hyperlink ref="H16" location="'4 Build'!A214" display="Build →"/>
+    <hyperlink ref="H16" location="'4 Build'!A229" display="Build →"/>
     <hyperlink ref="G17" location="'2 Cases'!A113" display="Edit →"/>
-    <hyperlink ref="H17" location="'4 Build'!A234" display="Build →"/>
+    <hyperlink ref="H17" location="'4 Build'!A252" display="Build →"/>
     <hyperlink ref="G18" location="'2 Cases'!A127" display="Edit →"/>
-    <hyperlink ref="H18" location="'4 Build'!A260" display="Build →"/>
+    <hyperlink ref="H18" location="'4 Build'!A278" display="Build →"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -7714,9 +7930,9 @@
     <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38" customHeight="1">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7729,7 +7945,7 @@
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7756,19 +7972,19 @@
         <v>42</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B6" s="9">
         <f>Loan_SelectedCase</f>
         <v/>
       </c>
       <c r="C6" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1">
@@ -7809,16 +8025,16 @@
     <col min="3" max="3" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7833,19 +8049,19 @@
         <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="24" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B6" s="9">
         <f>Loan_SelectedCase</f>
         <v/>
       </c>
       <c r="C6" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1">
@@ -7887,9 +8103,9 @@
     <col min="5" max="6" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38" customHeight="1">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7899,7 +8115,7 @@
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7922,7 +8138,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7938,7 +8154,7 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -7954,7 +8170,7 @@
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -7970,7 +8186,7 @@
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -55,7 +55,7 @@
     <definedName name="Loan_C03_Rate">'2 Cases'!$B$28</definedName>
     <definedName name="Loan_C03_Repayment">'2 Cases'!$F$28</definedName>
     <definedName name="Loan_C03_Result">'4 Build'!$B$89</definedName>
-    <definedName name="Loan_C03_Settings">'2 Cases'!$A$31:$B$32</definedName>
+    <definedName name="Loan_C03_Setting_balloonfraction">'2 Cases'!$B$32</definedName>
     <definedName name="Loan_C03_Trade">'4 Build'!$B$83</definedName>
     <definedName name="Loan_C04_Discount">'2 Cases'!$B$39</definedName>
     <definedName name="Loan_C04_Fair0">'4 Build'!$B$115</definedName>
@@ -69,9 +69,11 @@
     <definedName name="Loan_C04_Rate">'2 Cases'!$B$38</definedName>
     <definedName name="Loan_C04_Repayment">'2 Cases'!$F$38</definedName>
     <definedName name="Loan_C04_Result">'4 Build'!$B$112</definedName>
-    <definedName name="Loan_C04_Settings">'2 Cases'!$A$41:$B$42</definedName>
+    <definedName name="Loan_C04_Setting_amortizationrate">'2 Cases'!$B$42</definedName>
     <definedName name="Loan_C04_Trade">'4 Build'!$B$106</definedName>
-    <definedName name="Loan_C05_Coupons">'2 Cases'!$D$51:$F$53</definedName>
+    <definedName name="Loan_C05_CouponIndices">'2 Cases'!$F$52:$F$53</definedName>
+    <definedName name="Loan_C05_CouponPeriods">'2 Cases'!$D$52:$D$53</definedName>
+    <definedName name="Loan_C05_CouponRates">'2 Cases'!$E$52:$E$53</definedName>
     <definedName name="Loan_C05_Discount">'2 Cases'!$B$49</definedName>
     <definedName name="Loan_C05_Fair0">'4 Build'!$B$135</definedName>
     <definedName name="Loan_C05_Fair1">'4 Build'!$B$138</definedName>
@@ -96,7 +98,9 @@
     <definedName name="Loan_C06_Rate">'2 Cases'!$B$62</definedName>
     <definedName name="Loan_C06_Repayment">'2 Cases'!$F$62</definedName>
     <definedName name="Loan_C06_Result">'4 Build'!$B$158</definedName>
-    <definedName name="Loan_C06_Settings">'2 Cases'!$A$65:$B$68</definedName>
+    <definedName name="Loan_C06_Setting_amortizationrate">'2 Cases'!$B$66</definedName>
+    <definedName name="Loan_C06_Setting_cap">'2 Cases'!$B$68</definedName>
+    <definedName name="Loan_C06_Setting_floor">'2 Cases'!$B$67</definedName>
     <definedName name="Loan_C06_Trade">'4 Build'!$B$152</definedName>
     <definedName name="Loan_C07_Discount">'2 Cases'!$B$75</definedName>
     <definedName name="Loan_C07_Fair0">'4 Build'!$B$181</definedName>
@@ -110,7 +114,7 @@
     <definedName name="Loan_C07_Rate">'2 Cases'!$B$74</definedName>
     <definedName name="Loan_C07_Repayment">'2 Cases'!$F$74</definedName>
     <definedName name="Loan_C07_Result">'4 Build'!$B$178</definedName>
-    <definedName name="Loan_C07_Settings">'2 Cases'!$A$77:$B$78</definedName>
+    <definedName name="Loan_C07_Setting_annualcpr">'2 Cases'!$B$78</definedName>
     <definedName name="Loan_C07_Trade">'4 Build'!$B$172</definedName>
     <definedName name="Loan_C08_Discount">'2 Cases'!$B$85</definedName>
     <definedName name="Loan_C08_Fair0">'4 Build'!$B$204</definedName>
@@ -124,7 +128,8 @@
     <definedName name="Loan_C08_Rate">'2 Cases'!$B$84</definedName>
     <definedName name="Loan_C08_Repayment">'2 Cases'!$F$84</definedName>
     <definedName name="Loan_C08_Result">'4 Build'!$B$201</definedName>
-    <definedName name="Loan_C08_Settings">'2 Cases'!$A$87:$B$89</definedName>
+    <definedName name="Loan_C08_Setting_creditindex">'2 Cases'!$B$88</definedName>
+    <definedName name="Loan_C08_Setting_recovery">'2 Cases'!$B$89</definedName>
     <definedName name="Loan_C08_Trade">'4 Build'!$B$195</definedName>
     <definedName name="Loan_C09_Discount">'2 Cases'!$B$96</definedName>
     <definedName name="Loan_C09_Fair0">'4 Build'!$B$224</definedName>
@@ -150,9 +155,11 @@
     <definedName name="Loan_C10_Rate">'2 Cases'!$B$105</definedName>
     <definedName name="Loan_C10_Repayment">'2 Cases'!$F$105</definedName>
     <definedName name="Loan_C10_Result">'4 Build'!$B$244</definedName>
-    <definedName name="Loan_C10_Settings">'2 Cases'!$A$108:$B$109</definedName>
+    <definedName name="Loan_C10_Setting_amortizationrate">'2 Cases'!$B$109</definedName>
     <definedName name="Loan_C10_Trade">'4 Build'!$B$238</definedName>
-    <definedName name="Loan_C11_Coupons">'2 Cases'!$D$118:$F$121</definedName>
+    <definedName name="Loan_C11_CouponIndices">'2 Cases'!$F$119:$F$121</definedName>
+    <definedName name="Loan_C11_CouponPeriods">'2 Cases'!$D$119:$D$121</definedName>
+    <definedName name="Loan_C11_CouponRates">'2 Cases'!$E$119:$E$121</definedName>
     <definedName name="Loan_C11_Discount">'2 Cases'!$B$116</definedName>
     <definedName name="Loan_C11_Fair0">'4 Build'!$B$267</definedName>
     <definedName name="Loan_C11_Fair1">'4 Build'!$B$270</definedName>
@@ -169,7 +176,9 @@
     <definedName name="Loan_C11_Repayment">'2 Cases'!$F$115</definedName>
     <definedName name="Loan_C11_Result">'4 Build'!$B$264</definedName>
     <definedName name="Loan_C11_Trade">'4 Build'!$B$258</definedName>
-    <definedName name="Loan_C12_Coupons">'2 Cases'!$D$132:$F$135</definedName>
+    <definedName name="Loan_C12_CouponIndices">'2 Cases'!$F$133:$F$135</definedName>
+    <definedName name="Loan_C12_CouponPeriods">'2 Cases'!$D$133:$D$135</definedName>
+    <definedName name="Loan_C12_CouponRates">'2 Cases'!$E$133:$E$135</definedName>
     <definedName name="Loan_C12_Discount">'2 Cases'!$B$130</definedName>
     <definedName name="Loan_C12_Fair0">'4 Build'!$B$293</definedName>
     <definedName name="Loan_C12_Fair1">'4 Build'!$B$296</definedName>
@@ -5628,7 +5637,7 @@
         <v>206</v>
       </c>
       <c r="B37" s="10" cm="1" t="str">
-        <f t="array" ref="B37">_xll.QS.INSTRUMENT.LOAN("Loan.C01.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C01_Rate,Loan_C01_Index,Loan_C01_Repayment,Loan_Frequency,Loan_DayCounter,,)</f>
+        <f t="array" ref="B37">_xll.QS.INSTRUMENT.LOAN("Loan.C01.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C01_Rate,Loan_C01_Index,Loan_C01_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="s">
@@ -5638,7 +5647,7 @@
     <row r="38" spans="1:3" ht="48" customHeight="1">
       <c r="A38" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C01.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C01_Rate, Loan_C01_Index, Loan_C01_Repayment, Loan_Frequency, Loan_DayCounter, , )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C01.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C01_Rate, Loan_C01_Index, Loan_C01_Repayment, Loan_Frequency, Loan_DayCounter, , , , )</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -5740,7 +5749,7 @@
         <v>206</v>
       </c>
       <c r="B57" s="10" cm="1" t="str">
-        <f t="array" ref="B57">_xll.QS.INSTRUMENT.LOAN("Loan.C02.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C02_Rate,Loan_C02_Index,Loan_C02_Repayment,Loan_Frequency,Loan_DayCounter,,)</f>
+        <f t="array" ref="B57">_xll.QS.INSTRUMENT.LOAN("Loan.C02.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C02_Rate,Loan_C02_Index,Loan_C02_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
         <v/>
       </c>
       <c r="C57" s="7" t="s">
@@ -5750,7 +5759,7 @@
     <row r="58" spans="1:3" ht="48" customHeight="1">
       <c r="A58" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B57),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C02.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C02_Rate, Loan_C02_Index, Loan_C02_Repayment, Loan_Frequency, Loan_DayCounter, , )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C02.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C02_Rate, Loan_C02_Index, Loan_C02_Repayment, Loan_Frequency, Loan_DayCounter, , , , )</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -5852,7 +5861,7 @@
         <v>215</v>
       </c>
       <c r="B77" s="10" cm="1" t="str">
-        <f t="array" ref="B77">_xll.QS.LOAN.SETTINGS("Loan.C03.Options",INDEX(Loan_C03_Settings,2,2))</f>
+        <f t="array" ref="B77">_xll.QS.LOAN.SETTINGS("Loan.C03.Options",Loan_C03_Setting_balloonfraction)</f>
         <v/>
       </c>
       <c r="C77" s="7" t="s">
@@ -5862,7 +5871,7 @@
     <row r="78" spans="1:3" ht="33.75" customHeight="1">
       <c r="A78" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B77),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C03.Options", INDEX(Loan_C03_Settings, 2, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C03.Options", Loan_C03_Setting_balloonfraction)</v>
       </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -5872,7 +5881,7 @@
         <v>206</v>
       </c>
       <c r="B80" s="10" cm="1" t="str">
-        <f t="array" ref="B80">_xll.QS.INSTRUMENT.LOAN("Loan.C03.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C03_Rate,Loan_C03_Index,Loan_C03_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C03_Options,)</f>
+        <f t="array" ref="B80">_xll.QS.INSTRUMENT.LOAN("Loan.C03.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C03_Rate,Loan_C03_Index,Loan_C03_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C03_Options,,,)</f>
         <v/>
       </c>
       <c r="C80" s="7" t="s">
@@ -5882,7 +5891,7 @@
     <row r="81" spans="1:3" ht="48" customHeight="1">
       <c r="A81" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B80),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C03.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C03_Rate, Loan_C03_Index, Loan_C03_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C03_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C03.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C03_Rate, Loan_C03_Index, Loan_C03_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C03_Options, , , )</v>
       </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -5984,7 +5993,7 @@
         <v>215</v>
       </c>
       <c r="B100" s="10" cm="1" t="str">
-        <f t="array" ref="B100">_xll.QS.LOAN.SETTINGS("Loan.C04.Options",,INDEX(Loan_C04_Settings,2,2))</f>
+        <f t="array" ref="B100">_xll.QS.LOAN.SETTINGS("Loan.C04.Options",,Loan_C04_Setting_amortizationrate)</f>
         <v/>
       </c>
       <c r="C100" s="7" t="s">
@@ -5994,7 +6003,7 @@
     <row r="101" spans="1:3" ht="33.75" customHeight="1">
       <c r="A101" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C04.Options", , INDEX(Loan_C04_Settings, 2, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C04.Options", , Loan_C04_Setting_amortizationrate)</v>
       </c>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -6004,7 +6013,7 @@
         <v>206</v>
       </c>
       <c r="B103" s="10" cm="1" t="str">
-        <f t="array" ref="B103">_xll.QS.INSTRUMENT.LOAN("Loan.C04.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C04_Rate,Loan_C04_Index,Loan_C04_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C04_Options,)</f>
+        <f t="array" ref="B103">_xll.QS.INSTRUMENT.LOAN("Loan.C04.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C04_Rate,Loan_C04_Index,Loan_C04_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C04_Options,,,)</f>
         <v/>
       </c>
       <c r="C103" s="7" t="s">
@@ -6014,7 +6023,7 @@
     <row r="104" spans="1:3" ht="48" customHeight="1">
       <c r="A104" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B103),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C04.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C04_Rate, Loan_C04_Index, Loan_C04_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C04_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C04.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C04_Rate, Loan_C04_Index, Loan_C04_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C04_Options, , , )</v>
       </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -6116,7 +6125,7 @@
         <v>206</v>
       </c>
       <c r="B123" s="10" cm="1" t="str">
-        <f t="array" ref="B123">_xll.QS.INSTRUMENT.LOAN("Loan.C05.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C05_Rate,Loan_C05_Index,Loan_C05_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C05_Coupons)</f>
+        <f t="array" ref="B123">_xll.QS.INSTRUMENT.LOAN("Loan.C05.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C05_Rate,Loan_C05_Index,Loan_C05_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C05_CouponPeriods,Loan_C05_CouponRates,Loan_C05_CouponIndices)</f>
         <v/>
       </c>
       <c r="C123" s="7" t="s">
@@ -6126,7 +6135,7 @@
     <row r="124" spans="1:3" ht="48" customHeight="1">
       <c r="A124" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B123),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C05.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C05_Rate, Loan_C05_Index, Loan_C05_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C05_Coupons)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C05.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C05_Rate, Loan_C05_Index, Loan_C05_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C05_CouponPeriods, Loan_C05_CouponRates, Loan_C05_CouponIndices)</v>
       </c>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -6248,7 +6257,7 @@
         <v>215</v>
       </c>
       <c r="B146" s="10" cm="1" t="str">
-        <f t="array" ref="B146">_xll.QS.LOAN.SETTINGS("Loan.C06.Options",,INDEX(Loan_C06_Settings,2,2),,,,,,,,INDEX(Loan_C06_Settings,3,2),INDEX(Loan_C06_Settings,4,2))</f>
+        <f t="array" ref="B146">_xll.QS.LOAN.SETTINGS("Loan.C06.Options",,Loan_C06_Setting_amortizationrate,,,,,,,,Loan_C06_Setting_floor,Loan_C06_Setting_cap)</f>
         <v/>
       </c>
       <c r="C146" s="7" t="s">
@@ -6258,7 +6267,7 @@
     <row r="147" spans="1:3" ht="33.75" customHeight="1">
       <c r="A147" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B146),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C06.Options", , INDEX(Loan_C06_Settings, 2, 2), , , , , , , , INDEX(Loan_C06_Settings, 3, 2), INDEX(Loan_C06_Settings, 4, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C06.Options", , Loan_C06_Setting_amortizationrate, , , , , , , , Loan_C06_Setting_floor, Loan_C06_Setting_cap)</v>
       </c>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -6268,7 +6277,7 @@
         <v>206</v>
       </c>
       <c r="B149" s="10" cm="1" t="str">
-        <f t="array" ref="B149">_xll.QS.INSTRUMENT.LOAN("Loan.C06.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C06_Rate,Loan_C06_Index,Loan_C06_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C06_Options,)</f>
+        <f t="array" ref="B149">_xll.QS.INSTRUMENT.LOAN("Loan.C06.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C06_Rate,Loan_C06_Index,Loan_C06_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C06_Options,,,)</f>
         <v/>
       </c>
       <c r="C149" s="7" t="s">
@@ -6278,7 +6287,7 @@
     <row r="150" spans="1:3" ht="48" customHeight="1">
       <c r="A150" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B149),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C06.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C06_Rate, Loan_C06_Index, Loan_C06_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C06_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C06.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C06_Rate, Loan_C06_Index, Loan_C06_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C06_Options, , , )</v>
       </c>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -6360,7 +6369,7 @@
         <v>215</v>
       </c>
       <c r="B166" s="10" cm="1" t="str">
-        <f t="array" ref="B166">_xll.QS.LOAN.SETTINGS("Loan.C07.Options",,,,,,,,,,,,,,INDEX(Loan_C07_Settings,2,2))</f>
+        <f t="array" ref="B166">_xll.QS.LOAN.SETTINGS("Loan.C07.Options",,,,,,,,,,,,,,Loan_C07_Setting_annualcpr)</f>
         <v/>
       </c>
       <c r="C166" s="7" t="s">
@@ -6370,7 +6379,7 @@
     <row r="167" spans="1:3" ht="33.75" customHeight="1">
       <c r="A167" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B166),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C07.Options", , , , , , , , , , , , , , INDEX(Loan_C07_Settings, 2, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C07.Options", , , , , , , , , , , , , , Loan_C07_Setting_annualcpr)</v>
       </c>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -6380,7 +6389,7 @@
         <v>206</v>
       </c>
       <c r="B169" s="10" cm="1" t="str">
-        <f t="array" ref="B169">_xll.QS.INSTRUMENT.LOAN("Loan.C07.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C07_Rate,Loan_C07_Index,Loan_C07_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C07_Options,)</f>
+        <f t="array" ref="B169">_xll.QS.INSTRUMENT.LOAN("Loan.C07.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C07_Rate,Loan_C07_Index,Loan_C07_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C07_Options,,,)</f>
         <v/>
       </c>
       <c r="C169" s="7" t="s">
@@ -6390,7 +6399,7 @@
     <row r="170" spans="1:3" ht="48" customHeight="1">
       <c r="A170" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B169),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C07.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C07_Rate, Loan_C07_Index, Loan_C07_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C07_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C07.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C07_Rate, Loan_C07_Index, Loan_C07_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C07_Options, , , )</v>
       </c>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -6492,7 +6501,7 @@
         <v>215</v>
       </c>
       <c r="B189" s="10" cm="1" t="str">
-        <f t="array" ref="B189">_xll.QS.LOAN.SETTINGS("Loan.C08.Options",,,INDEX(Loan_C08_Settings,2,2),INDEX(Loan_C08_Settings,3,2))</f>
+        <f t="array" ref="B189">_xll.QS.LOAN.SETTINGS("Loan.C08.Options",,,Loan_C08_Setting_creditindex,Loan_C08_Setting_recovery)</f>
         <v/>
       </c>
       <c r="C189" s="7" t="s">
@@ -6502,7 +6511,7 @@
     <row r="190" spans="1:3" ht="33.75" customHeight="1">
       <c r="A190" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B189),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C08.Options", , , INDEX(Loan_C08_Settings, 2, 2), INDEX(Loan_C08_Settings, 3, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C08.Options", , , Loan_C08_Setting_creditindex, Loan_C08_Setting_recovery)</v>
       </c>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -6512,7 +6521,7 @@
         <v>206</v>
       </c>
       <c r="B192" s="10" cm="1" t="str">
-        <f t="array" ref="B192">_xll.QS.INSTRUMENT.LOAN("Loan.C08.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C08_Rate,Loan_C08_Index,Loan_C08_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C08_Options,)</f>
+        <f t="array" ref="B192">_xll.QS.INSTRUMENT.LOAN("Loan.C08.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C08_Rate,Loan_C08_Index,Loan_C08_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C08_Options,,,)</f>
         <v/>
       </c>
       <c r="C192" s="7" t="s">
@@ -6522,7 +6531,7 @@
     <row r="193" spans="1:3" ht="48" customHeight="1">
       <c r="A193" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B192),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C08.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C08_Rate, Loan_C08_Index, Loan_C08_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C08_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C08.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C08_Rate, Loan_C08_Index, Loan_C08_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C08_Options, , , )</v>
       </c>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -6624,7 +6633,7 @@
         <v>206</v>
       </c>
       <c r="B212" s="10" cm="1" t="str">
-        <f t="array" ref="B212">_xll.QS.INSTRUMENT.LOAN("Loan.C09.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C09_Rate,Loan_C09_Index,Loan_C09_Repayment,Loan_Frequency,Loan_DayCounter,,)</f>
+        <f t="array" ref="B212">_xll.QS.INSTRUMENT.LOAN("Loan.C09.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C09_Rate,Loan_C09_Index,Loan_C09_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
         <v/>
       </c>
       <c r="C212" s="7" t="s">
@@ -6634,7 +6643,7 @@
     <row r="213" spans="1:3" ht="48" customHeight="1">
       <c r="A213" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B212),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C09.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C09_Rate, Loan_C09_Index, Loan_C09_Repayment, Loan_Frequency, Loan_DayCounter, , )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C09.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C09_Rate, Loan_C09_Index, Loan_C09_Repayment, Loan_Frequency, Loan_DayCounter, , , , )</v>
       </c>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6736,7 +6745,7 @@
         <v>215</v>
       </c>
       <c r="B232" s="10" cm="1" t="str">
-        <f t="array" ref="B232">_xll.QS.LOAN.SETTINGS("Loan.C10.Options",,INDEX(Loan_C10_Settings,2,2))</f>
+        <f t="array" ref="B232">_xll.QS.LOAN.SETTINGS("Loan.C10.Options",,Loan_C10_Setting_amortizationrate)</f>
         <v/>
       </c>
       <c r="C232" s="7" t="s">
@@ -6746,7 +6755,7 @@
     <row r="233" spans="1:3" ht="33.75" customHeight="1">
       <c r="A233" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B232),",",", ")</f>
-        <v>=QS.LOAN.SETTINGS("Loan.C10.Options", , INDEX(Loan_C10_Settings, 2, 2))</v>
+        <v>=QS.LOAN.SETTINGS("Loan.C10.Options", , Loan_C10_Setting_amortizationrate)</v>
       </c>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6756,7 +6765,7 @@
         <v>206</v>
       </c>
       <c r="B235" s="10" cm="1" t="str">
-        <f t="array" ref="B235">_xll.QS.INSTRUMENT.LOAN("Loan.C10.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C10_Rate,Loan_C10_Index,Loan_C10_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C10_Options,)</f>
+        <f t="array" ref="B235">_xll.QS.INSTRUMENT.LOAN("Loan.C10.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C10_Rate,Loan_C10_Index,Loan_C10_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C10_Options,,,)</f>
         <v/>
       </c>
       <c r="C235" s="7" t="s">
@@ -6766,7 +6775,7 @@
     <row r="236" spans="1:3" ht="48" customHeight="1">
       <c r="A236" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B235),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C10.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C10_Rate, Loan_C10_Index, Loan_C10_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C10_Options, )</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C10.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C10_Rate, Loan_C10_Index, Loan_C10_Repayment, Loan_Frequency, Loan_DayCounter, Loan_C10_Options, , , )</v>
       </c>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6868,7 +6877,7 @@
         <v>206</v>
       </c>
       <c r="B255" s="10" cm="1" t="str">
-        <f t="array" ref="B255">_xll.QS.INSTRUMENT.LOAN("Loan.C11.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C11_Rate,Loan_C11_Index,Loan_C11_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C11_Coupons)</f>
+        <f t="array" ref="B255">_xll.QS.INSTRUMENT.LOAN("Loan.C11.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C11_Rate,Loan_C11_Index,Loan_C11_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C11_CouponPeriods,Loan_C11_CouponRates,Loan_C11_CouponIndices)</f>
         <v/>
       </c>
       <c r="C255" s="7" t="s">
@@ -6878,7 +6887,7 @@
     <row r="256" spans="1:3" ht="48" customHeight="1">
       <c r="A256" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B255),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C11.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C11_Rate, Loan_C11_Index, Loan_C11_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C11_Coupons)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C11.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C11_Rate, Loan_C11_Index, Loan_C11_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C11_CouponPeriods, Loan_C11_CouponRates, Loan_C11_CouponIndices)</v>
       </c>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7020,7 +7029,7 @@
         <v>206</v>
       </c>
       <c r="B281" s="10" cm="1" t="str">
-        <f t="array" ref="B281">_xll.QS.INSTRUMENT.LOAN("Loan.C12.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C12_Rate,Loan_C12_Index,Loan_C12_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C12_Coupons)</f>
+        <f t="array" ref="B281">_xll.QS.INSTRUMENT.LOAN("Loan.C12.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C12_Rate,Loan_C12_Index,Loan_C12_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C12_CouponPeriods,Loan_C12_CouponRates,Loan_C12_CouponIndices)</f>
         <v/>
       </c>
       <c r="C281" s="7" t="s">
@@ -7030,7 +7039,7 @@
     <row r="282" spans="1:3" ht="48" customHeight="1">
       <c r="A282" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B281),",",", ")</f>
-        <v>=QS.INSTRUMENT.LOAN("Loan.C12.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C12_Rate, Loan_C12_Index, Loan_C12_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C12_Coupons)</v>
+        <v>=QS.INSTRUMENT.LOAN("Loan.C12.Instrument", Loan_Start, Loan_Maturity, Loan_Currency, Loan_Notional, Loan_C12_Rate, Loan_C12_Index, Loan_C12_Repayment, Loan_Frequency, Loan_DayCounter, , Loan_C12_CouponPeriods, Loan_C12_CouponRates, Loan_C12_CouponIndices)</v>
       </c>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -18,7 +18,7 @@
     <sheet name="8 Layouts" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="Loan_BaseCurves">'3 Market'!$B$59</definedName>
+    <definedName name="Loan_BaseCurves">'3 Market'!$B$38</definedName>
     <definedName name="Loan_C01_Discount">'2 Cases'!$B$9</definedName>
     <definedName name="Loan_C01_Fair0">'4 Build'!$B$49</definedName>
     <definedName name="Loan_C01_FairRate0">'5 Results'!$D$7</definedName>
@@ -197,22 +197,16 @@
     <definedName name="Loan_C12_Trade">'4 Build'!$B$284</definedName>
     <definedName name="Loan_CaseNames">'5 Results'!$A$7:$A$18</definedName>
     <definedName name="Loan_Context">'4 Build'!$B$7</definedName>
-    <definedName name="Loan_Credit">'3 Market'!$B$74</definedName>
-    <definedName name="Loan_CreditQuote1">'3 Market'!$B$35</definedName>
-    <definedName name="Loan_CreditQuote2">'3 Market'!$B$38</definedName>
-    <definedName name="Loan_CreditQuote3">'3 Market'!$B$41</definedName>
-    <definedName name="Loan_CreditQuote4">'3 Market'!$B$44</definedName>
-    <definedName name="Loan_CreditQuote5">'3 Market'!$B$47</definedName>
-    <definedName name="Loan_CreditQuote6">'3 Market'!$B$50</definedName>
-    <definedName name="Loan_CreditQuote7">'3 Market'!$B$53</definedName>
+    <definedName name="Loan_Credit">'3 Market'!$B$35</definedName>
+    <definedName name="Loan_CreditMid">'3 Market'!$B$18:$B$24</definedName>
     <definedName name="Loan_CreditQuotes">'3 Market'!$A$18:$A$24</definedName>
     <definedName name="Loan_Currency">'1 Inputs'!$B$15</definedName>
-    <definedName name="Loan_Curves">'3 Market'!$B$68</definedName>
+    <definedName name="Loan_Curves">'3 Market'!$B$47</definedName>
     <definedName name="Loan_DayCounter">'1 Inputs'!$B$14</definedName>
     <definedName name="Loan_EstrCurve">'4 Build'!$B$22</definedName>
     <definedName name="Loan_FixedRate">'1 Inputs'!$B$9</definedName>
     <definedName name="Loan_FloatingSpread">'1 Inputs'!$B$10</definedName>
-    <definedName name="Loan_ForwardCurves">'3 Market'!$B$62</definedName>
+    <definedName name="Loan_ForwardCurves">'3 Market'!$B$41</definedName>
     <definedName name="Loan_ForwardRates">'3 Market'!$C$7:$C$11</definedName>
     <definedName name="Loan_Frequency">'1 Inputs'!$B$13</definedName>
     <definedName name="Loan_FundingCurrency">'1 Inputs'!$A$29</definedName>
@@ -221,13 +215,10 @@
     <definedName name="Loan_FundingPolicy">'4 Build'!$B$16</definedName>
     <definedName name="Loan_FundingPricer">'4 Build'!$B$19</definedName>
     <definedName name="Loan_FundingSpreads">'3 Market'!$D$7:$D$11</definedName>
-    <definedName name="Loan_InitialCredit">'3 Market'!$B$71</definedName>
-    <definedName name="Loan_InitialCurves">'3 Market'!$B$56</definedName>
-    <definedName name="Loan_InitialQuotes">'3 Market'!$B$32</definedName>
+    <definedName name="Loan_MarketInputs">'3 Market'!$B$35:$B$49</definedName>
     <definedName name="Loan_Maturity">'1 Inputs'!$B$12</definedName>
     <definedName name="Loan_Notional">'1 Inputs'!$B$8</definedName>
     <definedName name="Loan_Pillars">'3 Market'!$A$7:$A$11</definedName>
-    <definedName name="Loan_Quotes">Loan_CreditQuote7</definedName>
     <definedName name="Loan_Recovery">'3 Market'!$B$27</definedName>
     <definedName name="Loan_Request0">'4 Build'!$B$25</definedName>
     <definedName name="Loan_Request1">'4 Build'!$B$28</definedName>
@@ -239,10 +230,11 @@
     <definedName name="Loan_RiskFreeMapping">'1 Inputs'!$A$28:$B$28</definedName>
     <definedName name="Loan_RiskFreePolicy">'4 Build'!$B$10</definedName>
     <definedName name="Loan_RiskFreePricer">'4 Build'!$B$13</definedName>
+    <definedName name="Loan_Root">'3 Market'!$B$32</definedName>
     <definedName name="Loan_SelectedCase">'5 Results'!$B$22</definedName>
     <definedName name="Loan_SelectedResult">'4 Build'!$B$319</definedName>
     <definedName name="Loan_Side">'1 Inputs'!$B$16</definedName>
-    <definedName name="Loan_SpreadCurves">'3 Market'!$B$65</definedName>
+    <definedName name="Loan_SpreadCurves">'3 Market'!$B$44</definedName>
     <definedName name="Loan_Start">'1 Inputs'!$B$11</definedName>
     <definedName name="Loan_ValuationDate">'1 Inputs'!$B$7</definedName>
     <definedName name="Loan_ZeroRates">'3 Market'!$B$7:$B$11</definedName>
@@ -428,7 +420,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Sets the valuation date for the market.</t>
+          <t>Owns the market stores and date.</t>
         </r>
       </text>
     </comment>
@@ -441,7 +433,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Each update consumes the preceding store revision.</t>
+          <t>Independent CDS identifier and quote arrays.</t>
         </r>
       </text>
     </comment>
@@ -454,7 +446,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Each update consumes the preceding store revision.</t>
+          <t>Every addition references the same root; fields are separate arrays.</t>
         </r>
       </text>
     </comment>
@@ -467,7 +459,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Each update consumes the preceding store revision.</t>
+          <t>Every addition references the same root; fields are separate arrays.</t>
         </r>
       </text>
     </comment>
@@ -480,7 +472,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Each update consumes the preceding store revision.</t>
+          <t>Every addition references the same root; fields are separate arrays.</t>
         </r>
       </text>
     </comment>
@@ -493,124 +485,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Each update consumes the preceding store revision.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B50" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Each update consumes the preceding store revision.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Each update consumes the preceding store revision.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B56" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Curve construction choices are separate from contract terms.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B59" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>The context builds this curve from the blue input range.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B62" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EURIBOR12m projects floating coupon fixings.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B65" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>The spread is constructed with the same curve API.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B68" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>The discount policy chooses whether to use ESTR or FUNDING.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B71" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Borrower survival is calibrated from the CDS quotes.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B74" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Only the borrower-credit case attaches this credit index to its contract.</t>
+          <t>Funding is an ordinary context curve.</t>
         </r>
       </text>
     </comment>
@@ -1691,7 +1566,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="250">
   <si>
     <t>Loans · compare one change at a time</t>
   </si>
@@ -2179,76 +2054,34 @@
     <t>Why it is needed</t>
   </si>
   <si>
-    <t>1. Create quote store</t>
-  </si>
-  <si>
-    <t>Sets the valuation date for the market.</t>
-  </si>
-  <si>
-    <t>2.1 Load CDS quote</t>
-  </si>
-  <si>
-    <t>Each update consumes the preceding store revision.</t>
-  </si>
-  <si>
-    <t>2.2 Load CDS quote</t>
-  </si>
-  <si>
-    <t>2.3 Load CDS quote</t>
-  </si>
-  <si>
-    <t>2.4 Load CDS quote</t>
-  </si>
-  <si>
-    <t>2.5 Load CDS quote</t>
-  </si>
-  <si>
-    <t>2.6 Load CDS quote</t>
-  </si>
-  <si>
-    <t>2.7 Load CDS quote</t>
-  </si>
-  <si>
-    <t>3. Create curve configurations</t>
-  </si>
-  <si>
-    <t>Curve construction choices are separate from contract terms.</t>
-  </si>
-  <si>
-    <t>4. Configure ESTR</t>
-  </si>
-  <si>
-    <t>The context builds this curve from the blue input range.</t>
-  </si>
-  <si>
-    <t>5. Configure projection curve</t>
-  </si>
-  <si>
-    <t>EURIBOR12m projects floating coupon fixings.</t>
-  </si>
-  <si>
-    <t>6. Configure treasury spread</t>
-  </si>
-  <si>
-    <t>The spread is constructed with the same curve API.</t>
-  </si>
-  <si>
-    <t>7. Configure funding curve</t>
-  </si>
-  <si>
-    <t>The discount policy chooses whether to use ESTR or FUNDING.</t>
-  </si>
-  <si>
-    <t>8. Create credit configurations</t>
-  </si>
-  <si>
-    <t>Borrower survival is calibrated from the CDS quotes.</t>
-  </si>
-  <si>
-    <t>9. Configure borrower credit</t>
-  </si>
-  <si>
-    <t>Only the borrower-credit case attaches this credit index to its contract.</t>
+    <t>1. Create root context</t>
+  </si>
+  <si>
+    <t>Owns the market stores and date.</t>
+  </si>
+  <si>
+    <t>2. Add borrower credit</t>
+  </si>
+  <si>
+    <t>Independent CDS identifier and quote arrays.</t>
+  </si>
+  <si>
+    <t>Add ESTR</t>
+  </si>
+  <si>
+    <t>Every addition references the same root; fields are separate arrays.</t>
+  </si>
+  <si>
+    <t>Add EURIBOR12m</t>
+  </si>
+  <si>
+    <t>Add FUNDINGSPREAD</t>
+  </si>
+  <si>
+    <t>Add funding curve</t>
+  </si>
+  <si>
+    <t>Funding is an ordinary context curve.</t>
   </si>
   <si>
     <t>Build and evaluate the loan agreements</t>
@@ -3018,7 +2851,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -3045,7 +2878,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+    <row r="3" spans="1:6" ht="26" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3055,7 +2888,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="26.25" customHeight="1">
+    <row r="4" spans="1:6" ht="26" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3063,7 +2896,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="26.25" customHeight="1">
+    <row r="6" spans="1:6" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -3073,7 +2906,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="26.25" customHeight="1">
+    <row r="7" spans="1:6" ht="26" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -3081,7 +2914,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="26.25" customHeight="1">
+    <row r="9" spans="1:6" ht="26" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
@@ -3091,7 +2924,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="33.75" customHeight="1">
+    <row r="10" spans="1:6" ht="34" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -3105,7 +2938,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="33.75" customHeight="1">
+    <row r="11" spans="1:6" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -3119,7 +2952,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="33.75" customHeight="1">
+    <row r="12" spans="1:6" ht="34" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -3133,7 +2966,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="33.75" customHeight="1">
+    <row r="13" spans="1:6" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -3147,7 +2980,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="33.75" customHeight="1">
+    <row r="14" spans="1:6" ht="34" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -3161,7 +2994,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="33.75" customHeight="1">
+    <row r="15" spans="1:6" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -3175,7 +3008,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1">
+    <row r="16" spans="1:6" ht="34" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -3189,7 +3022,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1">
+    <row r="17" spans="1:6" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -3203,7 +3036,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="26.25" customHeight="1">
+    <row r="20" spans="1:6" ht="26" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
@@ -3249,7 +3082,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="26.25" customHeight="1">
+    <row r="25" spans="1:6" ht="26" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -3259,7 +3092,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" ht="33.75" customHeight="1">
+    <row r="26" spans="1:6" ht="34" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -3269,7 +3102,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1">
+    <row r="27" spans="1:6" ht="34" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
@@ -3279,7 +3112,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" ht="33.75" customHeight="1">
+    <row r="28" spans="1:6" ht="34" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -3289,7 +3122,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="30" spans="1:6" ht="26.25" customHeight="1">
+    <row r="30" spans="1:6" ht="26" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>39</v>
       </c>
@@ -3299,7 +3132,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" ht="26.25" customHeight="1">
+    <row r="31" spans="1:6" ht="26" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3371,7 +3204,7 @@
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3409,7 +3242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32.25" customHeight="1">
+    <row r="7" spans="1:3" ht="32" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -3420,7 +3253,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32.25" customHeight="1">
+    <row r="8" spans="1:3" ht="32" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
@@ -3431,7 +3264,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32.25" customHeight="1">
+    <row r="9" spans="1:3" ht="32" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -3442,7 +3275,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32.25" customHeight="1">
+    <row r="10" spans="1:3" ht="32" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3453,7 +3286,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32.25" customHeight="1">
+    <row r="11" spans="1:3" ht="32" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
@@ -3464,7 +3297,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32.25" customHeight="1">
+    <row r="12" spans="1:3" ht="32" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -3475,7 +3308,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="32.25" customHeight="1">
+    <row r="13" spans="1:3" ht="32" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -3486,7 +3319,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="32.25" customHeight="1">
+    <row r="14" spans="1:3" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -3497,7 +3330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="32.25" customHeight="1">
+    <row r="15" spans="1:3" ht="32" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>67</v>
       </c>
@@ -3508,7 +3341,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="32.25" customHeight="1">
+    <row r="16" spans="1:3" ht="32" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -3611,7 +3444,7 @@
     <col min="6" max="6" width="22.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38.25" customHeight="1">
+    <row r="1" spans="1:6" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -4830,7 +4663,7 @@
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="1" customWidth="1"/>
@@ -4839,7 +4672,7 @@
     <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="38.25" customHeight="1">
+    <row r="1" spans="1:4" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>135</v>
       </c>
@@ -5033,7 +4866,7 @@
         <v>0.017</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="32.25" customHeight="1">
+    <row r="27" spans="1:4" ht="32" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>157</v>
       </c>
@@ -5055,308 +4888,128 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="38.25" customHeight="1">
+    <row r="32" spans="1:4" ht="38" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>162</v>
       </c>
       <c r="B32" s="10" cm="1" t="str">
-        <f t="array" ref="B32">_xll.QS.QUOTES.CREATE("Loan.Quotes",Loan_ValuationDate)</f>
+        <f t="array" ref="B32">_xll.QS.CONTEXT.CREATE("Loan.Root",Loan_ValuationDate,"EUR","ESTR")</f>
         <v/>
       </c>
       <c r="C32" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="33.75" customHeight="1">
+    <row r="33" spans="1:3" ht="34" customHeight="1">
       <c r="A33" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B32),",",", ")</f>
-        <v>=QS.QUOTES.CREATE("Loan.Quotes", Loan_ValuationDate)</v>
+        <v>=QS.CONTEXT.CREATE("Loan.Root", Loan_ValuationDate, "EUR", "ESTR")</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
     </row>
-    <row r="35" spans="1:3" ht="38.25" customHeight="1">
+    <row r="35" spans="1:3" ht="38" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>164</v>
       </c>
       <c r="B35" s="10" cm="1" t="str">
-        <f t="array" ref="B35">_xll.QS.QUOTES.SET(Loan_InitialQuotes,'3 Market'!A18,'3 Market'!B18,,)</f>
+        <f t="array" ref="B35">_xll.QS.CONTEXT.ADD.CREDIT.CURVE(Loan_Root,"Credit:BORROWER","EUR","ESTR",Loan_Recovery,Loan_CreditQuotes,Loan_CreditMid)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="33.75" customHeight="1">
+    <row r="36" spans="1:3" ht="34" customHeight="1">
       <c r="A36" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_InitialQuotes, '3 Market'!A18, '3 Market'!B18, , )</v>
+        <v>=QS.CONTEXT.ADD.CREDIT.CURVE(Loan_Root, "Credit:BORROWER", "EUR", "ESTR", Loan_Recovery, Loan_CreditQuotes, Loan_CreditMid)</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
     </row>
-    <row r="38" spans="1:3" ht="38.25" customHeight="1">
+    <row r="38" spans="1:3" ht="38" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B38" s="10" cm="1" t="str">
-        <f t="array" ref="B38">_xll.QS.QUOTES.SET(Loan_CreditQuote1,'3 Market'!A19,'3 Market'!B19,,)</f>
+        <f t="array" ref="B38">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"ESTR",Loan_Pillars,Loan_ZeroRates,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
         <v/>
       </c>
       <c r="C38" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="33.75" customHeight="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="34" customHeight="1">
       <c r="A39" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B38),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote1, '3 Market'!A19, '3 Market'!B19, , )</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "ESTR", Loan_Pillars, Loan_ZeroRates, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
     </row>
-    <row r="41" spans="1:3" ht="38.25" customHeight="1">
+    <row r="41" spans="1:3" ht="38" customHeight="1">
       <c r="A41" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="10" cm="1" t="str">
+        <f t="array" ref="B41">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"EURIBOR12m",Loan_Pillars,Loan_ForwardRates,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
+        <v/>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B41" s="10" cm="1" t="str">
-        <f t="array" ref="B41">_xll.QS.QUOTES.SET(Loan_CreditQuote2,'3 Market'!A20,'3 Market'!B20,,)</f>
-        <v/>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="33.75" customHeight="1">
+    </row>
+    <row r="42" spans="1:3" ht="34" customHeight="1">
       <c r="A42" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B41),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote2, '3 Market'!A20, '3 Market'!B20, , )</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "EURIBOR12m", Loan_Pillars, Loan_ForwardRates, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
       </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
     </row>
-    <row r="44" spans="1:3" ht="38.25" customHeight="1">
+    <row r="44" spans="1:3" ht="38" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="10" cm="1" t="str">
-        <f t="array" ref="B44">_xll.QS.QUOTES.SET(Loan_CreditQuote3,'3 Market'!A21,'3 Market'!B21,,)</f>
+        <f t="array" ref="B44">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"FUNDINGSPREAD",Loan_Pillars,Loan_FundingSpreads,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
         <v/>
       </c>
       <c r="C44" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="33.75" customHeight="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="34" customHeight="1">
       <c r="A45" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B44),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote3, '3 Market'!A21, '3 Market'!B21, , )</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "FUNDINGSPREAD", Loan_Pillars, Loan_FundingSpreads, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
     </row>
-    <row r="47" spans="1:3" ht="38.25" customHeight="1">
+    <row r="47" spans="1:3" ht="38" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="10" cm="1" t="str">
-        <f t="array" ref="B47">_xll.QS.QUOTES.SET(Loan_CreditQuote4,'3 Market'!A22,'3 Market'!B22,,)</f>
+        <f t="array" ref="B47">_xll.QS.CONTEXT.ADD.COMPOSITE.CURVE(Loan_Root,"FUNDING","EURIBOR12m","FUNDINGSPREAD")</f>
         <v/>
       </c>
       <c r="C47" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="33.75" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="34" customHeight="1">
       <c r="A48" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B47),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote4, '3 Market'!A22, '3 Market'!B22, , )</v>
+        <v>=QS.CONTEXT.ADD.COMPOSITE.CURVE(Loan_Root, "FUNDING", "EURIBOR12m", "FUNDINGSPREAD")</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
     </row>
-    <row r="50" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B50" s="10" cm="1" t="str">
-        <f t="array" ref="B50">_xll.QS.QUOTES.SET(Loan_CreditQuote5,'3 Market'!A23,'3 Market'!B23,,)</f>
-        <v/>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A51" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B50),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote5, '3 Market'!A23, '3 Market'!B23, , )</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-    </row>
-    <row r="53" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A53" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="10" cm="1" t="str">
-        <f t="array" ref="B53">_xll.QS.QUOTES.SET(Loan_CreditQuote6,'3 Market'!A24,'3 Market'!B24,,)</f>
-        <v/>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A54" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B53),",",", ")</f>
-        <v>=QS.QUOTES.SET(Loan_CreditQuote6, '3 Market'!A24, '3 Market'!B24, , )</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-    </row>
-    <row r="56" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="10" cm="1" t="str">
-        <f t="array" ref="B56">_xll.QS.CURVE.CONFIGS.CREATE("Loan.Curves")</f>
-        <v/>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A57" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B56),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("Loan.Curves")</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-    </row>
-    <row r="59" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" s="10" cm="1" t="str">
-        <f t="array" ref="B59">_xll.QS.CURVE.CONFIGS.ADD.ZERO(Loan_InitialCurves,"ESTR","Actual360","Linear",TRUE,Loan_Pillars,Loan_ZeroRates,"Continuous","Annual")</f>
-        <v/>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A60" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B59),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_InitialCurves, "ESTR", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_ZeroRates, "Continuous", "Annual")</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-    </row>
-    <row r="62" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A62" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B62" s="10" cm="1" t="str">
-        <f t="array" ref="B62">_xll.QS.CURVE.CONFIGS.ADD.ZERO(Loan_BaseCurves,"EURIBOR12m","Actual360","Linear",TRUE,Loan_Pillars,Loan_ForwardRates,"Continuous","Annual")</f>
-        <v/>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A63" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B62),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_BaseCurves, "EURIBOR12m", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_ForwardRates, "Continuous", "Annual")</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-    </row>
-    <row r="65" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A65" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B65" s="10" cm="1" t="str">
-        <f t="array" ref="B65">_xll.QS.CURVE.CONFIGS.ADD.ZERO(Loan_ForwardCurves,"FUNDINGSPREAD","Actual360","Linear",TRUE,Loan_Pillars,Loan_FundingSpreads,"Continuous","Annual")</f>
-        <v/>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A66" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B65),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.ZERO(Loan_ForwardCurves, "FUNDINGSPREAD", "Actual360", "Linear", TRUE, Loan_Pillars, Loan_FundingSpreads, "Continuous", "Annual")</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-    </row>
-    <row r="68" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A68" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B68" s="10" cm="1" t="str">
-        <f t="array" ref="B68">_xll.QS.CURVE.CONFIGS.ADD.COMPOSITE(Loan_SpreadCurves,"FUNDING","EURIBOR12m","FUNDINGSPREAD")</f>
-        <v/>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A69" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B68),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.COMPOSITE(Loan_SpreadCurves, "FUNDING", "EURIBOR12m", "FUNDINGSPREAD")</v>
-      </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-    </row>
-    <row r="71" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A71" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B71" s="10" cm="1" t="str">
-        <f t="array" ref="B71">_xll.QS.CREDIT.CURVE.CONFIGS.CREATE("Loan.Credit")</f>
-        <v/>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A72" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B71),",",", ")</f>
-        <v>=QS.CREDIT.CURVE.CONFIGS.CREATE("Loan.Credit")</v>
-      </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-    </row>
-    <row r="74" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A74" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B74" s="10" cm="1" t="str">
-        <f t="array" ref="B74">_xll.QS.CREDIT.CURVE.CONFIGS.ADD(Loan_InitialCredit,"Credit:BORROWER","EUR","ESTR",Loan_Recovery,Loan_CreditQuotes)</f>
-        <v/>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A75" s="14" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B74),",",", ")</f>
-        <v>=QS.CREDIT.CURVE.CONFIGS.ADD(Loan_InitialCredit, "Credit:BORROWER", "EUR", "ESTR", Loan_Recovery, Loan_CreditQuotes)</v>
-      </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D3"/>
     <mergeCell ref="A13:D14"/>
@@ -5366,15 +5019,6 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -5402,16 +5046,16 @@
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5426,53 +5070,53 @@
         <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.FROM.COMPONENTS("Loan.Context",Loan_Quotes,Loan_Curves,Loan_Credit,,,,,,,,,"EUR","ESTR","Mid")</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.PREPARE("Loan.Context",Loan_Root,Loan_MarketInputs)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="33.75" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.COMPONENTS("Loan.Context", Loan_Quotes, Loan_Curves, Loan_Credit, , , , , , , , , "EUR", "ESTR", "Mid")</v>
+        <v>=QS.CONTEXT.PREPARE("Loan.Context", Loan_Root, Loan_MarketInputs)</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="10" spans="1:3" ht="38.25" customHeight="1">
+    <row r="10" spans="1:3" ht="38" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy",Loan_RiskFreeCurrency,Loan_RiskFreeIndex)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy", Loan_RiskFreeCurrency, Loan_RiskFreeIndex)</v>
@@ -5480,19 +5124,19 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+    <row r="13" spans="1:3" ht="38" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.PRICER.CREATE("Loan.RiskFreePricer","LoanPricer",Loan_RiskFreePolicy)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.RiskFreePricer", "LoanPricer", Loan_RiskFreePolicy)</v>
@@ -5500,19 +5144,19 @@
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+    <row r="16" spans="1:3" ht="38" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy",Loan_FundingCurrency,Loan_FundingIndex)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy", Loan_FundingCurrency, Loan_FundingIndex)</v>
@@ -5520,19 +5164,19 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
     </row>
-    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+    <row r="19" spans="1:3" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.PRICER.CREATE("Loan.FundingPricer","LoanPricer",Loan_FundingPolicy)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.FundingPricer", "LoanPricer", Loan_FundingPolicy)</v>
@@ -5540,19 +5184,19 @@
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
     </row>
-    <row r="22" spans="1:3" ht="38.25" customHeight="1">
+    <row r="22" spans="1:3" ht="38" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
         <f t="array" ref="B22">_xll.QS.CURVE.GET(Loan_Context,"ESTR")</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="33.75" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
         <v>=QS.CURVE.GET(Loan_Context, "ESTR")</v>
@@ -5560,19 +5204,19 @@
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
-    <row r="25" spans="1:3" ht="38.25" customHeight="1">
+    <row r="25" spans="1:3" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
         <f t="array" ref="B25">_xll.QS.REQUEST.FAIR.RATE(0)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="33.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(0)</v>
@@ -5580,19 +5224,19 @@
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="28" spans="1:3" ht="38.25" customHeight="1">
+    <row r="28" spans="1:3" ht="38" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B28" s="10" cm="1" t="str">
         <f t="array" ref="B28">_xll.QS.REQUEST.FAIR.RATE(1)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="33.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(1)</v>
@@ -5600,19 +5244,19 @@
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
     </row>
-    <row r="31" spans="1:3" ht="38.25" customHeight="1">
+    <row r="31" spans="1:3" ht="38" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B31" s="10" cm="1" t="str">
         <f t="array" ref="B31">_xll.QS.REQUEST.FAIR.RATE(2)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="33.75" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(2)</v>
@@ -5629,12 +5273,12 @@
     </row>
     <row r="35" spans="1:3" ht="24" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="38" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B37" s="10" cm="1" t="str">
         <f t="array" ref="B37">_xll.QS.INSTRUMENT.LOAN("Loan.C01.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C01_Rate,Loan_C01_Index,Loan_C01_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
@@ -5652,19 +5296,19 @@
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="40" spans="1:3" ht="38.25" customHeight="1">
+    <row r="40" spans="1:3" ht="38" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B40" s="10" cm="1" t="str">
         <f t="array" ref="B40">_xll.QS.TRADE.CREATE("Loan.C01.Trade",Loan_C01_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="34" customHeight="1">
       <c r="A41" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C01.Trade", Loan_C01_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5672,19 +5316,19 @@
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
     </row>
-    <row r="43" spans="1:3" ht="38.25" customHeight="1">
+    <row r="43" spans="1:3" ht="38" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B43" s="10">
         <f>IF(Loan_C01_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="34" customHeight="1">
       <c r="A44" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
         <v>=IF(Loan_C01_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5692,42 +5336,42 @@
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
     </row>
-    <row r="46" spans="1:3" ht="38.25" customHeight="1">
+    <row r="46" spans="1:3" ht="38" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B46" s="10" cm="1" t="str">
-        <f t="array" ref="B46">_xll.QS.EVALUATE("Loan.C01.Result",Loan_C01_Pricer,Loan_C01_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B46">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C01_Trade,Loan_Requests,,Loan_C01_Pricer)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="34" customHeight="1">
       <c r="A47" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C01.Result", Loan_C01_Pricer, Loan_C01_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C01_Trade, Loan_Requests, , Loan_C01_Pricer)</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
     </row>
-    <row r="49" spans="1:3" ht="38.25" customHeight="1">
+    <row r="49" spans="1:3" ht="38" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B49" s="10" cm="1" t="str">
-        <f t="array" ref="B49">_xll.QS.EVALUATE("Loan.C01.Fair0",Loan_C01_Pricer,Loan_C01_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B49">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C01_Trade,Loan_Request0,,Loan_C01_Pricer)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="34" customHeight="1">
       <c r="A50" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C01.Fair0", Loan_C01_Pricer, Loan_C01_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C01_Trade, Loan_Request0, , Loan_C01_Pricer)</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -5741,12 +5385,12 @@
     </row>
     <row r="55" spans="1:3" ht="24" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="38" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B57" s="10" cm="1" t="str">
         <f t="array" ref="B57">_xll.QS.INSTRUMENT.LOAN("Loan.C02.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C02_Rate,Loan_C02_Index,Loan_C02_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
@@ -5764,19 +5408,19 @@
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
     </row>
-    <row r="60" spans="1:3" ht="38.25" customHeight="1">
+    <row r="60" spans="1:3" ht="38" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B60" s="10" cm="1" t="str">
         <f t="array" ref="B60">_xll.QS.TRADE.CREATE("Loan.C02.Trade",Loan_C02_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C60" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="34" customHeight="1">
       <c r="A61" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B60),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C02.Trade", Loan_C02_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5784,19 +5428,19 @@
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
     </row>
-    <row r="63" spans="1:3" ht="38.25" customHeight="1">
+    <row r="63" spans="1:3" ht="38" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B63" s="10">
         <f>IF(Loan_C02_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C63" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="34" customHeight="1">
       <c r="A64" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B63),",",", ")</f>
         <v>=IF(Loan_C02_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5804,42 +5448,42 @@
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
     </row>
-    <row r="66" spans="1:3" ht="38.25" customHeight="1">
+    <row r="66" spans="1:3" ht="38" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B66" s="10" cm="1" t="str">
-        <f t="array" ref="B66">_xll.QS.EVALUATE("Loan.C02.Result",Loan_C02_Pricer,Loan_C02_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B66">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C02_Trade,Loan_Requests,,Loan_C02_Pricer)</f>
         <v/>
       </c>
       <c r="C66" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="34" customHeight="1">
       <c r="A67" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B66),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C02.Result", Loan_C02_Pricer, Loan_C02_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C02_Trade, Loan_Requests, , Loan_C02_Pricer)</v>
       </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
-    <row r="69" spans="1:3" ht="38.25" customHeight="1">
+    <row r="69" spans="1:3" ht="38" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B69" s="10" cm="1" t="str">
-        <f t="array" ref="B69">_xll.QS.EVALUATE("Loan.C02.Fair0",Loan_C02_Pricer,Loan_C02_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B69">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C02_Trade,Loan_Request0,,Loan_C02_Pricer)</f>
         <v/>
       </c>
       <c r="C69" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="34" customHeight="1">
       <c r="A70" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B69),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C02.Fair0", Loan_C02_Pricer, Loan_C02_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C02_Trade, Loan_Request0, , Loan_C02_Pricer)</v>
       </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -5853,22 +5497,22 @@
     </row>
     <row r="75" spans="1:3" ht="24" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="38" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B77" s="10" cm="1" t="str">
         <f t="array" ref="B77">_xll.QS.LOAN.SETTINGS("Loan.C03.Options",Loan_C03_Setting_balloonfraction)</f>
         <v/>
       </c>
       <c r="C77" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="34" customHeight="1">
       <c r="A78" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B77),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C03.Options", Loan_C03_Setting_balloonfraction)</v>
@@ -5876,9 +5520,9 @@
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
     </row>
-    <row r="80" spans="1:3" ht="38.25" customHeight="1">
+    <row r="80" spans="1:3" ht="38" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B80" s="10" cm="1" t="str">
         <f t="array" ref="B80">_xll.QS.INSTRUMENT.LOAN("Loan.C03.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C03_Rate,Loan_C03_Index,Loan_C03_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C03_Options,,,)</f>
@@ -5896,19 +5540,19 @@
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
     </row>
-    <row r="83" spans="1:3" ht="38.25" customHeight="1">
+    <row r="83" spans="1:3" ht="38" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B83" s="10" cm="1" t="str">
         <f t="array" ref="B83">_xll.QS.TRADE.CREATE("Loan.C03.Trade",Loan_C03_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C83" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="34" customHeight="1">
       <c r="A84" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B83),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C03.Trade", Loan_C03_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5916,19 +5560,19 @@
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
     </row>
-    <row r="86" spans="1:3" ht="38.25" customHeight="1">
+    <row r="86" spans="1:3" ht="38" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B86" s="10">
         <f>IF(Loan_C03_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C86" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="34" customHeight="1">
       <c r="A87" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B86),",",", ")</f>
         <v>=IF(Loan_C03_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5936,42 +5580,42 @@
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
     </row>
-    <row r="89" spans="1:3" ht="38.25" customHeight="1">
+    <row r="89" spans="1:3" ht="38" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B89" s="10" cm="1" t="str">
-        <f t="array" ref="B89">_xll.QS.EVALUATE("Loan.C03.Result",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B89">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C03_Trade,Loan_Requests,,Loan_C03_Pricer)</f>
         <v/>
       </c>
       <c r="C89" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="34" customHeight="1">
       <c r="A90" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B89),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C03.Result", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C03_Trade, Loan_Requests, , Loan_C03_Pricer)</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
     </row>
-    <row r="92" spans="1:3" ht="38.25" customHeight="1">
+    <row r="92" spans="1:3" ht="38" customHeight="1">
       <c r="A92" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B92" s="10" cm="1" t="str">
-        <f t="array" ref="B92">_xll.QS.EVALUATE("Loan.C03.Fair0",Loan_C03_Pricer,Loan_C03_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B92">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C03_Trade,Loan_Request0,,Loan_C03_Pricer)</f>
         <v/>
       </c>
       <c r="C92" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="34" customHeight="1">
       <c r="A93" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B92),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C03.Fair0", Loan_C03_Pricer, Loan_C03_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C03_Trade, Loan_Request0, , Loan_C03_Pricer)</v>
       </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -5985,22 +5629,22 @@
     </row>
     <row r="98" spans="1:3" ht="24" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="38" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B100" s="10" cm="1" t="str">
         <f t="array" ref="B100">_xll.QS.LOAN.SETTINGS("Loan.C04.Options",,Loan_C04_Setting_amortizationrate)</f>
         <v/>
       </c>
       <c r="C100" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="34" customHeight="1">
       <c r="A101" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C04.Options", , Loan_C04_Setting_amortizationrate)</v>
@@ -6008,9 +5652,9 @@
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
     </row>
-    <row r="103" spans="1:3" ht="38.25" customHeight="1">
+    <row r="103" spans="1:3" ht="38" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B103" s="10" cm="1" t="str">
         <f t="array" ref="B103">_xll.QS.INSTRUMENT.LOAN("Loan.C04.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C04_Rate,Loan_C04_Index,Loan_C04_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C04_Options,,,)</f>
@@ -6028,19 +5672,19 @@
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
     </row>
-    <row r="106" spans="1:3" ht="38.25" customHeight="1">
+    <row r="106" spans="1:3" ht="38" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B106" s="10" cm="1" t="str">
         <f t="array" ref="B106">_xll.QS.TRADE.CREATE("Loan.C04.Trade",Loan_C04_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C106" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="34" customHeight="1">
       <c r="A107" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B106),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C04.Trade", Loan_C04_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6048,19 +5692,19 @@
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
     </row>
-    <row r="109" spans="1:3" ht="38.25" customHeight="1">
+    <row r="109" spans="1:3" ht="38" customHeight="1">
       <c r="A109" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B109" s="10">
         <f>IF(Loan_C04_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C109" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="34" customHeight="1">
       <c r="A110" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B109),",",", ")</f>
         <v>=IF(Loan_C04_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6068,42 +5712,42 @@
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
     </row>
-    <row r="112" spans="1:3" ht="38.25" customHeight="1">
+    <row r="112" spans="1:3" ht="38" customHeight="1">
       <c r="A112" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B112" s="10" cm="1" t="str">
-        <f t="array" ref="B112">_xll.QS.EVALUATE("Loan.C04.Result",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B112">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C04_Trade,Loan_Requests,,Loan_C04_Pricer)</f>
         <v/>
       </c>
       <c r="C112" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="34" customHeight="1">
       <c r="A113" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B112),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C04.Result", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C04_Trade, Loan_Requests, , Loan_C04_Pricer)</v>
       </c>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
     </row>
-    <row r="115" spans="1:3" ht="38.25" customHeight="1">
+    <row r="115" spans="1:3" ht="38" customHeight="1">
       <c r="A115" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B115" s="10" cm="1" t="str">
-        <f t="array" ref="B115">_xll.QS.EVALUATE("Loan.C04.Fair0",Loan_C04_Pricer,Loan_C04_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B115">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C04_Trade,Loan_Request0,,Loan_C04_Pricer)</f>
         <v/>
       </c>
       <c r="C115" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="34" customHeight="1">
       <c r="A116" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B115),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C04.Fair0", Loan_C04_Pricer, Loan_C04_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C04_Trade, Loan_Request0, , Loan_C04_Pricer)</v>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -6117,12 +5761,12 @@
     </row>
     <row r="121" spans="1:3" ht="24" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="38" customHeight="1">
       <c r="A123" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B123" s="10" cm="1" t="str">
         <f t="array" ref="B123">_xll.QS.INSTRUMENT.LOAN("Loan.C05.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C05_Rate,Loan_C05_Index,Loan_C05_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C05_CouponPeriods,Loan_C05_CouponRates,Loan_C05_CouponIndices)</f>
@@ -6140,19 +5784,19 @@
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
     </row>
-    <row r="126" spans="1:3" ht="38.25" customHeight="1">
+    <row r="126" spans="1:3" ht="38" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B126" s="10" cm="1" t="str">
         <f t="array" ref="B126">_xll.QS.TRADE.CREATE("Loan.C05.Trade",Loan_C05_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C126" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="34" customHeight="1">
       <c r="A127" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B126),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C05.Trade", Loan_C05_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6160,19 +5804,19 @@
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
     </row>
-    <row r="129" spans="1:3" ht="38.25" customHeight="1">
+    <row r="129" spans="1:3" ht="38" customHeight="1">
       <c r="A129" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B129" s="10">
         <f>IF(Loan_C05_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C129" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="34" customHeight="1">
       <c r="A130" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B129),",",", ")</f>
         <v>=IF(Loan_C05_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6180,62 +5824,62 @@
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
     </row>
-    <row r="132" spans="1:3" ht="38.25" customHeight="1">
+    <row r="132" spans="1:3" ht="38" customHeight="1">
       <c r="A132" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B132" s="10" cm="1" t="str">
-        <f t="array" ref="B132">_xll.QS.EVALUATE("Loan.C05.Result",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B132">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C05_Trade,Loan_Requests,,Loan_C05_Pricer)</f>
         <v/>
       </c>
       <c r="C132" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="34" customHeight="1">
       <c r="A133" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B132),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Result", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Requests, , Loan_C05_Pricer)</v>
       </c>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
     </row>
-    <row r="135" spans="1:3" ht="38.25" customHeight="1">
+    <row r="135" spans="1:3" ht="38" customHeight="1">
       <c r="A135" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B135" s="10" cm="1" t="str">
-        <f t="array" ref="B135">_xll.QS.EVALUATE("Loan.C05.Fair0",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B135">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C05_Trade,Loan_Request0,,Loan_C05_Pricer)</f>
         <v/>
       </c>
       <c r="C135" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="34" customHeight="1">
       <c r="A136" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B135),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Fair0", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Request0, , Loan_C05_Pricer)</v>
       </c>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
     </row>
-    <row r="138" spans="1:3" ht="38.25" customHeight="1">
+    <row r="138" spans="1:3" ht="38" customHeight="1">
       <c r="A138" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B138" s="10" cm="1" t="str">
-        <f t="array" ref="B138">_xll.QS.EVALUATE("Loan.C05.Fair1",Loan_C05_Pricer,Loan_C05_Trade,Loan_Context,Loan_Request1)</f>
+        <f t="array" ref="B138">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C05_Trade,Loan_Request1,,Loan_C05_Pricer)</f>
         <v/>
       </c>
       <c r="C138" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="34" customHeight="1">
       <c r="A139" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B138),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C05.Fair1", Loan_C05_Pricer, Loan_C05_Trade, Loan_Context, Loan_Request1)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Request1, , Loan_C05_Pricer)</v>
       </c>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -6249,22 +5893,22 @@
     </row>
     <row r="144" spans="1:3" ht="24" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="38" customHeight="1">
       <c r="A146" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B146" s="10" cm="1" t="str">
         <f t="array" ref="B146">_xll.QS.LOAN.SETTINGS("Loan.C06.Options",,Loan_C06_Setting_amortizationrate,,,,,,,,Loan_C06_Setting_floor,Loan_C06_Setting_cap)</f>
         <v/>
       </c>
       <c r="C146" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="34" customHeight="1">
       <c r="A147" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B146),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C06.Options", , Loan_C06_Setting_amortizationrate, , , , , , , , Loan_C06_Setting_floor, Loan_C06_Setting_cap)</v>
@@ -6272,9 +5916,9 @@
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
     </row>
-    <row r="149" spans="1:3" ht="38.25" customHeight="1">
+    <row r="149" spans="1:3" ht="38" customHeight="1">
       <c r="A149" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B149" s="10" cm="1" t="str">
         <f t="array" ref="B149">_xll.QS.INSTRUMENT.LOAN("Loan.C06.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C06_Rate,Loan_C06_Index,Loan_C06_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C06_Options,,,)</f>
@@ -6292,19 +5936,19 @@
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
     </row>
-    <row r="152" spans="1:3" ht="38.25" customHeight="1">
+    <row r="152" spans="1:3" ht="38" customHeight="1">
       <c r="A152" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B152" s="10" cm="1" t="str">
         <f t="array" ref="B152">_xll.QS.TRADE.CREATE("Loan.C06.Trade",Loan_C06_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C152" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="34" customHeight="1">
       <c r="A153" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B152),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C06.Trade", Loan_C06_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6312,19 +5956,19 @@
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
     </row>
-    <row r="155" spans="1:3" ht="38.25" customHeight="1">
+    <row r="155" spans="1:3" ht="38" customHeight="1">
       <c r="A155" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B155" s="10">
         <f>IF(Loan_C06_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C155" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="34" customHeight="1">
       <c r="A156" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B155),",",", ")</f>
         <v>=IF(Loan_C06_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6332,22 +5976,22 @@
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
     </row>
-    <row r="158" spans="1:3" ht="38.25" customHeight="1">
+    <row r="158" spans="1:3" ht="38" customHeight="1">
       <c r="A158" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B158" s="10" cm="1" t="str">
-        <f t="array" ref="B158">_xll.QS.EVALUATE("Loan.C06.Result",Loan_C06_Pricer,Loan_C06_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B158">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C06_Trade,Loan_Requests,,Loan_C06_Pricer)</f>
         <v/>
       </c>
       <c r="C158" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="34" customHeight="1">
       <c r="A159" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B158),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C06.Result", Loan_C06_Pricer, Loan_C06_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C06_Trade, Loan_Requests, , Loan_C06_Pricer)</v>
       </c>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -6361,22 +6005,22 @@
     </row>
     <row r="164" spans="1:3" ht="24" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="38" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B166" s="10" cm="1" t="str">
         <f t="array" ref="B166">_xll.QS.LOAN.SETTINGS("Loan.C07.Options",,,,,,,,,,,,,,Loan_C07_Setting_annualcpr)</f>
         <v/>
       </c>
       <c r="C166" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="34" customHeight="1">
       <c r="A167" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B166),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C07.Options", , , , , , , , , , , , , , Loan_C07_Setting_annualcpr)</v>
@@ -6384,9 +6028,9 @@
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
     </row>
-    <row r="169" spans="1:3" ht="38.25" customHeight="1">
+    <row r="169" spans="1:3" ht="38" customHeight="1">
       <c r="A169" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B169" s="10" cm="1" t="str">
         <f t="array" ref="B169">_xll.QS.INSTRUMENT.LOAN("Loan.C07.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C07_Rate,Loan_C07_Index,Loan_C07_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C07_Options,,,)</f>
@@ -6404,19 +6048,19 @@
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
     </row>
-    <row r="172" spans="1:3" ht="38.25" customHeight="1">
+    <row r="172" spans="1:3" ht="38" customHeight="1">
       <c r="A172" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B172" s="10" cm="1" t="str">
         <f t="array" ref="B172">_xll.QS.TRADE.CREATE("Loan.C07.Trade",Loan_C07_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C172" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="34" customHeight="1">
       <c r="A173" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B172),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C07.Trade", Loan_C07_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6424,19 +6068,19 @@
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
     </row>
-    <row r="175" spans="1:3" ht="38.25" customHeight="1">
+    <row r="175" spans="1:3" ht="38" customHeight="1">
       <c r="A175" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B175" s="10">
         <f>IF(Loan_C07_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C175" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="34" customHeight="1">
       <c r="A176" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B175),",",", ")</f>
         <v>=IF(Loan_C07_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6444,42 +6088,42 @@
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
     </row>
-    <row r="178" spans="1:3" ht="38.25" customHeight="1">
+    <row r="178" spans="1:3" ht="38" customHeight="1">
       <c r="A178" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B178" s="10" cm="1" t="str">
-        <f t="array" ref="B178">_xll.QS.EVALUATE("Loan.C07.Result",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B178">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C07_Trade,Loan_Requests,,Loan_C07_Pricer)</f>
         <v/>
       </c>
       <c r="C178" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="34" customHeight="1">
       <c r="A179" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B178),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C07.Result", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C07_Trade, Loan_Requests, , Loan_C07_Pricer)</v>
       </c>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
     </row>
-    <row r="181" spans="1:3" ht="38.25" customHeight="1">
+    <row r="181" spans="1:3" ht="38" customHeight="1">
       <c r="A181" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B181" s="10" cm="1" t="str">
-        <f t="array" ref="B181">_xll.QS.EVALUATE("Loan.C07.Fair0",Loan_C07_Pricer,Loan_C07_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B181">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C07_Trade,Loan_Request0,,Loan_C07_Pricer)</f>
         <v/>
       </c>
       <c r="C181" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="34" customHeight="1">
       <c r="A182" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B181),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C07.Fair0", Loan_C07_Pricer, Loan_C07_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C07_Trade, Loan_Request0, , Loan_C07_Pricer)</v>
       </c>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -6493,22 +6137,22 @@
     </row>
     <row r="187" spans="1:3" ht="24" customHeight="1">
       <c r="A187" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="38" customHeight="1">
       <c r="A189" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B189" s="10" cm="1" t="str">
         <f t="array" ref="B189">_xll.QS.LOAN.SETTINGS("Loan.C08.Options",,,Loan_C08_Setting_creditindex,Loan_C08_Setting_recovery)</f>
         <v/>
       </c>
       <c r="C189" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="34" customHeight="1">
       <c r="A190" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B189),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C08.Options", , , Loan_C08_Setting_creditindex, Loan_C08_Setting_recovery)</v>
@@ -6516,9 +6160,9 @@
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
     </row>
-    <row r="192" spans="1:3" ht="38.25" customHeight="1">
+    <row r="192" spans="1:3" ht="38" customHeight="1">
       <c r="A192" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B192" s="10" cm="1" t="str">
         <f t="array" ref="B192">_xll.QS.INSTRUMENT.LOAN("Loan.C08.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C08_Rate,Loan_C08_Index,Loan_C08_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C08_Options,,,)</f>
@@ -6536,19 +6180,19 @@
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
     </row>
-    <row r="195" spans="1:3" ht="38.25" customHeight="1">
+    <row r="195" spans="1:3" ht="38" customHeight="1">
       <c r="A195" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B195" s="10" cm="1" t="str">
         <f t="array" ref="B195">_xll.QS.TRADE.CREATE("Loan.C08.Trade",Loan_C08_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C195" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="34" customHeight="1">
       <c r="A196" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B195),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C08.Trade", Loan_C08_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6556,19 +6200,19 @@
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
     </row>
-    <row r="198" spans="1:3" ht="38.25" customHeight="1">
+    <row r="198" spans="1:3" ht="38" customHeight="1">
       <c r="A198" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B198" s="10">
         <f>IF(Loan_C08_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C198" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="34" customHeight="1">
       <c r="A199" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B198),",",", ")</f>
         <v>=IF(Loan_C08_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6576,42 +6220,42 @@
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
     </row>
-    <row r="201" spans="1:3" ht="38.25" customHeight="1">
+    <row r="201" spans="1:3" ht="38" customHeight="1">
       <c r="A201" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B201" s="10" cm="1" t="str">
-        <f t="array" ref="B201">_xll.QS.EVALUATE("Loan.C08.Result",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B201">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C08_Trade,Loan_Requests,,Loan_C08_Pricer)</f>
         <v/>
       </c>
       <c r="C201" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="34" customHeight="1">
       <c r="A202" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B201),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C08.Result", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C08_Trade, Loan_Requests, , Loan_C08_Pricer)</v>
       </c>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
     </row>
-    <row r="204" spans="1:3" ht="38.25" customHeight="1">
+    <row r="204" spans="1:3" ht="38" customHeight="1">
       <c r="A204" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B204" s="10" cm="1" t="str">
-        <f t="array" ref="B204">_xll.QS.EVALUATE("Loan.C08.Fair0",Loan_C08_Pricer,Loan_C08_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B204">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C08_Trade,Loan_Request0,,Loan_C08_Pricer)</f>
         <v/>
       </c>
       <c r="C204" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="34" customHeight="1">
       <c r="A205" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B204),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C08.Fair0", Loan_C08_Pricer, Loan_C08_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C08_Trade, Loan_Request0, , Loan_C08_Pricer)</v>
       </c>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -6625,12 +6269,12 @@
     </row>
     <row r="210" spans="1:3" ht="24" customHeight="1">
       <c r="A210" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="38" customHeight="1">
       <c r="A212" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B212" s="10" cm="1" t="str">
         <f t="array" ref="B212">_xll.QS.INSTRUMENT.LOAN("Loan.C09.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C09_Rate,Loan_C09_Index,Loan_C09_Repayment,Loan_Frequency,Loan_DayCounter,,,,)</f>
@@ -6648,19 +6292,19 @@
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
     </row>
-    <row r="215" spans="1:3" ht="38.25" customHeight="1">
+    <row r="215" spans="1:3" ht="38" customHeight="1">
       <c r="A215" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B215" s="10" cm="1" t="str">
         <f t="array" ref="B215">_xll.QS.TRADE.CREATE("Loan.C09.Trade",Loan_C09_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C215" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="34" customHeight="1">
       <c r="A216" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B215),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C09.Trade", Loan_C09_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6668,19 +6312,19 @@
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
     </row>
-    <row r="218" spans="1:3" ht="38.25" customHeight="1">
+    <row r="218" spans="1:3" ht="38" customHeight="1">
       <c r="A218" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B218" s="10">
         <f>IF(Loan_C09_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C218" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="34" customHeight="1">
       <c r="A219" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B218),",",", ")</f>
         <v>=IF(Loan_C09_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6688,42 +6332,42 @@
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
     </row>
-    <row r="221" spans="1:3" ht="38.25" customHeight="1">
+    <row r="221" spans="1:3" ht="38" customHeight="1">
       <c r="A221" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B221" s="10" cm="1" t="str">
-        <f t="array" ref="B221">_xll.QS.EVALUATE("Loan.C09.Result",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B221">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C09_Trade,Loan_Requests,,Loan_C09_Pricer)</f>
         <v/>
       </c>
       <c r="C221" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="34" customHeight="1">
       <c r="A222" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B221),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C09.Result", Loan_C09_Pricer, Loan_C09_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C09_Trade, Loan_Requests, , Loan_C09_Pricer)</v>
       </c>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
     </row>
-    <row r="224" spans="1:3" ht="38.25" customHeight="1">
+    <row r="224" spans="1:3" ht="38" customHeight="1">
       <c r="A224" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B224" s="10" cm="1" t="str">
-        <f t="array" ref="B224">_xll.QS.EVALUATE("Loan.C09.Fair0",Loan_C09_Pricer,Loan_C09_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B224">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C09_Trade,Loan_Request0,,Loan_C09_Pricer)</f>
         <v/>
       </c>
       <c r="C224" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="34" customHeight="1">
       <c r="A225" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B224),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C09.Fair0", Loan_C09_Pricer, Loan_C09_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C09_Trade, Loan_Request0, , Loan_C09_Pricer)</v>
       </c>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6737,22 +6381,22 @@
     </row>
     <row r="230" spans="1:3" ht="24" customHeight="1">
       <c r="A230" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="38" customHeight="1">
       <c r="A232" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B232" s="10" cm="1" t="str">
         <f t="array" ref="B232">_xll.QS.LOAN.SETTINGS("Loan.C10.Options",,Loan_C10_Setting_amortizationrate)</f>
         <v/>
       </c>
       <c r="C232" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="33.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="34" customHeight="1">
       <c r="A233" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B232),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C10.Options", , Loan_C10_Setting_amortizationrate)</v>
@@ -6760,9 +6404,9 @@
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
     </row>
-    <row r="235" spans="1:3" ht="38.25" customHeight="1">
+    <row r="235" spans="1:3" ht="38" customHeight="1">
       <c r="A235" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B235" s="10" cm="1" t="str">
         <f t="array" ref="B235">_xll.QS.INSTRUMENT.LOAN("Loan.C10.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C10_Rate,Loan_C10_Index,Loan_C10_Repayment,Loan_Frequency,Loan_DayCounter,Loan_C10_Options,,,)</f>
@@ -6780,19 +6424,19 @@
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
     </row>
-    <row r="238" spans="1:3" ht="38.25" customHeight="1">
+    <row r="238" spans="1:3" ht="38" customHeight="1">
       <c r="A238" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B238" s="10" cm="1" t="str">
         <f t="array" ref="B238">_xll.QS.TRADE.CREATE("Loan.C10.Trade",Loan_C10_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C238" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="34" customHeight="1">
       <c r="A239" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B238),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C10.Trade", Loan_C10_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6800,19 +6444,19 @@
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
     </row>
-    <row r="241" spans="1:3" ht="38.25" customHeight="1">
+    <row r="241" spans="1:3" ht="38" customHeight="1">
       <c r="A241" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B241" s="10">
         <f>IF(Loan_C10_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C241" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="34" customHeight="1">
       <c r="A242" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B241),",",", ")</f>
         <v>=IF(Loan_C10_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6820,42 +6464,42 @@
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
     </row>
-    <row r="244" spans="1:3" ht="38.25" customHeight="1">
+    <row r="244" spans="1:3" ht="38" customHeight="1">
       <c r="A244" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B244" s="10" cm="1" t="str">
-        <f t="array" ref="B244">_xll.QS.EVALUATE("Loan.C10.Result",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B244">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C10_Trade,Loan_Requests,,Loan_C10_Pricer)</f>
         <v/>
       </c>
       <c r="C244" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="34" customHeight="1">
       <c r="A245" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B244),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C10.Result", Loan_C10_Pricer, Loan_C10_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C10_Trade, Loan_Requests, , Loan_C10_Pricer)</v>
       </c>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
     </row>
-    <row r="247" spans="1:3" ht="38.25" customHeight="1">
+    <row r="247" spans="1:3" ht="38" customHeight="1">
       <c r="A247" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B247" s="10" cm="1" t="str">
-        <f t="array" ref="B247">_xll.QS.EVALUATE("Loan.C10.Fair0",Loan_C10_Pricer,Loan_C10_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B247">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C10_Trade,Loan_Request0,,Loan_C10_Pricer)</f>
         <v/>
       </c>
       <c r="C247" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="34" customHeight="1">
       <c r="A248" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B247),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C10.Fair0", Loan_C10_Pricer, Loan_C10_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C10_Trade, Loan_Request0, , Loan_C10_Pricer)</v>
       </c>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6869,12 +6513,12 @@
     </row>
     <row r="253" spans="1:3" ht="24" customHeight="1">
       <c r="A253" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="38" customHeight="1">
       <c r="A255" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B255" s="10" cm="1" t="str">
         <f t="array" ref="B255">_xll.QS.INSTRUMENT.LOAN("Loan.C11.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C11_Rate,Loan_C11_Index,Loan_C11_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C11_CouponPeriods,Loan_C11_CouponRates,Loan_C11_CouponIndices)</f>
@@ -6892,19 +6536,19 @@
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
     </row>
-    <row r="258" spans="1:3" ht="38.25" customHeight="1">
+    <row r="258" spans="1:3" ht="38" customHeight="1">
       <c r="A258" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B258" s="10" cm="1" t="str">
         <f t="array" ref="B258">_xll.QS.TRADE.CREATE("Loan.C11.Trade",Loan_C11_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C258" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="34" customHeight="1">
       <c r="A259" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B258),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C11.Trade", Loan_C11_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6912,19 +6556,19 @@
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
     </row>
-    <row r="261" spans="1:3" ht="38.25" customHeight="1">
+    <row r="261" spans="1:3" ht="38" customHeight="1">
       <c r="A261" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B261" s="10">
         <f>IF(Loan_C11_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C261" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="34" customHeight="1">
       <c r="A262" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B261),",",", ")</f>
         <v>=IF(Loan_C11_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6932,82 +6576,82 @@
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
     </row>
-    <row r="264" spans="1:3" ht="38.25" customHeight="1">
+    <row r="264" spans="1:3" ht="38" customHeight="1">
       <c r="A264" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B264" s="10" cm="1" t="str">
-        <f t="array" ref="B264">_xll.QS.EVALUATE("Loan.C11.Result",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B264">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C11_Trade,Loan_Requests,,Loan_C11_Pricer)</f>
         <v/>
       </c>
       <c r="C264" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="34" customHeight="1">
       <c r="A265" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B264),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Result", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Requests, , Loan_C11_Pricer)</v>
       </c>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
     </row>
-    <row r="267" spans="1:3" ht="38.25" customHeight="1">
+    <row r="267" spans="1:3" ht="38" customHeight="1">
       <c r="A267" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B267" s="10" cm="1" t="str">
-        <f t="array" ref="B267">_xll.QS.EVALUATE("Loan.C11.Fair0",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B267">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C11_Trade,Loan_Request0,,Loan_C11_Pricer)</f>
         <v/>
       </c>
       <c r="C267" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="34" customHeight="1">
       <c r="A268" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B267),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair0", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request0, , Loan_C11_Pricer)</v>
       </c>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
     </row>
-    <row r="270" spans="1:3" ht="38.25" customHeight="1">
+    <row r="270" spans="1:3" ht="38" customHeight="1">
       <c r="A270" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B270" s="10" cm="1" t="str">
-        <f t="array" ref="B270">_xll.QS.EVALUATE("Loan.C11.Fair1",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request1)</f>
+        <f t="array" ref="B270">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C11_Trade,Loan_Request1,,Loan_C11_Pricer)</f>
         <v/>
       </c>
       <c r="C270" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="34" customHeight="1">
       <c r="A271" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B270),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair1", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request1)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request1, , Loan_C11_Pricer)</v>
       </c>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
     </row>
-    <row r="273" spans="1:3" ht="38.25" customHeight="1">
+    <row r="273" spans="1:3" ht="38" customHeight="1">
       <c r="A273" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B273" s="10" cm="1" t="str">
-        <f t="array" ref="B273">_xll.QS.EVALUATE("Loan.C11.Fair2",Loan_C11_Pricer,Loan_C11_Trade,Loan_Context,Loan_Request2)</f>
+        <f t="array" ref="B273">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C11_Trade,Loan_Request2,,Loan_C11_Pricer)</f>
         <v/>
       </c>
       <c r="C273" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="34" customHeight="1">
       <c r="A274" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B273),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C11.Fair2", Loan_C11_Pricer, Loan_C11_Trade, Loan_Context, Loan_Request2)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request2, , Loan_C11_Pricer)</v>
       </c>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7021,12 +6665,12 @@
     </row>
     <row r="279" spans="1:3" ht="24" customHeight="1">
       <c r="A279" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" ht="38.25" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="38" customHeight="1">
       <c r="A281" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B281" s="10" cm="1" t="str">
         <f t="array" ref="B281">_xll.QS.INSTRUMENT.LOAN("Loan.C12.Instrument",Loan_Start,Loan_Maturity,Loan_Currency,Loan_Notional,Loan_C12_Rate,Loan_C12_Index,Loan_C12_Repayment,Loan_Frequency,Loan_DayCounter,,Loan_C12_CouponPeriods,Loan_C12_CouponRates,Loan_C12_CouponIndices)</f>
@@ -7044,19 +6688,19 @@
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
     </row>
-    <row r="284" spans="1:3" ht="38.25" customHeight="1">
+    <row r="284" spans="1:3" ht="38" customHeight="1">
       <c r="A284" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B284" s="10" cm="1" t="str">
         <f t="array" ref="B284">_xll.QS.TRADE.CREATE("Loan.C12.Trade",Loan_C12_Instrument,Loan_ValuationDate,Loan_Side)</f>
         <v/>
       </c>
       <c r="C284" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" ht="33.75" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="34" customHeight="1">
       <c r="A285" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B284),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C12.Trade", Loan_C12_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -7064,19 +6708,19 @@
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
     </row>
-    <row r="287" spans="1:3" ht="38.25" customHeight="1">
+    <row r="287" spans="1:3" ht="38" customHeight="1">
       <c r="A287" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B287" s="10">
         <f>IF(Loan_C12_Discount="FUNDING",Loan_FundingPricer,Loan_RiskFreePricer)</f>
         <v/>
       </c>
       <c r="C287" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" ht="33.75" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="34" customHeight="1">
       <c r="A288" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B287),",",", ")</f>
         <v>=IF(Loan_C12_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -7084,92 +6728,92 @@
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
     </row>
-    <row r="290" spans="1:3" ht="38.25" customHeight="1">
+    <row r="290" spans="1:3" ht="38" customHeight="1">
       <c r="A290" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B290" s="10" cm="1" t="str">
-        <f t="array" ref="B290">_xll.QS.EVALUATE("Loan.C12.Result",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Requests)</f>
+        <f t="array" ref="B290">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C12_Trade,Loan_Requests,,Loan_C12_Pricer)</f>
         <v/>
       </c>
       <c r="C290" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" ht="33.75" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="34" customHeight="1">
       <c r="A291" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B290),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Result", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Requests)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Requests, , Loan_C12_Pricer)</v>
       </c>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
     </row>
-    <row r="293" spans="1:3" ht="38.25" customHeight="1">
+    <row r="293" spans="1:3" ht="38" customHeight="1">
       <c r="A293" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B293" s="10" cm="1" t="str">
-        <f t="array" ref="B293">_xll.QS.EVALUATE("Loan.C12.Fair0",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request0)</f>
+        <f t="array" ref="B293">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C12_Trade,Loan_Request0,,Loan_C12_Pricer)</f>
         <v/>
       </c>
       <c r="C293" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="34" customHeight="1">
       <c r="A294" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B293),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair0", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request0)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request0, , Loan_C12_Pricer)</v>
       </c>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
     </row>
-    <row r="296" spans="1:3" ht="38.25" customHeight="1">
+    <row r="296" spans="1:3" ht="38" customHeight="1">
       <c r="A296" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B296" s="10" cm="1" t="str">
-        <f t="array" ref="B296">_xll.QS.EVALUATE("Loan.C12.Fair1",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request1)</f>
+        <f t="array" ref="B296">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C12_Trade,Loan_Request1,,Loan_C12_Pricer)</f>
         <v/>
       </c>
       <c r="C296" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="34" customHeight="1">
       <c r="A297" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B296),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair1", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request1)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request1, , Loan_C12_Pricer)</v>
       </c>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
     </row>
-    <row r="299" spans="1:3" ht="38.25" customHeight="1">
+    <row r="299" spans="1:3" ht="38" customHeight="1">
       <c r="A299" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B299" s="10" cm="1" t="str">
-        <f t="array" ref="B299">_xll.QS.EVALUATE("Loan.C12.Fair2",Loan_C12_Pricer,Loan_C12_Trade,Loan_Context,Loan_Request2)</f>
+        <f t="array" ref="B299">_xll.QS.EVALUATE.RESULTS(Loan_Context,Loan_C12_Trade,Loan_Request2,,Loan_C12_Pricer)</f>
         <v/>
       </c>
       <c r="C299" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" ht="33.75" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="34" customHeight="1">
       <c r="A300" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B299),",",", ")</f>
-        <v>=QS.EVALUATE("Loan.C12.Fair2", Loan_C12_Pricer, Loan_C12_Trade, Loan_Context, Loan_Request2)</v>
+        <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request2, , Loan_C12_Pricer)</v>
       </c>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
     </row>
     <row r="304" spans="1:3" ht="36" customHeight="1">
       <c r="A304" s="5" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C304" s="5"/>
     </row>
@@ -7193,7 +6837,7 @@
     </row>
     <row r="307" spans="1:3" ht="24" customHeight="1">
       <c r="A307" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B307" s="10">
         <f>Loan_C03_Result</f>
@@ -7202,7 +6846,7 @@
     </row>
     <row r="308" spans="1:3" ht="24" customHeight="1">
       <c r="A308" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B308" s="10">
         <f>Loan_C04_Result</f>
@@ -7211,7 +6855,7 @@
     </row>
     <row r="309" spans="1:3" ht="24" customHeight="1">
       <c r="A309" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B309" s="10">
         <f>Loan_C05_Result</f>
@@ -7220,7 +6864,7 @@
     </row>
     <row r="310" spans="1:3" ht="24" customHeight="1">
       <c r="A310" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B310" s="10">
         <f>Loan_C06_Result</f>
@@ -7229,7 +6873,7 @@
     </row>
     <row r="311" spans="1:3" ht="24" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B311" s="10">
         <f>Loan_C07_Result</f>
@@ -7238,7 +6882,7 @@
     </row>
     <row r="312" spans="1:3" ht="24" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B312" s="10">
         <f>Loan_C08_Result</f>
@@ -7247,7 +6891,7 @@
     </row>
     <row r="313" spans="1:3" ht="24" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B313" s="10">
         <f>Loan_C09_Result</f>
@@ -7256,7 +6900,7 @@
     </row>
     <row r="314" spans="1:3" ht="24" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B314" s="10">
         <f>Loan_C10_Result</f>
@@ -7265,7 +6909,7 @@
     </row>
     <row r="315" spans="1:3" ht="24" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B315" s="10">
         <f>Loan_C11_Result</f>
@@ -7274,26 +6918,26 @@
     </row>
     <row r="316" spans="1:3" ht="24" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B316" s="10">
         <f>Loan_C12_Result</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="38.25" customHeight="1">
+    <row r="319" spans="1:3" ht="38" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B319" s="10">
         <f>INDEX(Loan_ResultHandles,MATCH(Loan_SelectedCase,Loan_CaseNames,0))</f>
         <v/>
       </c>
       <c r="C319" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="33.75" customHeight="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="34" customHeight="1">
       <c r="A320" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B319),",",", ")</f>
         <v>=INDEX(Loan_ResultHandles, MATCH(Loan_SelectedCase, Loan_CaseNames, 0))</v>
@@ -7438,9 +7082,9 @@
     <col min="7" max="8" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.25" customHeight="1">
+    <row r="1" spans="1:8" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7452,7 +7096,7 @@
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7477,36 +7121,36 @@
         <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="33.75" customHeight="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="34" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
@@ -7525,13 +7169,13 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="34" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -7550,15 +7194,15 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="34" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B9" s="15" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.RESULT.VALUE(Loan_C03_Result)</f>
@@ -7575,15 +7219,15 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="34" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B10" s="15" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.RESULT.VALUE(Loan_C04_Result)</f>
@@ -7600,15 +7244,15 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="34" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B11" s="15" cm="1" t="str">
         <f t="array" ref="B11">_xll.QS.RESULT.VALUE(Loan_C05_Result)</f>
@@ -7628,15 +7272,15 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="34" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B12" s="15" cm="1" t="str">
         <f t="array" ref="B12">_xll.QS.RESULT.VALUE(Loan_C06_Result)</f>
@@ -7647,20 +7291,20 @@
         <v/>
       </c>
       <c r="D12" s="7" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="34" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B13" s="15" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.RESULT.VALUE(Loan_C07_Result)</f>
@@ -7677,15 +7321,15 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="34" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B14" s="15" cm="1" t="str">
         <f t="array" ref="B14">_xll.QS.RESULT.VALUE(Loan_C08_Result)</f>
@@ -7702,15 +7346,15 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="34" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B15" s="15" cm="1" t="str">
         <f t="array" ref="B15">_xll.QS.RESULT.VALUE(Loan_C09_Result)</f>
@@ -7727,15 +7371,15 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="34" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B16" s="15" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.RESULT.VALUE(Loan_C10_Result)</f>
@@ -7752,15 +7396,15 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="34" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B17" s="15" cm="1" t="str">
         <f t="array" ref="B17">_xll.QS.RESULT.VALUE(Loan_C11_Result)</f>
@@ -7783,15 +7427,15 @@
         <v/>
       </c>
       <c r="G17" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="33.75" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="34" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B18" s="15" cm="1" t="str">
         <f t="array" ref="B18">_xll.QS.RESULT.VALUE(Loan_C12_Result)</f>
@@ -7814,21 +7458,21 @@
         <v/>
       </c>
       <c r="G18" s="6" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -7842,7 +7486,7 @@
     </row>
     <row r="26" spans="1:8" ht="24" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -7939,9 +7583,9 @@
     <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1">
+    <row r="1" spans="1:9" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7954,7 +7598,7 @@
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7981,19 +7625,19 @@
         <v>42</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B6" s="9">
         <f>Loan_SelectedCase</f>
         <v/>
       </c>
       <c r="C6" s="6" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1">
@@ -8034,16 +7678,16 @@
     <col min="3" max="3" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8058,19 +7702,19 @@
         <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="24" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B6" s="9">
         <f>Loan_SelectedCase</f>
         <v/>
       </c>
       <c r="C6" s="6" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1">
@@ -8112,9 +7756,9 @@
     <col min="5" max="6" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38.25" customHeight="1">
+    <row r="1" spans="1:6" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8124,7 +7768,7 @@
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8147,7 +7791,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -8163,7 +7807,7 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -8179,7 +7823,7 @@
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -8195,7 +7839,7 @@
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>

--- a/bindings/excel/examples/loan_pricing_example.xlsx
+++ b/bindings/excel/examples/loan_pricing_example.xlsx
@@ -2851,7 +2851,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -2878,7 +2878,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="26" customHeight="1">
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="26" customHeight="1">
+    <row r="4" spans="1:6" ht="26.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2896,7 +2896,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="26" customHeight="1">
+    <row r="6" spans="1:6" ht="26.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -2906,7 +2906,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="26" customHeight="1">
+    <row r="7" spans="1:6" ht="26.25" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2914,7 +2914,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="26" customHeight="1">
+    <row r="9" spans="1:6" ht="26.25" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
@@ -2924,7 +2924,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="34" customHeight="1">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="34" customHeight="1">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -2952,7 +2952,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="34" customHeight="1">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -2966,7 +2966,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="34" customHeight="1">
+    <row r="13" spans="1:6" ht="33.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -2980,7 +2980,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="34" customHeight="1">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -2994,7 +2994,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="34" customHeight="1">
+    <row r="15" spans="1:6" ht="33.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="34" customHeight="1">
+    <row r="16" spans="1:6" ht="33.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="34" customHeight="1">
+    <row r="17" spans="1:6" ht="33.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="26" customHeight="1">
+    <row r="20" spans="1:6" ht="26.25" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
@@ -3082,7 +3082,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="26" customHeight="1">
+    <row r="25" spans="1:6" ht="26.25" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -3092,7 +3092,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" ht="34" customHeight="1">
+    <row r="26" spans="1:6" ht="33.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -3102,7 +3102,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="34" customHeight="1">
+    <row r="27" spans="1:6" ht="33.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
@@ -3112,7 +3112,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" ht="34" customHeight="1">
+    <row r="28" spans="1:6" ht="33.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -3122,7 +3122,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="30" spans="1:6" ht="26" customHeight="1">
+    <row r="30" spans="1:6" ht="26.25" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>39</v>
       </c>
@@ -3132,7 +3132,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" ht="26" customHeight="1">
+    <row r="31" spans="1:6" ht="26.25" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3204,7 +3204,7 @@
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32" customHeight="1">
+    <row r="7" spans="1:3" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" customHeight="1">
+    <row r="8" spans="1:3" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32" customHeight="1">
+    <row r="9" spans="1:3" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" customHeight="1">
+    <row r="10" spans="1:3" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1">
+    <row r="11" spans="1:3" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32" customHeight="1">
+    <row r="12" spans="1:3" ht="32.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="32" customHeight="1">
+    <row r="13" spans="1:3" ht="32.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="32" customHeight="1">
+    <row r="14" spans="1:3" ht="32.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="32" customHeight="1">
+    <row r="15" spans="1:3" ht="32.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>67</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="32" customHeight="1">
+    <row r="16" spans="1:3" ht="32.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -3444,7 +3444,7 @@
     <col min="6" max="6" width="22.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38" customHeight="1">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -4672,7 +4672,7 @@
     <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="38" customHeight="1">
+    <row r="1" spans="1:4" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>135</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>0.017</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="32" customHeight="1">
+    <row r="27" spans="1:4" ht="32.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>157</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="38" customHeight="1">
+    <row r="32" spans="1:4" ht="38.25" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>162</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="34" customHeight="1">
+    <row r="33" spans="1:3" ht="33.75" customHeight="1">
       <c r="A33" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B32),",",", ")</f>
         <v>=QS.CONTEXT.CREATE("Loan.Root", Loan_ValuationDate, "EUR", "ESTR")</v>
@@ -4908,7 +4908,7 @@
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
     </row>
-    <row r="35" spans="1:3" ht="38" customHeight="1">
+    <row r="35" spans="1:3" ht="38.25" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>164</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="34" customHeight="1">
+    <row r="36" spans="1:3" ht="33.75" customHeight="1">
       <c r="A36" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
         <v>=QS.CONTEXT.ADD.CREDIT.CURVE(Loan_Root, "Credit:BORROWER", "EUR", "ESTR", Loan_Recovery, Loan_CreditQuotes, Loan_CreditMid)</v>
@@ -4928,67 +4928,67 @@
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
     </row>
-    <row r="38" spans="1:3" ht="38" customHeight="1">
+    <row r="38" spans="1:3" ht="38.25" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>166</v>
       </c>
       <c r="B38" s="10" cm="1" t="str">
-        <f t="array" ref="B38">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"ESTR",Loan_Pillars,Loan_ZeroRates,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
+        <f t="array" ref="B38">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"ESTR",Loan_Pillars,Loan_ZeroRates,"Actual360","Continuous","Annual","Linear",TRUE)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="34" customHeight="1">
+    <row r="39" spans="1:3" ht="33.75" customHeight="1">
       <c r="A39" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B38),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "ESTR", Loan_Pillars, Loan_ZeroRates, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "ESTR", Loan_Pillars, Loan_ZeroRates, "Actual360", "Continuous", "Annual", "Linear", TRUE)</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
     </row>
-    <row r="41" spans="1:3" ht="38" customHeight="1">
+    <row r="41" spans="1:3" ht="38.25" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>168</v>
       </c>
       <c r="B41" s="10" cm="1" t="str">
-        <f t="array" ref="B41">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"EURIBOR12m",Loan_Pillars,Loan_ForwardRates,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
+        <f t="array" ref="B41">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"EURIBOR12m",Loan_Pillars,Loan_ForwardRates,"Actual360","Continuous","Annual","Linear",TRUE)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="34" customHeight="1">
+    <row r="42" spans="1:3" ht="33.75" customHeight="1">
       <c r="A42" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B41),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "EURIBOR12m", Loan_Pillars, Loan_ForwardRates, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "EURIBOR12m", Loan_Pillars, Loan_ForwardRates, "Actual360", "Continuous", "Annual", "Linear", TRUE)</v>
       </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
     </row>
-    <row r="44" spans="1:3" ht="38" customHeight="1">
+    <row r="44" spans="1:3" ht="38.25" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>169</v>
       </c>
       <c r="B44" s="10" cm="1" t="str">
-        <f t="array" ref="B44">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"FUNDINGSPREAD",Loan_Pillars,Loan_FundingSpreads,"Actual360","Linear",TRUE,"Continuous","Annual")</f>
+        <f t="array" ref="B44">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root,"FUNDINGSPREAD",Loan_Pillars,Loan_FundingSpreads,"Actual360","Continuous","Annual","Linear",TRUE)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="34" customHeight="1">
+    <row r="45" spans="1:3" ht="33.75" customHeight="1">
       <c r="A45" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B44),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "FUNDINGSPREAD", Loan_Pillars, Loan_FundingSpreads, "Actual360", "Linear", TRUE, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Loan_Root, "FUNDINGSPREAD", Loan_Pillars, Loan_FundingSpreads, "Actual360", "Continuous", "Annual", "Linear", TRUE)</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
     </row>
-    <row r="47" spans="1:3" ht="38" customHeight="1">
+    <row r="47" spans="1:3" ht="38.25" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>170</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="34" customHeight="1">
+    <row r="48" spans="1:3" ht="33.75" customHeight="1">
       <c r="A48" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B47),",",", ")</f>
         <v>=QS.CONTEXT.ADD.COMPOSITE.CURVE(Loan_Root, "FUNDING", "EURIBOR12m", "FUNDINGSPREAD")</v>
@@ -5046,7 +5046,7 @@
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38" customHeight="1">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>177</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="34" customHeight="1">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
       <c r="A8" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
         <v>=QS.CONTEXT.PREPARE("Loan.Context", Loan_Root, Loan_MarketInputs)</v>
@@ -5104,7 +5104,7 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="10" spans="1:3" ht="38" customHeight="1">
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>179</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="34" customHeight="1">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
       <c r="A11" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.RiskFreePolicy", Loan_RiskFreeCurrency, Loan_RiskFreeIndex)</v>
@@ -5124,7 +5124,7 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="13" spans="1:3" ht="38" customHeight="1">
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>181</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="34" customHeight="1">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
       <c r="A14" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.RiskFreePricer", "LoanPricer", Loan_RiskFreePolicy)</v>
@@ -5144,7 +5144,7 @@
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="16" spans="1:3" ht="38" customHeight="1">
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>183</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="34" customHeight="1">
+    <row r="17" spans="1:3" ht="33.75" customHeight="1">
       <c r="A17" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.FIXED.INCOME("Loan.FundingPolicy", Loan_FundingCurrency, Loan_FundingIndex)</v>
@@ -5164,7 +5164,7 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
     </row>
-    <row r="19" spans="1:3" ht="38" customHeight="1">
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>184</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="34" customHeight="1">
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
       <c r="A20" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.PRICER.CREATE("Loan.FundingPricer", "LoanPricer", Loan_FundingPolicy)</v>
@@ -5184,7 +5184,7 @@
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
     </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1">
+    <row r="22" spans="1:3" ht="38.25" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>185</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="34" customHeight="1">
+    <row r="23" spans="1:3" ht="33.75" customHeight="1">
       <c r="A23" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
         <v>=QS.CURVE.GET(Loan_Context, "ESTR")</v>
@@ -5204,7 +5204,7 @@
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
-    <row r="25" spans="1:3" ht="38" customHeight="1">
+    <row r="25" spans="1:3" ht="38.25" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>187</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="34" customHeight="1">
+    <row r="26" spans="1:3" ht="33.75" customHeight="1">
       <c r="A26" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(0)</v>
@@ -5224,7 +5224,7 @@
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="28" spans="1:3" ht="38" customHeight="1">
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>189</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="34" customHeight="1">
+    <row r="29" spans="1:3" ht="33.75" customHeight="1">
       <c r="A29" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(1)</v>
@@ -5244,7 +5244,7 @@
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
     </row>
-    <row r="31" spans="1:3" ht="38" customHeight="1">
+    <row r="31" spans="1:3" ht="38.25" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>190</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="34" customHeight="1">
+    <row r="32" spans="1:3" ht="33.75" customHeight="1">
       <c r="A32" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
         <v>=QS.REQUEST.FAIR.RATE(2)</v>
@@ -5276,7 +5276,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="38" customHeight="1">
+    <row r="37" spans="1:3" ht="38.25" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>192</v>
       </c>
@@ -5296,7 +5296,7 @@
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="40" spans="1:3" ht="38" customHeight="1">
+    <row r="40" spans="1:3" ht="38.25" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>193</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="34" customHeight="1">
+    <row r="41" spans="1:3" ht="33.75" customHeight="1">
       <c r="A41" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C01.Trade", Loan_C01_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5316,7 +5316,7 @@
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
     </row>
-    <row r="43" spans="1:3" ht="38" customHeight="1">
+    <row r="43" spans="1:3" ht="38.25" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>195</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="34" customHeight="1">
+    <row r="44" spans="1:3" ht="33.75" customHeight="1">
       <c r="A44" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
         <v>=IF(Loan_C01_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5336,7 +5336,7 @@
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
     </row>
-    <row r="46" spans="1:3" ht="38" customHeight="1">
+    <row r="46" spans="1:3" ht="38.25" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>197</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="34" customHeight="1">
+    <row r="47" spans="1:3" ht="33.75" customHeight="1">
       <c r="A47" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C01_Trade, Loan_Requests, , Loan_C01_Pricer)</v>
@@ -5356,7 +5356,7 @@
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
     </row>
-    <row r="49" spans="1:3" ht="38" customHeight="1">
+    <row r="49" spans="1:3" ht="38.25" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>199</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="34" customHeight="1">
+    <row r="50" spans="1:3" ht="33.75" customHeight="1">
       <c r="A50" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C01_Trade, Loan_Request0, , Loan_C01_Pricer)</v>
@@ -5388,7 +5388,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="38" customHeight="1">
+    <row r="57" spans="1:3" ht="38.25" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>192</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
     </row>
-    <row r="60" spans="1:3" ht="38" customHeight="1">
+    <row r="60" spans="1:3" ht="38.25" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>193</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="34" customHeight="1">
+    <row r="61" spans="1:3" ht="33.75" customHeight="1">
       <c r="A61" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B60),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C02.Trade", Loan_C02_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5428,7 +5428,7 @@
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
     </row>
-    <row r="63" spans="1:3" ht="38" customHeight="1">
+    <row r="63" spans="1:3" ht="38.25" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>195</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="34" customHeight="1">
+    <row r="64" spans="1:3" ht="33.75" customHeight="1">
       <c r="A64" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B63),",",", ")</f>
         <v>=IF(Loan_C02_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5448,7 +5448,7 @@
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
     </row>
-    <row r="66" spans="1:3" ht="38" customHeight="1">
+    <row r="66" spans="1:3" ht="38.25" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>197</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="34" customHeight="1">
+    <row r="67" spans="1:3" ht="33.75" customHeight="1">
       <c r="A67" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B66),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C02_Trade, Loan_Requests, , Loan_C02_Pricer)</v>
@@ -5468,7 +5468,7 @@
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
     </row>
-    <row r="69" spans="1:3" ht="38" customHeight="1">
+    <row r="69" spans="1:3" ht="38.25" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>199</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="34" customHeight="1">
+    <row r="70" spans="1:3" ht="33.75" customHeight="1">
       <c r="A70" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B69),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C02_Trade, Loan_Request0, , Loan_C02_Pricer)</v>
@@ -5500,7 +5500,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="38" customHeight="1">
+    <row r="77" spans="1:3" ht="38.25" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>201</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="34" customHeight="1">
+    <row r="78" spans="1:3" ht="33.75" customHeight="1">
       <c r="A78" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B77),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C03.Options", Loan_C03_Setting_balloonfraction)</v>
@@ -5520,7 +5520,7 @@
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
     </row>
-    <row r="80" spans="1:3" ht="38" customHeight="1">
+    <row r="80" spans="1:3" ht="38.25" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>192</v>
       </c>
@@ -5540,7 +5540,7 @@
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
     </row>
-    <row r="83" spans="1:3" ht="38" customHeight="1">
+    <row r="83" spans="1:3" ht="38.25" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>193</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="34" customHeight="1">
+    <row r="84" spans="1:3" ht="33.75" customHeight="1">
       <c r="A84" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B83),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C03.Trade", Loan_C03_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5560,7 +5560,7 @@
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
     </row>
-    <row r="86" spans="1:3" ht="38" customHeight="1">
+    <row r="86" spans="1:3" ht="38.25" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>195</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="34" customHeight="1">
+    <row r="87" spans="1:3" ht="33.75" customHeight="1">
       <c r="A87" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B86),",",", ")</f>
         <v>=IF(Loan_C03_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5580,7 +5580,7 @@
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
     </row>
-    <row r="89" spans="1:3" ht="38" customHeight="1">
+    <row r="89" spans="1:3" ht="38.25" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>197</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="34" customHeight="1">
+    <row r="90" spans="1:3" ht="33.75" customHeight="1">
       <c r="A90" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B89),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C03_Trade, Loan_Requests, , Loan_C03_Pricer)</v>
@@ -5600,7 +5600,7 @@
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
     </row>
-    <row r="92" spans="1:3" ht="38" customHeight="1">
+    <row r="92" spans="1:3" ht="38.25" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>199</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="34" customHeight="1">
+    <row r="93" spans="1:3" ht="33.75" customHeight="1">
       <c r="A93" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B92),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C03_Trade, Loan_Request0, , Loan_C03_Pricer)</v>
@@ -5632,7 +5632,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="38" customHeight="1">
+    <row r="100" spans="1:3" ht="38.25" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>201</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="34" customHeight="1">
+    <row r="101" spans="1:3" ht="33.75" customHeight="1">
       <c r="A101" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B100),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C04.Options", , Loan_C04_Setting_amortizationrate)</v>
@@ -5652,7 +5652,7 @@
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
     </row>
-    <row r="103" spans="1:3" ht="38" customHeight="1">
+    <row r="103" spans="1:3" ht="38.25" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>192</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
     </row>
-    <row r="106" spans="1:3" ht="38" customHeight="1">
+    <row r="106" spans="1:3" ht="38.25" customHeight="1">
       <c r="A106" s="4" t="s">
         <v>193</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="34" customHeight="1">
+    <row r="107" spans="1:3" ht="33.75" customHeight="1">
       <c r="A107" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B106),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C04.Trade", Loan_C04_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5692,7 +5692,7 @@
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
     </row>
-    <row r="109" spans="1:3" ht="38" customHeight="1">
+    <row r="109" spans="1:3" ht="38.25" customHeight="1">
       <c r="A109" s="4" t="s">
         <v>195</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="34" customHeight="1">
+    <row r="110" spans="1:3" ht="33.75" customHeight="1">
       <c r="A110" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B109),",",", ")</f>
         <v>=IF(Loan_C04_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5712,7 +5712,7 @@
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
     </row>
-    <row r="112" spans="1:3" ht="38" customHeight="1">
+    <row r="112" spans="1:3" ht="38.25" customHeight="1">
       <c r="A112" s="4" t="s">
         <v>197</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="34" customHeight="1">
+    <row r="113" spans="1:3" ht="33.75" customHeight="1">
       <c r="A113" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B112),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C04_Trade, Loan_Requests, , Loan_C04_Pricer)</v>
@@ -5732,7 +5732,7 @@
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
     </row>
-    <row r="115" spans="1:3" ht="38" customHeight="1">
+    <row r="115" spans="1:3" ht="38.25" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>199</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="34" customHeight="1">
+    <row r="116" spans="1:3" ht="33.75" customHeight="1">
       <c r="A116" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B115),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C04_Trade, Loan_Request0, , Loan_C04_Pricer)</v>
@@ -5764,7 +5764,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="38" customHeight="1">
+    <row r="123" spans="1:3" ht="38.25" customHeight="1">
       <c r="A123" s="4" t="s">
         <v>192</v>
       </c>
@@ -5784,7 +5784,7 @@
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
     </row>
-    <row r="126" spans="1:3" ht="38" customHeight="1">
+    <row r="126" spans="1:3" ht="38.25" customHeight="1">
       <c r="A126" s="4" t="s">
         <v>193</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="34" customHeight="1">
+    <row r="127" spans="1:3" ht="33.75" customHeight="1">
       <c r="A127" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B126),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C05.Trade", Loan_C05_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5804,7 +5804,7 @@
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
     </row>
-    <row r="129" spans="1:3" ht="38" customHeight="1">
+    <row r="129" spans="1:3" ht="38.25" customHeight="1">
       <c r="A129" s="4" t="s">
         <v>195</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="34" customHeight="1">
+    <row r="130" spans="1:3" ht="33.75" customHeight="1">
       <c r="A130" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B129),",",", ")</f>
         <v>=IF(Loan_C05_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5824,7 +5824,7 @@
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
     </row>
-    <row r="132" spans="1:3" ht="38" customHeight="1">
+    <row r="132" spans="1:3" ht="38.25" customHeight="1">
       <c r="A132" s="4" t="s">
         <v>197</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="34" customHeight="1">
+    <row r="133" spans="1:3" ht="33.75" customHeight="1">
       <c r="A133" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B132),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Requests, , Loan_C05_Pricer)</v>
@@ -5844,7 +5844,7 @@
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
     </row>
-    <row r="135" spans="1:3" ht="38" customHeight="1">
+    <row r="135" spans="1:3" ht="38.25" customHeight="1">
       <c r="A135" s="4" t="s">
         <v>199</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="34" customHeight="1">
+    <row r="136" spans="1:3" ht="33.75" customHeight="1">
       <c r="A136" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B135),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Request0, , Loan_C05_Pricer)</v>
@@ -5864,7 +5864,7 @@
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
     </row>
-    <row r="138" spans="1:3" ht="38" customHeight="1">
+    <row r="138" spans="1:3" ht="38.25" customHeight="1">
       <c r="A138" s="4" t="s">
         <v>203</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="34" customHeight="1">
+    <row r="139" spans="1:3" ht="33.75" customHeight="1">
       <c r="A139" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B138),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C05_Trade, Loan_Request1, , Loan_C05_Pricer)</v>
@@ -5896,7 +5896,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="38" customHeight="1">
+    <row r="146" spans="1:3" ht="38.25" customHeight="1">
       <c r="A146" s="4" t="s">
         <v>201</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="34" customHeight="1">
+    <row r="147" spans="1:3" ht="33.75" customHeight="1">
       <c r="A147" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B146),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C06.Options", , Loan_C06_Setting_amortizationrate, , , , , , , , Loan_C06_Setting_floor, Loan_C06_Setting_cap)</v>
@@ -5916,7 +5916,7 @@
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
     </row>
-    <row r="149" spans="1:3" ht="38" customHeight="1">
+    <row r="149" spans="1:3" ht="38.25" customHeight="1">
       <c r="A149" s="4" t="s">
         <v>192</v>
       </c>
@@ -5936,7 +5936,7 @@
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
     </row>
-    <row r="152" spans="1:3" ht="38" customHeight="1">
+    <row r="152" spans="1:3" ht="38.25" customHeight="1">
       <c r="A152" s="4" t="s">
         <v>193</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="34" customHeight="1">
+    <row r="153" spans="1:3" ht="33.75" customHeight="1">
       <c r="A153" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B152),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C06.Trade", Loan_C06_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -5956,7 +5956,7 @@
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
     </row>
-    <row r="155" spans="1:3" ht="38" customHeight="1">
+    <row r="155" spans="1:3" ht="38.25" customHeight="1">
       <c r="A155" s="4" t="s">
         <v>195</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="34" customHeight="1">
+    <row r="156" spans="1:3" ht="33.75" customHeight="1">
       <c r="A156" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B155),",",", ")</f>
         <v>=IF(Loan_C06_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -5976,7 +5976,7 @@
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
     </row>
-    <row r="158" spans="1:3" ht="38" customHeight="1">
+    <row r="158" spans="1:3" ht="38.25" customHeight="1">
       <c r="A158" s="4" t="s">
         <v>197</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="34" customHeight="1">
+    <row r="159" spans="1:3" ht="33.75" customHeight="1">
       <c r="A159" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B158),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C06_Trade, Loan_Requests, , Loan_C06_Pricer)</v>
@@ -6008,7 +6008,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="38" customHeight="1">
+    <row r="166" spans="1:3" ht="38.25" customHeight="1">
       <c r="A166" s="4" t="s">
         <v>201</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="34" customHeight="1">
+    <row r="167" spans="1:3" ht="33.75" customHeight="1">
       <c r="A167" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B166),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C07.Options", , , , , , , , , , , , , , Loan_C07_Setting_annualcpr)</v>
@@ -6028,7 +6028,7 @@
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
     </row>
-    <row r="169" spans="1:3" ht="38" customHeight="1">
+    <row r="169" spans="1:3" ht="38.25" customHeight="1">
       <c r="A169" s="4" t="s">
         <v>192</v>
       </c>
@@ -6048,7 +6048,7 @@
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
     </row>
-    <row r="172" spans="1:3" ht="38" customHeight="1">
+    <row r="172" spans="1:3" ht="38.25" customHeight="1">
       <c r="A172" s="4" t="s">
         <v>193</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="34" customHeight="1">
+    <row r="173" spans="1:3" ht="33.75" customHeight="1">
       <c r="A173" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B172),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C07.Trade", Loan_C07_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6068,7 +6068,7 @@
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
     </row>
-    <row r="175" spans="1:3" ht="38" customHeight="1">
+    <row r="175" spans="1:3" ht="38.25" customHeight="1">
       <c r="A175" s="4" t="s">
         <v>195</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="34" customHeight="1">
+    <row r="176" spans="1:3" ht="33.75" customHeight="1">
       <c r="A176" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B175),",",", ")</f>
         <v>=IF(Loan_C07_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6088,7 +6088,7 @@
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
     </row>
-    <row r="178" spans="1:3" ht="38" customHeight="1">
+    <row r="178" spans="1:3" ht="38.25" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>197</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="34" customHeight="1">
+    <row r="179" spans="1:3" ht="33.75" customHeight="1">
       <c r="A179" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B178),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C07_Trade, Loan_Requests, , Loan_C07_Pricer)</v>
@@ -6108,7 +6108,7 @@
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
     </row>
-    <row r="181" spans="1:3" ht="38" customHeight="1">
+    <row r="181" spans="1:3" ht="38.25" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>199</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="34" customHeight="1">
+    <row r="182" spans="1:3" ht="33.75" customHeight="1">
       <c r="A182" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B181),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C07_Trade, Loan_Request0, , Loan_C07_Pricer)</v>
@@ -6140,7 +6140,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="38" customHeight="1">
+    <row r="189" spans="1:3" ht="38.25" customHeight="1">
       <c r="A189" s="4" t="s">
         <v>201</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="34" customHeight="1">
+    <row r="190" spans="1:3" ht="33.75" customHeight="1">
       <c r="A190" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B189),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C08.Options", , , Loan_C08_Setting_creditindex, Loan_C08_Setting_recovery)</v>
@@ -6160,7 +6160,7 @@
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
     </row>
-    <row r="192" spans="1:3" ht="38" customHeight="1">
+    <row r="192" spans="1:3" ht="38.25" customHeight="1">
       <c r="A192" s="4" t="s">
         <v>192</v>
       </c>
@@ -6180,7 +6180,7 @@
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
     </row>
-    <row r="195" spans="1:3" ht="38" customHeight="1">
+    <row r="195" spans="1:3" ht="38.25" customHeight="1">
       <c r="A195" s="4" t="s">
         <v>193</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="34" customHeight="1">
+    <row r="196" spans="1:3" ht="33.75" customHeight="1">
       <c r="A196" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B195),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C08.Trade", Loan_C08_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6200,7 +6200,7 @@
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
     </row>
-    <row r="198" spans="1:3" ht="38" customHeight="1">
+    <row r="198" spans="1:3" ht="38.25" customHeight="1">
       <c r="A198" s="4" t="s">
         <v>195</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="34" customHeight="1">
+    <row r="199" spans="1:3" ht="33.75" customHeight="1">
       <c r="A199" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B198),",",", ")</f>
         <v>=IF(Loan_C08_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6220,7 +6220,7 @@
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
     </row>
-    <row r="201" spans="1:3" ht="38" customHeight="1">
+    <row r="201" spans="1:3" ht="38.25" customHeight="1">
       <c r="A201" s="4" t="s">
         <v>197</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="34" customHeight="1">
+    <row r="202" spans="1:3" ht="33.75" customHeight="1">
       <c r="A202" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B201),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C08_Trade, Loan_Requests, , Loan_C08_Pricer)</v>
@@ -6240,7 +6240,7 @@
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
     </row>
-    <row r="204" spans="1:3" ht="38" customHeight="1">
+    <row r="204" spans="1:3" ht="38.25" customHeight="1">
       <c r="A204" s="4" t="s">
         <v>199</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="34" customHeight="1">
+    <row r="205" spans="1:3" ht="33.75" customHeight="1">
       <c r="A205" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B204),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C08_Trade, Loan_Request0, , Loan_C08_Pricer)</v>
@@ -6272,7 +6272,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="38" customHeight="1">
+    <row r="212" spans="1:3" ht="38.25" customHeight="1">
       <c r="A212" s="4" t="s">
         <v>192</v>
       </c>
@@ -6292,7 +6292,7 @@
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
     </row>
-    <row r="215" spans="1:3" ht="38" customHeight="1">
+    <row r="215" spans="1:3" ht="38.25" customHeight="1">
       <c r="A215" s="4" t="s">
         <v>193</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="34" customHeight="1">
+    <row r="216" spans="1:3" ht="33.75" customHeight="1">
       <c r="A216" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B215),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C09.Trade", Loan_C09_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6312,7 +6312,7 @@
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
     </row>
-    <row r="218" spans="1:3" ht="38" customHeight="1">
+    <row r="218" spans="1:3" ht="38.25" customHeight="1">
       <c r="A218" s="4" t="s">
         <v>195</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="34" customHeight="1">
+    <row r="219" spans="1:3" ht="33.75" customHeight="1">
       <c r="A219" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B218),",",", ")</f>
         <v>=IF(Loan_C09_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6332,7 +6332,7 @@
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
     </row>
-    <row r="221" spans="1:3" ht="38" customHeight="1">
+    <row r="221" spans="1:3" ht="38.25" customHeight="1">
       <c r="A221" s="4" t="s">
         <v>197</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="34" customHeight="1">
+    <row r="222" spans="1:3" ht="33.75" customHeight="1">
       <c r="A222" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B221),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C09_Trade, Loan_Requests, , Loan_C09_Pricer)</v>
@@ -6352,7 +6352,7 @@
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
     </row>
-    <row r="224" spans="1:3" ht="38" customHeight="1">
+    <row r="224" spans="1:3" ht="38.25" customHeight="1">
       <c r="A224" s="4" t="s">
         <v>199</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="34" customHeight="1">
+    <row r="225" spans="1:3" ht="33.75" customHeight="1">
       <c r="A225" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B224),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C09_Trade, Loan_Request0, , Loan_C09_Pricer)</v>
@@ -6384,7 +6384,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="38" customHeight="1">
+    <row r="232" spans="1:3" ht="38.25" customHeight="1">
       <c r="A232" s="4" t="s">
         <v>201</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="34" customHeight="1">
+    <row r="233" spans="1:3" ht="33.75" customHeight="1">
       <c r="A233" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B232),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Loan.C10.Options", , Loan_C10_Setting_amortizationrate)</v>
@@ -6404,7 +6404,7 @@
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
     </row>
-    <row r="235" spans="1:3" ht="38" customHeight="1">
+    <row r="235" spans="1:3" ht="38.25" customHeight="1">
       <c r="A235" s="4" t="s">
         <v>192</v>
       </c>
@@ -6424,7 +6424,7 @@
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
     </row>
-    <row r="238" spans="1:3" ht="38" customHeight="1">
+    <row r="238" spans="1:3" ht="38.25" customHeight="1">
       <c r="A238" s="4" t="s">
         <v>193</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="34" customHeight="1">
+    <row r="239" spans="1:3" ht="33.75" customHeight="1">
       <c r="A239" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B238),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C10.Trade", Loan_C10_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6444,7 +6444,7 @@
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
     </row>
-    <row r="241" spans="1:3" ht="38" customHeight="1">
+    <row r="241" spans="1:3" ht="38.25" customHeight="1">
       <c r="A241" s="4" t="s">
         <v>195</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="34" customHeight="1">
+    <row r="242" spans="1:3" ht="33.75" customHeight="1">
       <c r="A242" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B241),",",", ")</f>
         <v>=IF(Loan_C10_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6464,7 +6464,7 @@
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
     </row>
-    <row r="244" spans="1:3" ht="38" customHeight="1">
+    <row r="244" spans="1:3" ht="38.25" customHeight="1">
       <c r="A244" s="4" t="s">
         <v>197</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="34" customHeight="1">
+    <row r="245" spans="1:3" ht="33.75" customHeight="1">
       <c r="A245" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B244),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C10_Trade, Loan_Requests, , Loan_C10_Pricer)</v>
@@ -6484,7 +6484,7 @@
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
     </row>
-    <row r="247" spans="1:3" ht="38" customHeight="1">
+    <row r="247" spans="1:3" ht="38.25" customHeight="1">
       <c r="A247" s="4" t="s">
         <v>199</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="34" customHeight="1">
+    <row r="248" spans="1:3" ht="33.75" customHeight="1">
       <c r="A248" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B247),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C10_Trade, Loan_Request0, , Loan_C10_Pricer)</v>
@@ -6516,7 +6516,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="38" customHeight="1">
+    <row r="255" spans="1:3" ht="38.25" customHeight="1">
       <c r="A255" s="4" t="s">
         <v>192</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
     </row>
-    <row r="258" spans="1:3" ht="38" customHeight="1">
+    <row r="258" spans="1:3" ht="38.25" customHeight="1">
       <c r="A258" s="4" t="s">
         <v>193</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="34" customHeight="1">
+    <row r="259" spans="1:3" ht="33.75" customHeight="1">
       <c r="A259" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B258),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C11.Trade", Loan_C11_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6556,7 +6556,7 @@
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
     </row>
-    <row r="261" spans="1:3" ht="38" customHeight="1">
+    <row r="261" spans="1:3" ht="38.25" customHeight="1">
       <c r="A261" s="4" t="s">
         <v>195</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="34" customHeight="1">
+    <row r="262" spans="1:3" ht="33.75" customHeight="1">
       <c r="A262" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B261),",",", ")</f>
         <v>=IF(Loan_C11_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6576,7 +6576,7 @@
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
     </row>
-    <row r="264" spans="1:3" ht="38" customHeight="1">
+    <row r="264" spans="1:3" ht="38.25" customHeight="1">
       <c r="A264" s="4" t="s">
         <v>197</v>
       </c>
@@ -6588,7 +6588,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="34" customHeight="1">
+    <row r="265" spans="1:3" ht="33.75" customHeight="1">
       <c r="A265" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B264),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Requests, , Loan_C11_Pricer)</v>
@@ -6596,7 +6596,7 @@
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
     </row>
-    <row r="267" spans="1:3" ht="38" customHeight="1">
+    <row r="267" spans="1:3" ht="38.25" customHeight="1">
       <c r="A267" s="4" t="s">
         <v>199</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="34" customHeight="1">
+    <row r="268" spans="1:3" ht="33.75" customHeight="1">
       <c r="A268" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B267),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request0, , Loan_C11_Pricer)</v>
@@ -6616,7 +6616,7 @@
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
     </row>
-    <row r="270" spans="1:3" ht="38" customHeight="1">
+    <row r="270" spans="1:3" ht="38.25" customHeight="1">
       <c r="A270" s="4" t="s">
         <v>203</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="34" customHeight="1">
+    <row r="271" spans="1:3" ht="33.75" customHeight="1">
       <c r="A271" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B270),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request1, , Loan_C11_Pricer)</v>
@@ -6636,7 +6636,7 @@
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
     </row>
-    <row r="273" spans="1:3" ht="38" customHeight="1">
+    <row r="273" spans="1:3" ht="38.25" customHeight="1">
       <c r="A273" s="4" t="s">
         <v>204</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="34" customHeight="1">
+    <row r="274" spans="1:3" ht="33.75" customHeight="1">
       <c r="A274" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B273),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C11_Trade, Loan_Request2, , Loan_C11_Pricer)</v>
@@ -6668,7 +6668,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="38" customHeight="1">
+    <row r="281" spans="1:3" ht="38.25" customHeight="1">
       <c r="A281" s="4" t="s">
         <v>192</v>
       </c>
@@ -6688,7 +6688,7 @@
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
     </row>
-    <row r="284" spans="1:3" ht="38" customHeight="1">
+    <row r="284" spans="1:3" ht="38.25" customHeight="1">
       <c r="A284" s="4" t="s">
         <v>193</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="34" customHeight="1">
+    <row r="285" spans="1:3" ht="33.75" customHeight="1">
       <c r="A285" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B284),",",", ")</f>
         <v>=QS.TRADE.CREATE("Loan.C12.Trade", Loan_C12_Instrument, Loan_ValuationDate, Loan_Side)</v>
@@ -6708,7 +6708,7 @@
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
     </row>
-    <row r="287" spans="1:3" ht="38" customHeight="1">
+    <row r="287" spans="1:3" ht="38.25" customHeight="1">
       <c r="A287" s="4" t="s">
         <v>195</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="34" customHeight="1">
+    <row r="288" spans="1:3" ht="33.75" customHeight="1">
       <c r="A288" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B287),",",", ")</f>
         <v>=IF(Loan_C12_Discount="FUNDING", Loan_FundingPricer, Loan_RiskFreePricer)</v>
@@ -6728,7 +6728,7 @@
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
     </row>
-    <row r="290" spans="1:3" ht="38" customHeight="1">
+    <row r="290" spans="1:3" ht="38.25" customHeight="1">
       <c r="A290" s="4" t="s">
         <v>197</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="34" customHeight="1">
+    <row r="291" spans="1:3" ht="33.75" customHeight="1">
       <c r="A291" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B290),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Requests, , Loan_C12_Pricer)</v>
@@ -6748,7 +6748,7 @@
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
     </row>
-    <row r="293" spans="1:3" ht="38" customHeight="1">
+    <row r="293" spans="1:3" ht="38.25" customHeight="1">
       <c r="A293" s="4" t="s">
         <v>199</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="34" customHeight="1">
+    <row r="294" spans="1:3" ht="33.75" customHeight="1">
       <c r="A294" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B293),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request0, , Loan_C12_Pricer)</v>
@@ -6768,7 +6768,7 @@
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
     </row>
-    <row r="296" spans="1:3" ht="38" customHeight="1">
+    <row r="296" spans="1:3" ht="38.25" customHeight="1">
       <c r="A296" s="4" t="s">
         <v>203</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="34" customHeight="1">
+    <row r="297" spans="1:3" ht="33.75" customHeight="1">
       <c r="A297" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B296),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request1, , Loan_C12_Pricer)</v>
@@ -6788,7 +6788,7 @@
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
     </row>
-    <row r="299" spans="1:3" ht="38" customHeight="1">
+    <row r="299" spans="1:3" ht="38.25" customHeight="1">
       <c r="A299" s="4" t="s">
         <v>204</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="34" customHeight="1">
+    <row r="300" spans="1:3" ht="33.75" customHeight="1">
       <c r="A300" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B299),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(Loan_Context, Loan_C12_Trade, Loan_Request2, , Loan_C12_Pricer)</v>
@@ -6925,7 +6925,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="38" customHeight="1">
+    <row r="319" spans="1:3" ht="38.25" customHeight="1">
       <c r="A319" s="4" t="s">
         <v>233</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="34" customHeight="1">
+    <row r="320" spans="1:3" ht="33.75" customHeight="1">
       <c r="A320" s="14" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B319),",",", ")</f>
         <v>=INDEX(Loan_ResultHandles, MATCH(Loan_SelectedCase, Loan_CaseNames, 0))</v>
@@ -7082,7 +7082,7 @@
     <col min="7" max="8" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38" customHeight="1">
+    <row r="1" spans="1:8" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>205</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="34" customHeight="1">
+    <row r="7" spans="1:8" ht="33.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="34" customHeight="1">
+    <row r="8" spans="1:8" ht="33.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="34" customHeight="1">
+    <row r="9" spans="1:8" ht="33.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>218</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="34" customHeight="1">
+    <row r="10" spans="1:8" ht="33.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>219</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="34" customHeight="1">
+    <row r="11" spans="1:8" ht="33.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>220</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="34" customHeight="1">
+    <row r="12" spans="1:8" ht="33.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>221</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="34" customHeight="1">
+    <row r="13" spans="1:8" ht="33.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>223</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="34" customHeight="1">
+    <row r="14" spans="1:8" ht="33.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>224</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="34" customHeight="1">
+    <row r="15" spans="1:8" ht="33.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>225</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="34" customHeight="1">
+    <row r="16" spans="1:8" ht="33.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>226</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="34" customHeight="1">
+    <row r="17" spans="1:8" ht="33.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>227</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="34" customHeight="1">
+    <row r="18" spans="1:8" ht="33.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>228</v>
       </c>
@@ -7583,7 +7583,7 @@
     <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38" customHeight="1">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>236</v>
       </c>
@@ -7678,7 +7678,7 @@
     <col min="3" max="3" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>241</v>
       </c>
@@ -7756,7 +7756,7 @@
     <col min="5" max="6" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38" customHeight="1">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>244</v>
       </c>
